--- a/Scrum-Project-Management.xlsx
+++ b/Scrum-Project-Management.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Universidad\Cursos 9no semestre\Taller de proyectos 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Universidad\Cursos 9no semestre\Taller de proyectos 1\IDEA-PROYECTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA18670F-470A-4B1D-85FF-3C5E6BA5C732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3811CC63-30A2-4612-962D-9E0DD8643056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LO Diagrama de Gantt y Burndown" sheetId="1" r:id="rId1"/>
@@ -2472,6 +2472,34 @@
     <xf numFmtId="0" fontId="37" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2492,7 +2520,6 @@
     <xf numFmtId="0" fontId="13" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2500,8 +2527,6 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2520,31 +2545,6 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5503,7 +5503,7 @@
       <c r="H3" s="40"/>
       <c r="I3" s="40"/>
       <c r="J3" s="41"/>
-      <c r="K3" s="236" t="s">
+      <c r="K3" s="250" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="42" t="s">
@@ -5582,7 +5582,7 @@
       <c r="H4" s="40"/>
       <c r="I4" s="40"/>
       <c r="J4" s="41"/>
-      <c r="K4" s="237"/>
+      <c r="K4" s="251"/>
       <c r="L4" s="47" t="s">
         <v>3</v>
       </c>
@@ -5659,7 +5659,7 @@
       <c r="H5" s="37"/>
       <c r="I5" s="36"/>
       <c r="J5" s="37"/>
-      <c r="K5" s="237"/>
+      <c r="K5" s="251"/>
       <c r="L5" s="52" t="s">
         <v>4</v>
       </c>
@@ -5736,7 +5736,7 @@
       <c r="H6" s="37"/>
       <c r="I6" s="36"/>
       <c r="J6" s="37"/>
-      <c r="K6" s="237"/>
+      <c r="K6" s="251"/>
       <c r="L6" s="54" t="s">
         <v>5</v>
       </c>
@@ -5813,7 +5813,7 @@
       <c r="H7" s="37"/>
       <c r="I7" s="36"/>
       <c r="J7" s="37"/>
-      <c r="K7" s="238"/>
+      <c r="K7" s="252"/>
       <c r="L7" s="56" t="s">
         <v>6</v>
       </c>
@@ -5881,122 +5881,122 @@
       <c r="BV7" s="39"/>
     </row>
     <row r="8" spans="1:74" ht="23.1" customHeight="1">
-      <c r="B8" s="253" t="s">
+      <c r="B8" s="233" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="261" t="s">
+      <c r="C8" s="242" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="257" t="s">
+      <c r="D8" s="237" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="233" t="s">
+      <c r="E8" s="247" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="234"/>
-      <c r="G8" s="235"/>
-      <c r="H8" s="255" t="s">
+      <c r="F8" s="248"/>
+      <c r="G8" s="249"/>
+      <c r="H8" s="235" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="259" t="s">
+      <c r="I8" s="239" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="260" t="s">
+      <c r="J8" s="240" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="239" t="s">
+      <c r="K8" s="253" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="241" t="s">
+      <c r="L8" s="254" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="243" t="s">
+      <c r="M8" s="256" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="244"/>
-      <c r="O8" s="244"/>
-      <c r="P8" s="244"/>
-      <c r="Q8" s="245"/>
-      <c r="R8" s="246" t="s">
+      <c r="N8" s="231"/>
+      <c r="O8" s="231"/>
+      <c r="P8" s="231"/>
+      <c r="Q8" s="232"/>
+      <c r="R8" s="257" t="s">
         <v>17</v>
       </c>
-      <c r="S8" s="244"/>
-      <c r="T8" s="244"/>
-      <c r="U8" s="244"/>
-      <c r="V8" s="245"/>
-      <c r="W8" s="246" t="s">
+      <c r="S8" s="231"/>
+      <c r="T8" s="231"/>
+      <c r="U8" s="231"/>
+      <c r="V8" s="232"/>
+      <c r="W8" s="257" t="s">
         <v>18</v>
       </c>
-      <c r="X8" s="244"/>
-      <c r="Y8" s="244"/>
-      <c r="Z8" s="244"/>
-      <c r="AA8" s="245"/>
-      <c r="AB8" s="248" t="s">
+      <c r="X8" s="231"/>
+      <c r="Y8" s="231"/>
+      <c r="Z8" s="231"/>
+      <c r="AA8" s="232"/>
+      <c r="AB8" s="259" t="s">
         <v>19</v>
       </c>
-      <c r="AC8" s="244"/>
-      <c r="AD8" s="244"/>
-      <c r="AE8" s="244"/>
-      <c r="AF8" s="245"/>
-      <c r="AG8" s="249" t="s">
+      <c r="AC8" s="231"/>
+      <c r="AD8" s="231"/>
+      <c r="AE8" s="231"/>
+      <c r="AF8" s="232"/>
+      <c r="AG8" s="260" t="s">
         <v>20</v>
       </c>
-      <c r="AH8" s="244"/>
-      <c r="AI8" s="244"/>
-      <c r="AJ8" s="244"/>
-      <c r="AK8" s="245"/>
-      <c r="AL8" s="249" t="s">
+      <c r="AH8" s="231"/>
+      <c r="AI8" s="231"/>
+      <c r="AJ8" s="231"/>
+      <c r="AK8" s="232"/>
+      <c r="AL8" s="260" t="s">
         <v>21</v>
       </c>
-      <c r="AM8" s="244"/>
-      <c r="AN8" s="244"/>
-      <c r="AO8" s="244"/>
-      <c r="AP8" s="245"/>
-      <c r="AQ8" s="247" t="s">
+      <c r="AM8" s="231"/>
+      <c r="AN8" s="231"/>
+      <c r="AO8" s="231"/>
+      <c r="AP8" s="232"/>
+      <c r="AQ8" s="258" t="s">
         <v>22</v>
       </c>
-      <c r="AR8" s="244"/>
-      <c r="AS8" s="244"/>
-      <c r="AT8" s="244"/>
-      <c r="AU8" s="245"/>
-      <c r="AV8" s="250" t="s">
+      <c r="AR8" s="231"/>
+      <c r="AS8" s="231"/>
+      <c r="AT8" s="231"/>
+      <c r="AU8" s="232"/>
+      <c r="AV8" s="261" t="s">
         <v>23</v>
       </c>
-      <c r="AW8" s="244"/>
-      <c r="AX8" s="244"/>
-      <c r="AY8" s="244"/>
-      <c r="AZ8" s="245"/>
-      <c r="BA8" s="250" t="s">
+      <c r="AW8" s="231"/>
+      <c r="AX8" s="231"/>
+      <c r="AY8" s="231"/>
+      <c r="AZ8" s="232"/>
+      <c r="BA8" s="261" t="s">
         <v>24</v>
       </c>
-      <c r="BB8" s="244"/>
-      <c r="BC8" s="244"/>
-      <c r="BD8" s="244"/>
-      <c r="BE8" s="245"/>
-      <c r="BF8" s="251" t="s">
+      <c r="BB8" s="231"/>
+      <c r="BC8" s="231"/>
+      <c r="BD8" s="231"/>
+      <c r="BE8" s="232"/>
+      <c r="BF8" s="262" t="s">
         <v>25</v>
       </c>
-      <c r="BG8" s="244"/>
-      <c r="BH8" s="244"/>
-      <c r="BI8" s="244"/>
-      <c r="BJ8" s="245"/>
-      <c r="BK8" s="252"/>
-      <c r="BL8" s="244"/>
-      <c r="BM8" s="244"/>
-      <c r="BN8" s="244"/>
-      <c r="BO8" s="245"/>
-      <c r="BP8" s="252"/>
-      <c r="BQ8" s="244"/>
-      <c r="BR8" s="244"/>
-      <c r="BS8" s="244"/>
-      <c r="BT8" s="245"/>
+      <c r="BG8" s="231"/>
+      <c r="BH8" s="231"/>
+      <c r="BI8" s="231"/>
+      <c r="BJ8" s="232"/>
+      <c r="BK8" s="230"/>
+      <c r="BL8" s="231"/>
+      <c r="BM8" s="231"/>
+      <c r="BN8" s="231"/>
+      <c r="BO8" s="232"/>
+      <c r="BP8" s="230"/>
+      <c r="BQ8" s="231"/>
+      <c r="BR8" s="231"/>
+      <c r="BS8" s="231"/>
+      <c r="BT8" s="232"/>
       <c r="BU8" s="38"/>
       <c r="BV8" s="39"/>
     </row>
     <row r="9" spans="1:74" ht="23.1" customHeight="1" thickBot="1">
-      <c r="B9" s="254"/>
-      <c r="C9" s="262"/>
-      <c r="D9" s="258"/>
+      <c r="B9" s="234"/>
+      <c r="C9" s="243"/>
+      <c r="D9" s="238"/>
       <c r="E9" s="58" t="s">
         <v>28</v>
       </c>
@@ -6006,11 +6006,11 @@
       <c r="G9" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="256"/>
-      <c r="I9" s="245"/>
-      <c r="J9" s="240"/>
-      <c r="K9" s="240"/>
-      <c r="L9" s="242"/>
+      <c r="H9" s="236"/>
+      <c r="I9" s="232"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="255"/>
       <c r="M9" s="61" t="s">
         <v>31</v>
       </c>
@@ -8481,12 +8481,10 @@
         <v>4</v>
       </c>
       <c r="F35" s="198">
-        <f>SUM(F36:F39)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G35" s="199">
-        <f>SUM(G36:G39)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H35" s="200"/>
       <c r="I35" s="206">
@@ -8501,7 +8499,7 @@
       </c>
       <c r="L35" s="201">
         <f t="shared" si="4"/>
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M35" s="73"/>
       <c r="N35" s="74"/>
@@ -8671,11 +8669,11 @@
         <v>1</v>
       </c>
       <c r="F37" s="154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="155">
         <f>E37-F37</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="212"/>
       <c r="I37" s="157"/>
@@ -8683,7 +8681,7 @@
       <c r="K37" s="213"/>
       <c r="L37" s="201">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="73"/>
       <c r="N37" s="74"/>
@@ -8762,11 +8760,11 @@
         <v>1</v>
       </c>
       <c r="F38" s="154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="155">
         <f>E38-F38</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="212"/>
       <c r="I38" s="157"/>
@@ -8774,7 +8772,7 @@
       <c r="K38" s="213"/>
       <c r="L38" s="201">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="73"/>
       <c r="N38" s="74"/>
@@ -8853,11 +8851,11 @@
         <v>1</v>
       </c>
       <c r="F39" s="220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="190">
         <f>E39-F39</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="221"/>
       <c r="I39" s="222"/>
@@ -8865,7 +8863,7 @@
       <c r="K39" s="214"/>
       <c r="L39" s="201">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="73"/>
       <c r="N39" s="74"/>
@@ -9029,11 +9027,11 @@
       </c>
       <c r="F41" s="216">
         <f>SUM(F11:F14,F16:F19,F21:F24,F26:F29,F31:F34,F36:F39)</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G41" s="216">
         <f>SUM(G11:G14,G16:G19,G21:G24,G26:G29,G31:G34,G36:G39)</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H41" s="217">
         <v>7</v>
@@ -9535,89 +9533,82 @@
     <row r="47" spans="2:74" ht="381.95" customHeight="1"/>
     <row r="48" spans="2:74" ht="216.95" customHeight="1"/>
     <row r="50" spans="2:74" ht="50.1" customHeight="1">
-      <c r="B50" s="230"/>
-      <c r="C50" s="231"/>
-      <c r="D50" s="231"/>
-      <c r="E50" s="231"/>
-      <c r="F50" s="231"/>
-      <c r="G50" s="231"/>
-      <c r="H50" s="231"/>
-      <c r="I50" s="231"/>
-      <c r="J50" s="231"/>
-      <c r="K50" s="231"/>
-      <c r="L50" s="231"/>
-      <c r="M50" s="231"/>
-      <c r="N50" s="231"/>
-      <c r="O50" s="231"/>
-      <c r="P50" s="231"/>
-      <c r="Q50" s="231"/>
-      <c r="R50" s="231"/>
-      <c r="S50" s="231"/>
-      <c r="T50" s="231"/>
-      <c r="U50" s="231"/>
-      <c r="V50" s="231"/>
-      <c r="W50" s="231"/>
-      <c r="X50" s="231"/>
-      <c r="Y50" s="231"/>
-      <c r="Z50" s="231"/>
-      <c r="AA50" s="231"/>
-      <c r="AB50" s="231"/>
-      <c r="AC50" s="231"/>
-      <c r="AD50" s="231"/>
-      <c r="AE50" s="231"/>
-      <c r="AF50" s="231"/>
-      <c r="AG50" s="231"/>
-      <c r="AH50" s="231"/>
-      <c r="AI50" s="231"/>
-      <c r="AJ50" s="231"/>
-      <c r="AK50" s="231"/>
-      <c r="AL50" s="231"/>
-      <c r="AM50" s="231"/>
-      <c r="AN50" s="231"/>
-      <c r="AO50" s="231"/>
-      <c r="AP50" s="231"/>
-      <c r="AQ50" s="231"/>
-      <c r="AR50" s="231"/>
-      <c r="AS50" s="231"/>
-      <c r="AT50" s="231"/>
-      <c r="AU50" s="231"/>
-      <c r="AV50" s="231"/>
-      <c r="AW50" s="231"/>
-      <c r="AX50" s="231"/>
-      <c r="AY50" s="231"/>
-      <c r="AZ50" s="231"/>
-      <c r="BA50" s="231"/>
-      <c r="BB50" s="231"/>
-      <c r="BC50" s="231"/>
-      <c r="BD50" s="231"/>
-      <c r="BE50" s="231"/>
-      <c r="BF50" s="231"/>
-      <c r="BG50" s="231"/>
-      <c r="BH50" s="231"/>
-      <c r="BI50" s="231"/>
-      <c r="BJ50" s="231"/>
-      <c r="BK50" s="231"/>
-      <c r="BL50" s="231"/>
-      <c r="BM50" s="231"/>
-      <c r="BN50" s="231"/>
-      <c r="BO50" s="231"/>
-      <c r="BP50" s="231"/>
-      <c r="BQ50" s="231"/>
-      <c r="BR50" s="231"/>
-      <c r="BS50" s="231"/>
-      <c r="BT50" s="231"/>
-      <c r="BU50" s="231"/>
-      <c r="BV50" s="232"/>
+      <c r="B50" s="244"/>
+      <c r="C50" s="245"/>
+      <c r="D50" s="245"/>
+      <c r="E50" s="245"/>
+      <c r="F50" s="245"/>
+      <c r="G50" s="245"/>
+      <c r="H50" s="245"/>
+      <c r="I50" s="245"/>
+      <c r="J50" s="245"/>
+      <c r="K50" s="245"/>
+      <c r="L50" s="245"/>
+      <c r="M50" s="245"/>
+      <c r="N50" s="245"/>
+      <c r="O50" s="245"/>
+      <c r="P50" s="245"/>
+      <c r="Q50" s="245"/>
+      <c r="R50" s="245"/>
+      <c r="S50" s="245"/>
+      <c r="T50" s="245"/>
+      <c r="U50" s="245"/>
+      <c r="V50" s="245"/>
+      <c r="W50" s="245"/>
+      <c r="X50" s="245"/>
+      <c r="Y50" s="245"/>
+      <c r="Z50" s="245"/>
+      <c r="AA50" s="245"/>
+      <c r="AB50" s="245"/>
+      <c r="AC50" s="245"/>
+      <c r="AD50" s="245"/>
+      <c r="AE50" s="245"/>
+      <c r="AF50" s="245"/>
+      <c r="AG50" s="245"/>
+      <c r="AH50" s="245"/>
+      <c r="AI50" s="245"/>
+      <c r="AJ50" s="245"/>
+      <c r="AK50" s="245"/>
+      <c r="AL50" s="245"/>
+      <c r="AM50" s="245"/>
+      <c r="AN50" s="245"/>
+      <c r="AO50" s="245"/>
+      <c r="AP50" s="245"/>
+      <c r="AQ50" s="245"/>
+      <c r="AR50" s="245"/>
+      <c r="AS50" s="245"/>
+      <c r="AT50" s="245"/>
+      <c r="AU50" s="245"/>
+      <c r="AV50" s="245"/>
+      <c r="AW50" s="245"/>
+      <c r="AX50" s="245"/>
+      <c r="AY50" s="245"/>
+      <c r="AZ50" s="245"/>
+      <c r="BA50" s="245"/>
+      <c r="BB50" s="245"/>
+      <c r="BC50" s="245"/>
+      <c r="BD50" s="245"/>
+      <c r="BE50" s="245"/>
+      <c r="BF50" s="245"/>
+      <c r="BG50" s="245"/>
+      <c r="BH50" s="245"/>
+      <c r="BI50" s="245"/>
+      <c r="BJ50" s="245"/>
+      <c r="BK50" s="245"/>
+      <c r="BL50" s="245"/>
+      <c r="BM50" s="245"/>
+      <c r="BN50" s="245"/>
+      <c r="BO50" s="245"/>
+      <c r="BP50" s="245"/>
+      <c r="BQ50" s="245"/>
+      <c r="BR50" s="245"/>
+      <c r="BS50" s="245"/>
+      <c r="BT50" s="245"/>
+      <c r="BU50" s="245"/>
+      <c r="BV50" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="BP8:BT8"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="C8:C9"/>
     <mergeCell ref="B50:BV50"/>
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="K3:K7"/>
@@ -9634,6 +9625,13 @@
     <mergeCell ref="BA8:BE8"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="BK8:BO8"/>
+    <mergeCell ref="BP8:BT8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="C8:C9"/>
   </mergeCells>
   <phoneticPr fontId="34" type="noConversion"/>
   <conditionalFormatting sqref="L10">
@@ -9835,10 +9833,10 @@
         <v>127</v>
       </c>
       <c r="C9" s="209"/>
-      <c r="D9" s="228" t="s">
+      <c r="D9" s="209"/>
+      <c r="E9" s="228" t="s">
         <v>129</v>
       </c>
-      <c r="E9" s="209"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9955,7 +9953,7 @@
       <c r="H2" s="40"/>
       <c r="I2" s="40"/>
       <c r="J2" s="41"/>
-      <c r="K2" s="236" t="s">
+      <c r="K2" s="250" t="s">
         <v>1</v>
       </c>
       <c r="L2" s="42" t="s">
@@ -10034,7 +10032,7 @@
       <c r="H3" s="40"/>
       <c r="I3" s="40"/>
       <c r="J3" s="41"/>
-      <c r="K3" s="237"/>
+      <c r="K3" s="251"/>
       <c r="L3" s="47" t="s">
         <v>3</v>
       </c>
@@ -10111,7 +10109,7 @@
       <c r="H4" s="37"/>
       <c r="I4" s="36"/>
       <c r="J4" s="37"/>
-      <c r="K4" s="237"/>
+      <c r="K4" s="251"/>
       <c r="L4" s="52" t="s">
         <v>4</v>
       </c>
@@ -10188,7 +10186,7 @@
       <c r="H5" s="37"/>
       <c r="I5" s="36"/>
       <c r="J5" s="37"/>
-      <c r="K5" s="237"/>
+      <c r="K5" s="251"/>
       <c r="L5" s="54" t="s">
         <v>5</v>
       </c>
@@ -10265,7 +10263,7 @@
       <c r="H6" s="37"/>
       <c r="I6" s="36"/>
       <c r="J6" s="37"/>
-      <c r="K6" s="238"/>
+      <c r="K6" s="252"/>
       <c r="L6" s="56" t="s">
         <v>6</v>
       </c>
@@ -10333,126 +10331,126 @@
       <c r="BV6" s="39"/>
     </row>
     <row r="7" spans="2:74" ht="23.1" customHeight="1">
-      <c r="B7" s="253" t="s">
+      <c r="B7" s="233" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="261" t="s">
+      <c r="C7" s="242" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="257" t="s">
+      <c r="D7" s="237" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="233" t="s">
+      <c r="E7" s="247" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="234"/>
-      <c r="G7" s="235"/>
-      <c r="H7" s="255" t="s">
+      <c r="F7" s="248"/>
+      <c r="G7" s="249"/>
+      <c r="H7" s="235" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="259" t="s">
+      <c r="I7" s="239" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="260" t="s">
+      <c r="J7" s="240" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="239" t="s">
+      <c r="K7" s="253" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="241" t="s">
+      <c r="L7" s="254" t="s">
         <v>15</v>
       </c>
-      <c r="M7" s="243" t="s">
+      <c r="M7" s="256" t="s">
         <v>16</v>
       </c>
-      <c r="N7" s="244"/>
-      <c r="O7" s="244"/>
-      <c r="P7" s="244"/>
-      <c r="Q7" s="245"/>
-      <c r="R7" s="246" t="s">
+      <c r="N7" s="231"/>
+      <c r="O7" s="231"/>
+      <c r="P7" s="231"/>
+      <c r="Q7" s="232"/>
+      <c r="R7" s="257" t="s">
         <v>17</v>
       </c>
-      <c r="S7" s="244"/>
-      <c r="T7" s="244"/>
-      <c r="U7" s="244"/>
-      <c r="V7" s="245"/>
-      <c r="W7" s="246" t="s">
+      <c r="S7" s="231"/>
+      <c r="T7" s="231"/>
+      <c r="U7" s="231"/>
+      <c r="V7" s="232"/>
+      <c r="W7" s="257" t="s">
         <v>18</v>
       </c>
-      <c r="X7" s="244"/>
-      <c r="Y7" s="244"/>
-      <c r="Z7" s="244"/>
-      <c r="AA7" s="245"/>
-      <c r="AB7" s="248" t="s">
+      <c r="X7" s="231"/>
+      <c r="Y7" s="231"/>
+      <c r="Z7" s="231"/>
+      <c r="AA7" s="232"/>
+      <c r="AB7" s="259" t="s">
         <v>19</v>
       </c>
-      <c r="AC7" s="244"/>
-      <c r="AD7" s="244"/>
-      <c r="AE7" s="244"/>
-      <c r="AF7" s="245"/>
-      <c r="AG7" s="249" t="s">
+      <c r="AC7" s="231"/>
+      <c r="AD7" s="231"/>
+      <c r="AE7" s="231"/>
+      <c r="AF7" s="232"/>
+      <c r="AG7" s="260" t="s">
         <v>20</v>
       </c>
-      <c r="AH7" s="244"/>
-      <c r="AI7" s="244"/>
-      <c r="AJ7" s="244"/>
-      <c r="AK7" s="245"/>
-      <c r="AL7" s="249" t="s">
+      <c r="AH7" s="231"/>
+      <c r="AI7" s="231"/>
+      <c r="AJ7" s="231"/>
+      <c r="AK7" s="232"/>
+      <c r="AL7" s="260" t="s">
         <v>21</v>
       </c>
-      <c r="AM7" s="244"/>
-      <c r="AN7" s="244"/>
-      <c r="AO7" s="244"/>
-      <c r="AP7" s="245"/>
-      <c r="AQ7" s="247" t="s">
+      <c r="AM7" s="231"/>
+      <c r="AN7" s="231"/>
+      <c r="AO7" s="231"/>
+      <c r="AP7" s="232"/>
+      <c r="AQ7" s="258" t="s">
         <v>22</v>
       </c>
-      <c r="AR7" s="244"/>
-      <c r="AS7" s="244"/>
-      <c r="AT7" s="244"/>
-      <c r="AU7" s="245"/>
-      <c r="AV7" s="250" t="s">
+      <c r="AR7" s="231"/>
+      <c r="AS7" s="231"/>
+      <c r="AT7" s="231"/>
+      <c r="AU7" s="232"/>
+      <c r="AV7" s="261" t="s">
         <v>23</v>
       </c>
-      <c r="AW7" s="244"/>
-      <c r="AX7" s="244"/>
-      <c r="AY7" s="244"/>
-      <c r="AZ7" s="245"/>
-      <c r="BA7" s="250" t="s">
+      <c r="AW7" s="231"/>
+      <c r="AX7" s="231"/>
+      <c r="AY7" s="231"/>
+      <c r="AZ7" s="232"/>
+      <c r="BA7" s="261" t="s">
         <v>24</v>
       </c>
-      <c r="BB7" s="244"/>
-      <c r="BC7" s="244"/>
-      <c r="BD7" s="244"/>
-      <c r="BE7" s="245"/>
-      <c r="BF7" s="251" t="s">
+      <c r="BB7" s="231"/>
+      <c r="BC7" s="231"/>
+      <c r="BD7" s="231"/>
+      <c r="BE7" s="232"/>
+      <c r="BF7" s="262" t="s">
         <v>25</v>
       </c>
-      <c r="BG7" s="244"/>
-      <c r="BH7" s="244"/>
-      <c r="BI7" s="244"/>
-      <c r="BJ7" s="245"/>
+      <c r="BG7" s="231"/>
+      <c r="BH7" s="231"/>
+      <c r="BI7" s="231"/>
+      <c r="BJ7" s="232"/>
       <c r="BK7" s="263" t="s">
         <v>26</v>
       </c>
-      <c r="BL7" s="244"/>
-      <c r="BM7" s="244"/>
-      <c r="BN7" s="244"/>
-      <c r="BO7" s="245"/>
+      <c r="BL7" s="231"/>
+      <c r="BM7" s="231"/>
+      <c r="BN7" s="231"/>
+      <c r="BO7" s="232"/>
       <c r="BP7" s="263" t="s">
         <v>27</v>
       </c>
-      <c r="BQ7" s="244"/>
-      <c r="BR7" s="244"/>
-      <c r="BS7" s="244"/>
-      <c r="BT7" s="245"/>
+      <c r="BQ7" s="231"/>
+      <c r="BR7" s="231"/>
+      <c r="BS7" s="231"/>
+      <c r="BT7" s="232"/>
       <c r="BU7" s="38"/>
       <c r="BV7" s="39"/>
     </row>
     <row r="8" spans="2:74" ht="23.1" customHeight="1" thickBot="1">
-      <c r="B8" s="254"/>
-      <c r="C8" s="262"/>
-      <c r="D8" s="258"/>
+      <c r="B8" s="234"/>
+      <c r="C8" s="243"/>
+      <c r="D8" s="238"/>
       <c r="E8" s="58" t="s">
         <v>28</v>
       </c>
@@ -10462,11 +10460,11 @@
       <c r="G8" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="256"/>
-      <c r="I8" s="245"/>
-      <c r="J8" s="240"/>
-      <c r="K8" s="240"/>
-      <c r="L8" s="242"/>
+      <c r="H8" s="236"/>
+      <c r="I8" s="232"/>
+      <c r="J8" s="241"/>
+      <c r="K8" s="241"/>
+      <c r="L8" s="255"/>
       <c r="M8" s="61" t="s">
         <v>31</v>
       </c>
@@ -13986,6 +13984,13 @@
     <row r="42" spans="2:74" ht="216.95" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="BP7:BT7"/>
+    <mergeCell ref="AL7:AP7"/>
+    <mergeCell ref="AQ7:AU7"/>
+    <mergeCell ref="AV7:AZ7"/>
+    <mergeCell ref="BA7:BE7"/>
+    <mergeCell ref="BF7:BJ7"/>
+    <mergeCell ref="BK7:BO7"/>
     <mergeCell ref="AG7:AK7"/>
     <mergeCell ref="K2:K6"/>
     <mergeCell ref="B7:B8"/>
@@ -14001,13 +14006,6 @@
     <mergeCell ref="R7:V7"/>
     <mergeCell ref="W7:AA7"/>
     <mergeCell ref="AB7:AF7"/>
-    <mergeCell ref="BP7:BT7"/>
-    <mergeCell ref="AL7:AP7"/>
-    <mergeCell ref="AQ7:AU7"/>
-    <mergeCell ref="AV7:AZ7"/>
-    <mergeCell ref="BA7:BE7"/>
-    <mergeCell ref="BF7:BJ7"/>
-    <mergeCell ref="BK7:BO7"/>
   </mergeCells>
   <conditionalFormatting sqref="L9:L33">
     <cfRule type="dataBar" priority="1">

--- a/Scrum-Project-Management.xlsx
+++ b/Scrum-Project-Management.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\IDEA-PROYECTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8496ADCA-BD09-4529-830F-C95133DDDB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA5EA38-1FF2-4922-B283-80E448E7C4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,29 +17,30 @@
     <sheet name="Sprint 2" sheetId="7" r:id="rId2"/>
     <sheet name="Sprint 3" sheetId="8" r:id="rId3"/>
     <sheet name="Sprint 4" sheetId="9" r:id="rId4"/>
-    <sheet name="Post-It" sheetId="6" r:id="rId5"/>
-    <sheet name="a de Gantt en blanco y burndown" sheetId="2" r:id="rId6"/>
-    <sheet name="Backlog de lanzamientos" sheetId="3" r:id="rId7"/>
-    <sheet name="Historias de usuario o tareas" sheetId="4" r:id="rId8"/>
+    <sheet name="Sprint 5" sheetId="10" r:id="rId5"/>
+    <sheet name="Post-It" sheetId="6" r:id="rId6"/>
+    <sheet name="a de Gantt en blanco y burndown" sheetId="2" r:id="rId7"/>
+    <sheet name="Backlog de lanzamientos" sheetId="3" r:id="rId8"/>
+    <sheet name="Historias de usuario o tareas" sheetId="4" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'a de Gantt en blanco y burndown'!$B$1:$BV$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Backlog de lanzamientos'!$B$1:$J$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Historias de usuario o tareas'!$B$1:$E$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'a de Gantt en blanco y burndown'!$B$1:$BV$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Backlog de lanzamientos'!$B$1:$J$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Historias de usuario o tareas'!$B$1:$E$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Sprint 1'!$B$1:$BV$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Sprint 2'!$B$1:$BV$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Sprint 3'!$B$1:$BV$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Sprint 4'!$B$1:$BV$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Sprint 5'!$B$1:$BV$34</definedName>
     <definedName name="Interval">'[1]Office Work Schedule'!#REF!</definedName>
     <definedName name="ScheduleStart">'[1]Office Work Schedule'!#REF!</definedName>
     <definedName name="Type">'[2]Maintenance Work Order'!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="243">
   <si>
     <t>DIAGRAMA DE GANTT Y BURNDOWN</t>
   </si>
@@ -736,6 +737,54 @@
   </si>
   <si>
     <t>Probar recuperación de respaldo exitosamente.</t>
+  </si>
+  <si>
+    <t>HU-20: Exportación de Datos Anonimizados (8h)</t>
+  </si>
+  <si>
+    <t>HU-21: Soporte Multilenguaje (8h)</t>
+  </si>
+  <si>
+    <t>HU-30: Manual de Usuario (8h)</t>
+  </si>
+  <si>
+    <t>HU-29: Documentación Técnica (12h)</t>
+  </si>
+  <si>
+    <t>Implementar exportación de registros en formato CSV/Excel.</t>
+  </si>
+  <si>
+    <t>Asegurar eliminación de datos personales antes de exportar.</t>
+  </si>
+  <si>
+    <t>Crear estructura de archivos para traducción (Español/Quechua).</t>
+  </si>
+  <si>
+    <t>Traducir textos clave de la interfaz y mensajes del sistema.</t>
+  </si>
+  <si>
+    <t>Redactar guía detallada con pasos para usar el sistema.</t>
+  </si>
+  <si>
+    <t>Incluir capturas de pantalla y ejemplos de diagnóstico.</t>
+  </si>
+  <si>
+    <t>Documentar arquitectura general del sistema y modelo CNN.</t>
+  </si>
+  <si>
+    <t>Describir dependencias, instalación y flujo de datos.</t>
+  </si>
+  <si>
+    <t>Validar exportación correcta y legible por herramientas externas.</t>
+  </si>
+  <si>
+    <t>Implementar cambio dinámico de idioma desde la configuración.</t>
+  </si>
+  <si>
+    <t>Publicar el manual en formato PDF y en línea (web).</t>
+  </si>
+  <si>
+    <t>Crear diagrama final del sistema y anexar resultados finales.</t>
   </si>
 </sst>
 </file>
@@ -2206,7 +2255,7 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="33" fillId="32" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="271">
+  <cellXfs count="273">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2790,6 +2839,38 @@
     <xf numFmtId="1" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2810,7 +2891,6 @@
     <xf numFmtId="0" fontId="13" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2818,8 +2898,6 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2838,31 +2916,6 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5132,22 +5185,22 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5335,19 +5388,19 @@
                   <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>34</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>34</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>34</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>34</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5425,22 +5478,22 @@
                   <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>34</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>34</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>34</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>34</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>34</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5680,6 +5733,649 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 5'!$L$30</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HRS COMPLETADO</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="1"/>
+              <a:tileRect/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sprint 5'!$M$27:$BT$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 5'!$M$30:$BT$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6892-4634-8355-B1C038EDB366}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="72"/>
+        <c:axId val="1150741088"/>
+        <c:axId val="1179485168"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 5'!$L$28</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PLAN</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sprint 5'!$M$27:$BT$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 5'!$M$28:$BT$28</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>28.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.200000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6892-4634-8355-B1C038EDB366}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 5'!$L$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ESTIMAR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sprint 5'!$M$27:$BT$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 5'!$M$29:$BT$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6892-4634-8355-B1C038EDB366}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 5'!$L$31</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HRS RESTANTE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sprint 5'!$M$27:$BT$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 5'!$M$31:$BT$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6892-4634-8355-B1C038EDB366}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1180770320"/>
+        <c:axId val="1180774800"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1150741088"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1179485168"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1179485168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="36"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1150741088"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:dateAx>
+        <c:axId val="1180770320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1180774800"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="0"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="1"/>
+        <c:majorTimeUnit val="days"/>
+        <c:minorUnit val="1"/>
+        <c:minorTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1180774800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="36"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1180770320"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1050" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -7629,6 +8325,49 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>55770</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>119269</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1990725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27B9FA8E-EAC2-4709-BAB4-BB2FD1212A12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>203200</xdr:colOff>
       <xdr:row>40</xdr:row>
@@ -8011,7 +8750,7 @@
       <c r="H3" s="40"/>
       <c r="I3" s="40"/>
       <c r="J3" s="41"/>
-      <c r="K3" s="243" t="s">
+      <c r="K3" s="259" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="42" t="s">
@@ -8090,7 +8829,7 @@
       <c r="H4" s="40"/>
       <c r="I4" s="40"/>
       <c r="J4" s="41"/>
-      <c r="K4" s="244"/>
+      <c r="K4" s="260"/>
       <c r="L4" s="47" t="s">
         <v>3</v>
       </c>
@@ -8167,7 +8906,7 @@
       <c r="H5" s="37"/>
       <c r="I5" s="36"/>
       <c r="J5" s="37"/>
-      <c r="K5" s="244"/>
+      <c r="K5" s="260"/>
       <c r="L5" s="52" t="s">
         <v>4</v>
       </c>
@@ -8244,7 +8983,7 @@
       <c r="H6" s="37"/>
       <c r="I6" s="36"/>
       <c r="J6" s="37"/>
-      <c r="K6" s="244"/>
+      <c r="K6" s="260"/>
       <c r="L6" s="54" t="s">
         <v>5</v>
       </c>
@@ -8321,7 +9060,7 @@
       <c r="H7" s="37"/>
       <c r="I7" s="36"/>
       <c r="J7" s="37"/>
-      <c r="K7" s="245"/>
+      <c r="K7" s="261"/>
       <c r="L7" s="56" t="s">
         <v>6</v>
       </c>
@@ -8389,122 +9128,122 @@
       <c r="BV7" s="39"/>
     </row>
     <row r="8" spans="1:74" ht="23.1" customHeight="1">
-      <c r="B8" s="260" t="s">
+      <c r="B8" s="242" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="268" t="s">
+      <c r="C8" s="251" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="264" t="s">
+      <c r="D8" s="246" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="240" t="s">
+      <c r="E8" s="256" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="241"/>
-      <c r="G8" s="242"/>
-      <c r="H8" s="262" t="s">
+      <c r="F8" s="257"/>
+      <c r="G8" s="258"/>
+      <c r="H8" s="244" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="266" t="s">
+      <c r="I8" s="248" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="267" t="s">
+      <c r="J8" s="249" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="246" t="s">
+      <c r="K8" s="262" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="248" t="s">
+      <c r="L8" s="263" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="250" t="s">
+      <c r="M8" s="265" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="251"/>
-      <c r="O8" s="251"/>
-      <c r="P8" s="251"/>
-      <c r="Q8" s="252"/>
-      <c r="R8" s="253" t="s">
+      <c r="N8" s="240"/>
+      <c r="O8" s="240"/>
+      <c r="P8" s="240"/>
+      <c r="Q8" s="241"/>
+      <c r="R8" s="266" t="s">
         <v>17</v>
       </c>
-      <c r="S8" s="251"/>
-      <c r="T8" s="251"/>
-      <c r="U8" s="251"/>
-      <c r="V8" s="252"/>
-      <c r="W8" s="253" t="s">
+      <c r="S8" s="240"/>
+      <c r="T8" s="240"/>
+      <c r="U8" s="240"/>
+      <c r="V8" s="241"/>
+      <c r="W8" s="266" t="s">
         <v>18</v>
       </c>
-      <c r="X8" s="251"/>
-      <c r="Y8" s="251"/>
-      <c r="Z8" s="251"/>
-      <c r="AA8" s="252"/>
-      <c r="AB8" s="255" t="s">
+      <c r="X8" s="240"/>
+      <c r="Y8" s="240"/>
+      <c r="Z8" s="240"/>
+      <c r="AA8" s="241"/>
+      <c r="AB8" s="268" t="s">
         <v>19</v>
       </c>
-      <c r="AC8" s="251"/>
-      <c r="AD8" s="251"/>
-      <c r="AE8" s="251"/>
-      <c r="AF8" s="252"/>
-      <c r="AG8" s="256" t="s">
+      <c r="AC8" s="240"/>
+      <c r="AD8" s="240"/>
+      <c r="AE8" s="240"/>
+      <c r="AF8" s="241"/>
+      <c r="AG8" s="269" t="s">
         <v>20</v>
       </c>
-      <c r="AH8" s="251"/>
-      <c r="AI8" s="251"/>
-      <c r="AJ8" s="251"/>
-      <c r="AK8" s="252"/>
-      <c r="AL8" s="256" t="s">
+      <c r="AH8" s="240"/>
+      <c r="AI8" s="240"/>
+      <c r="AJ8" s="240"/>
+      <c r="AK8" s="241"/>
+      <c r="AL8" s="269" t="s">
         <v>21</v>
       </c>
-      <c r="AM8" s="251"/>
-      <c r="AN8" s="251"/>
-      <c r="AO8" s="251"/>
-      <c r="AP8" s="252"/>
-      <c r="AQ8" s="254" t="s">
+      <c r="AM8" s="240"/>
+      <c r="AN8" s="240"/>
+      <c r="AO8" s="240"/>
+      <c r="AP8" s="241"/>
+      <c r="AQ8" s="267" t="s">
         <v>22</v>
       </c>
-      <c r="AR8" s="251"/>
-      <c r="AS8" s="251"/>
-      <c r="AT8" s="251"/>
-      <c r="AU8" s="252"/>
-      <c r="AV8" s="257" t="s">
+      <c r="AR8" s="240"/>
+      <c r="AS8" s="240"/>
+      <c r="AT8" s="240"/>
+      <c r="AU8" s="241"/>
+      <c r="AV8" s="270" t="s">
         <v>23</v>
       </c>
-      <c r="AW8" s="251"/>
-      <c r="AX8" s="251"/>
-      <c r="AY8" s="251"/>
-      <c r="AZ8" s="252"/>
-      <c r="BA8" s="257" t="s">
+      <c r="AW8" s="240"/>
+      <c r="AX8" s="240"/>
+      <c r="AY8" s="240"/>
+      <c r="AZ8" s="241"/>
+      <c r="BA8" s="270" t="s">
         <v>24</v>
       </c>
-      <c r="BB8" s="251"/>
-      <c r="BC8" s="251"/>
-      <c r="BD8" s="251"/>
-      <c r="BE8" s="252"/>
-      <c r="BF8" s="258" t="s">
+      <c r="BB8" s="240"/>
+      <c r="BC8" s="240"/>
+      <c r="BD8" s="240"/>
+      <c r="BE8" s="241"/>
+      <c r="BF8" s="271" t="s">
         <v>25</v>
       </c>
-      <c r="BG8" s="251"/>
-      <c r="BH8" s="251"/>
-      <c r="BI8" s="251"/>
-      <c r="BJ8" s="252"/>
-      <c r="BK8" s="259"/>
-      <c r="BL8" s="251"/>
-      <c r="BM8" s="251"/>
-      <c r="BN8" s="251"/>
-      <c r="BO8" s="252"/>
-      <c r="BP8" s="259"/>
-      <c r="BQ8" s="251"/>
-      <c r="BR8" s="251"/>
-      <c r="BS8" s="251"/>
-      <c r="BT8" s="252"/>
+      <c r="BG8" s="240"/>
+      <c r="BH8" s="240"/>
+      <c r="BI8" s="240"/>
+      <c r="BJ8" s="241"/>
+      <c r="BK8" s="239"/>
+      <c r="BL8" s="240"/>
+      <c r="BM8" s="240"/>
+      <c r="BN8" s="240"/>
+      <c r="BO8" s="241"/>
+      <c r="BP8" s="239"/>
+      <c r="BQ8" s="240"/>
+      <c r="BR8" s="240"/>
+      <c r="BS8" s="240"/>
+      <c r="BT8" s="241"/>
       <c r="BU8" s="38"/>
       <c r="BV8" s="39"/>
     </row>
     <row r="9" spans="1:74" ht="23.1" customHeight="1" thickBot="1">
-      <c r="B9" s="261"/>
-      <c r="C9" s="269"/>
-      <c r="D9" s="265"/>
+      <c r="B9" s="243"/>
+      <c r="C9" s="252"/>
+      <c r="D9" s="247"/>
       <c r="E9" s="58" t="s">
         <v>28</v>
       </c>
@@ -8514,11 +9253,11 @@
       <c r="G9" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="263"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="247"/>
-      <c r="K9" s="247"/>
-      <c r="L9" s="249"/>
+      <c r="H9" s="245"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="250"/>
+      <c r="K9" s="250"/>
+      <c r="L9" s="264"/>
       <c r="M9" s="61" t="s">
         <v>31</v>
       </c>
@@ -12059,89 +12798,82 @@
     <row r="47" spans="2:74" ht="381.95" customHeight="1"/>
     <row r="48" spans="2:74" ht="216.95" customHeight="1"/>
     <row r="50" spans="2:74" ht="50.1" customHeight="1">
-      <c r="B50" s="237"/>
-      <c r="C50" s="238"/>
-      <c r="D50" s="238"/>
-      <c r="E50" s="238"/>
-      <c r="F50" s="238"/>
-      <c r="G50" s="238"/>
-      <c r="H50" s="238"/>
-      <c r="I50" s="238"/>
-      <c r="J50" s="238"/>
-      <c r="K50" s="238"/>
-      <c r="L50" s="238"/>
-      <c r="M50" s="238"/>
-      <c r="N50" s="238"/>
-      <c r="O50" s="238"/>
-      <c r="P50" s="238"/>
-      <c r="Q50" s="238"/>
-      <c r="R50" s="238"/>
-      <c r="S50" s="238"/>
-      <c r="T50" s="238"/>
-      <c r="U50" s="238"/>
-      <c r="V50" s="238"/>
-      <c r="W50" s="238"/>
-      <c r="X50" s="238"/>
-      <c r="Y50" s="238"/>
-      <c r="Z50" s="238"/>
-      <c r="AA50" s="238"/>
-      <c r="AB50" s="238"/>
-      <c r="AC50" s="238"/>
-      <c r="AD50" s="238"/>
-      <c r="AE50" s="238"/>
-      <c r="AF50" s="238"/>
-      <c r="AG50" s="238"/>
-      <c r="AH50" s="238"/>
-      <c r="AI50" s="238"/>
-      <c r="AJ50" s="238"/>
-      <c r="AK50" s="238"/>
-      <c r="AL50" s="238"/>
-      <c r="AM50" s="238"/>
-      <c r="AN50" s="238"/>
-      <c r="AO50" s="238"/>
-      <c r="AP50" s="238"/>
-      <c r="AQ50" s="238"/>
-      <c r="AR50" s="238"/>
-      <c r="AS50" s="238"/>
-      <c r="AT50" s="238"/>
-      <c r="AU50" s="238"/>
-      <c r="AV50" s="238"/>
-      <c r="AW50" s="238"/>
-      <c r="AX50" s="238"/>
-      <c r="AY50" s="238"/>
-      <c r="AZ50" s="238"/>
-      <c r="BA50" s="238"/>
-      <c r="BB50" s="238"/>
-      <c r="BC50" s="238"/>
-      <c r="BD50" s="238"/>
-      <c r="BE50" s="238"/>
-      <c r="BF50" s="238"/>
-      <c r="BG50" s="238"/>
-      <c r="BH50" s="238"/>
-      <c r="BI50" s="238"/>
-      <c r="BJ50" s="238"/>
-      <c r="BK50" s="238"/>
-      <c r="BL50" s="238"/>
-      <c r="BM50" s="238"/>
-      <c r="BN50" s="238"/>
-      <c r="BO50" s="238"/>
-      <c r="BP50" s="238"/>
-      <c r="BQ50" s="238"/>
-      <c r="BR50" s="238"/>
-      <c r="BS50" s="238"/>
-      <c r="BT50" s="238"/>
-      <c r="BU50" s="238"/>
-      <c r="BV50" s="239"/>
+      <c r="B50" s="253"/>
+      <c r="C50" s="254"/>
+      <c r="D50" s="254"/>
+      <c r="E50" s="254"/>
+      <c r="F50" s="254"/>
+      <c r="G50" s="254"/>
+      <c r="H50" s="254"/>
+      <c r="I50" s="254"/>
+      <c r="J50" s="254"/>
+      <c r="K50" s="254"/>
+      <c r="L50" s="254"/>
+      <c r="M50" s="254"/>
+      <c r="N50" s="254"/>
+      <c r="O50" s="254"/>
+      <c r="P50" s="254"/>
+      <c r="Q50" s="254"/>
+      <c r="R50" s="254"/>
+      <c r="S50" s="254"/>
+      <c r="T50" s="254"/>
+      <c r="U50" s="254"/>
+      <c r="V50" s="254"/>
+      <c r="W50" s="254"/>
+      <c r="X50" s="254"/>
+      <c r="Y50" s="254"/>
+      <c r="Z50" s="254"/>
+      <c r="AA50" s="254"/>
+      <c r="AB50" s="254"/>
+      <c r="AC50" s="254"/>
+      <c r="AD50" s="254"/>
+      <c r="AE50" s="254"/>
+      <c r="AF50" s="254"/>
+      <c r="AG50" s="254"/>
+      <c r="AH50" s="254"/>
+      <c r="AI50" s="254"/>
+      <c r="AJ50" s="254"/>
+      <c r="AK50" s="254"/>
+      <c r="AL50" s="254"/>
+      <c r="AM50" s="254"/>
+      <c r="AN50" s="254"/>
+      <c r="AO50" s="254"/>
+      <c r="AP50" s="254"/>
+      <c r="AQ50" s="254"/>
+      <c r="AR50" s="254"/>
+      <c r="AS50" s="254"/>
+      <c r="AT50" s="254"/>
+      <c r="AU50" s="254"/>
+      <c r="AV50" s="254"/>
+      <c r="AW50" s="254"/>
+      <c r="AX50" s="254"/>
+      <c r="AY50" s="254"/>
+      <c r="AZ50" s="254"/>
+      <c r="BA50" s="254"/>
+      <c r="BB50" s="254"/>
+      <c r="BC50" s="254"/>
+      <c r="BD50" s="254"/>
+      <c r="BE50" s="254"/>
+      <c r="BF50" s="254"/>
+      <c r="BG50" s="254"/>
+      <c r="BH50" s="254"/>
+      <c r="BI50" s="254"/>
+      <c r="BJ50" s="254"/>
+      <c r="BK50" s="254"/>
+      <c r="BL50" s="254"/>
+      <c r="BM50" s="254"/>
+      <c r="BN50" s="254"/>
+      <c r="BO50" s="254"/>
+      <c r="BP50" s="254"/>
+      <c r="BQ50" s="254"/>
+      <c r="BR50" s="254"/>
+      <c r="BS50" s="254"/>
+      <c r="BT50" s="254"/>
+      <c r="BU50" s="254"/>
+      <c r="BV50" s="255"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="BP8:BT8"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="C8:C9"/>
     <mergeCell ref="B50:BV50"/>
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="K3:K7"/>
@@ -12158,6 +12890,13 @@
     <mergeCell ref="BA8:BE8"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="BK8:BO8"/>
+    <mergeCell ref="BP8:BT8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="C8:C9"/>
   </mergeCells>
   <phoneticPr fontId="34" type="noConversion"/>
   <conditionalFormatting sqref="L10">
@@ -12397,7 +13136,7 @@
       <c r="H3" s="40"/>
       <c r="I3" s="40"/>
       <c r="J3" s="41"/>
-      <c r="K3" s="243" t="s">
+      <c r="K3" s="259" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="42" t="s">
@@ -12476,7 +13215,7 @@
       <c r="H4" s="40"/>
       <c r="I4" s="40"/>
       <c r="J4" s="41"/>
-      <c r="K4" s="244"/>
+      <c r="K4" s="260"/>
       <c r="L4" s="47" t="s">
         <v>3</v>
       </c>
@@ -12553,7 +13292,7 @@
       <c r="H5" s="37"/>
       <c r="I5" s="36"/>
       <c r="J5" s="37"/>
-      <c r="K5" s="244"/>
+      <c r="K5" s="260"/>
       <c r="L5" s="52" t="s">
         <v>4</v>
       </c>
@@ -12630,7 +13369,7 @@
       <c r="H6" s="37"/>
       <c r="I6" s="36"/>
       <c r="J6" s="37"/>
-      <c r="K6" s="244"/>
+      <c r="K6" s="260"/>
       <c r="L6" s="54" t="s">
         <v>5</v>
       </c>
@@ -12707,7 +13446,7 @@
       <c r="H7" s="37"/>
       <c r="I7" s="36"/>
       <c r="J7" s="37"/>
-      <c r="K7" s="245"/>
+      <c r="K7" s="261"/>
       <c r="L7" s="56" t="s">
         <v>6</v>
       </c>
@@ -12775,122 +13514,122 @@
       <c r="BV7" s="39"/>
     </row>
     <row r="8" spans="1:74" ht="23.1" customHeight="1" thickBot="1">
-      <c r="B8" s="260" t="s">
+      <c r="B8" s="242" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="268" t="s">
+      <c r="C8" s="251" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="264" t="s">
+      <c r="D8" s="246" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="240" t="s">
+      <c r="E8" s="256" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="241"/>
-      <c r="G8" s="242"/>
-      <c r="H8" s="262" t="s">
+      <c r="F8" s="257"/>
+      <c r="G8" s="258"/>
+      <c r="H8" s="244" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="266" t="s">
+      <c r="I8" s="248" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="267" t="s">
+      <c r="J8" s="249" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="246" t="s">
+      <c r="K8" s="262" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="248" t="s">
+      <c r="L8" s="263" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="250" t="s">
+      <c r="M8" s="265" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="251"/>
-      <c r="O8" s="251"/>
-      <c r="P8" s="251"/>
-      <c r="Q8" s="252"/>
-      <c r="R8" s="253" t="s">
+      <c r="N8" s="240"/>
+      <c r="O8" s="240"/>
+      <c r="P8" s="240"/>
+      <c r="Q8" s="241"/>
+      <c r="R8" s="266" t="s">
         <v>17</v>
       </c>
-      <c r="S8" s="251"/>
-      <c r="T8" s="251"/>
-      <c r="U8" s="251"/>
-      <c r="V8" s="252"/>
-      <c r="W8" s="253" t="s">
+      <c r="S8" s="240"/>
+      <c r="T8" s="240"/>
+      <c r="U8" s="240"/>
+      <c r="V8" s="241"/>
+      <c r="W8" s="266" t="s">
         <v>18</v>
       </c>
-      <c r="X8" s="251"/>
-      <c r="Y8" s="251"/>
-      <c r="Z8" s="251"/>
-      <c r="AA8" s="252"/>
-      <c r="AB8" s="255" t="s">
+      <c r="X8" s="240"/>
+      <c r="Y8" s="240"/>
+      <c r="Z8" s="240"/>
+      <c r="AA8" s="241"/>
+      <c r="AB8" s="268" t="s">
         <v>19</v>
       </c>
-      <c r="AC8" s="251"/>
-      <c r="AD8" s="251"/>
-      <c r="AE8" s="251"/>
-      <c r="AF8" s="252"/>
-      <c r="AG8" s="256" t="s">
+      <c r="AC8" s="240"/>
+      <c r="AD8" s="240"/>
+      <c r="AE8" s="240"/>
+      <c r="AF8" s="241"/>
+      <c r="AG8" s="269" t="s">
         <v>20</v>
       </c>
-      <c r="AH8" s="251"/>
-      <c r="AI8" s="251"/>
-      <c r="AJ8" s="251"/>
-      <c r="AK8" s="252"/>
-      <c r="AL8" s="256" t="s">
+      <c r="AH8" s="240"/>
+      <c r="AI8" s="240"/>
+      <c r="AJ8" s="240"/>
+      <c r="AK8" s="241"/>
+      <c r="AL8" s="269" t="s">
         <v>21</v>
       </c>
-      <c r="AM8" s="251"/>
-      <c r="AN8" s="251"/>
-      <c r="AO8" s="251"/>
-      <c r="AP8" s="252"/>
-      <c r="AQ8" s="254" t="s">
+      <c r="AM8" s="240"/>
+      <c r="AN8" s="240"/>
+      <c r="AO8" s="240"/>
+      <c r="AP8" s="241"/>
+      <c r="AQ8" s="267" t="s">
         <v>22</v>
       </c>
-      <c r="AR8" s="251"/>
-      <c r="AS8" s="251"/>
-      <c r="AT8" s="251"/>
-      <c r="AU8" s="252"/>
-      <c r="AV8" s="257" t="s">
+      <c r="AR8" s="240"/>
+      <c r="AS8" s="240"/>
+      <c r="AT8" s="240"/>
+      <c r="AU8" s="241"/>
+      <c r="AV8" s="270" t="s">
         <v>23</v>
       </c>
-      <c r="AW8" s="251"/>
-      <c r="AX8" s="251"/>
-      <c r="AY8" s="251"/>
-      <c r="AZ8" s="252"/>
-      <c r="BA8" s="257" t="s">
+      <c r="AW8" s="240"/>
+      <c r="AX8" s="240"/>
+      <c r="AY8" s="240"/>
+      <c r="AZ8" s="241"/>
+      <c r="BA8" s="270" t="s">
         <v>24</v>
       </c>
-      <c r="BB8" s="251"/>
-      <c r="BC8" s="251"/>
-      <c r="BD8" s="251"/>
-      <c r="BE8" s="252"/>
-      <c r="BF8" s="258" t="s">
+      <c r="BB8" s="240"/>
+      <c r="BC8" s="240"/>
+      <c r="BD8" s="240"/>
+      <c r="BE8" s="241"/>
+      <c r="BF8" s="271" t="s">
         <v>25</v>
       </c>
-      <c r="BG8" s="251"/>
-      <c r="BH8" s="251"/>
-      <c r="BI8" s="251"/>
-      <c r="BJ8" s="252"/>
-      <c r="BK8" s="259"/>
-      <c r="BL8" s="251"/>
-      <c r="BM8" s="251"/>
-      <c r="BN8" s="251"/>
-      <c r="BO8" s="252"/>
-      <c r="BP8" s="259"/>
-      <c r="BQ8" s="251"/>
-      <c r="BR8" s="251"/>
-      <c r="BS8" s="251"/>
-      <c r="BT8" s="252"/>
+      <c r="BG8" s="240"/>
+      <c r="BH8" s="240"/>
+      <c r="BI8" s="240"/>
+      <c r="BJ8" s="241"/>
+      <c r="BK8" s="239"/>
+      <c r="BL8" s="240"/>
+      <c r="BM8" s="240"/>
+      <c r="BN8" s="240"/>
+      <c r="BO8" s="241"/>
+      <c r="BP8" s="239"/>
+      <c r="BQ8" s="240"/>
+      <c r="BR8" s="240"/>
+      <c r="BS8" s="240"/>
+      <c r="BT8" s="241"/>
       <c r="BU8" s="38"/>
       <c r="BV8" s="39"/>
     </row>
     <row r="9" spans="1:74" ht="23.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B9" s="261"/>
-      <c r="C9" s="269"/>
-      <c r="D9" s="265"/>
+      <c r="B9" s="243"/>
+      <c r="C9" s="252"/>
+      <c r="D9" s="247"/>
       <c r="E9" s="58" t="s">
         <v>28</v>
       </c>
@@ -12900,11 +13639,11 @@
       <c r="G9" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="263"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="247"/>
-      <c r="K9" s="247"/>
-      <c r="L9" s="249"/>
+      <c r="H9" s="245"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="250"/>
+      <c r="K9" s="250"/>
+      <c r="L9" s="264"/>
       <c r="M9" s="61" t="s">
         <v>31</v>
       </c>
@@ -16444,91 +17183,82 @@
     <row r="47" spans="2:74" ht="381.95" customHeight="1"/>
     <row r="48" spans="2:74" ht="216.95" customHeight="1"/>
     <row r="50" spans="2:74" ht="50.1" customHeight="1">
-      <c r="B50" s="237"/>
-      <c r="C50" s="238"/>
-      <c r="D50" s="238"/>
-      <c r="E50" s="238"/>
-      <c r="F50" s="238"/>
-      <c r="G50" s="238"/>
-      <c r="H50" s="238"/>
-      <c r="I50" s="238"/>
-      <c r="J50" s="238"/>
-      <c r="K50" s="238"/>
-      <c r="L50" s="238"/>
-      <c r="M50" s="238"/>
-      <c r="N50" s="238"/>
-      <c r="O50" s="238"/>
-      <c r="P50" s="238"/>
-      <c r="Q50" s="238"/>
-      <c r="R50" s="238"/>
-      <c r="S50" s="238"/>
-      <c r="T50" s="238"/>
-      <c r="U50" s="238"/>
-      <c r="V50" s="238"/>
-      <c r="W50" s="238"/>
-      <c r="X50" s="238"/>
-      <c r="Y50" s="238"/>
-      <c r="Z50" s="238"/>
-      <c r="AA50" s="238"/>
-      <c r="AB50" s="238"/>
-      <c r="AC50" s="238"/>
-      <c r="AD50" s="238"/>
-      <c r="AE50" s="238"/>
-      <c r="AF50" s="238"/>
-      <c r="AG50" s="238"/>
-      <c r="AH50" s="238"/>
-      <c r="AI50" s="238"/>
-      <c r="AJ50" s="238"/>
-      <c r="AK50" s="238"/>
-      <c r="AL50" s="238"/>
-      <c r="AM50" s="238"/>
-      <c r="AN50" s="238"/>
-      <c r="AO50" s="238"/>
-      <c r="AP50" s="238"/>
-      <c r="AQ50" s="238"/>
-      <c r="AR50" s="238"/>
-      <c r="AS50" s="238"/>
-      <c r="AT50" s="238"/>
-      <c r="AU50" s="238"/>
-      <c r="AV50" s="238"/>
-      <c r="AW50" s="238"/>
-      <c r="AX50" s="238"/>
-      <c r="AY50" s="238"/>
-      <c r="AZ50" s="238"/>
-      <c r="BA50" s="238"/>
-      <c r="BB50" s="238"/>
-      <c r="BC50" s="238"/>
-      <c r="BD50" s="238"/>
-      <c r="BE50" s="238"/>
-      <c r="BF50" s="238"/>
-      <c r="BG50" s="238"/>
-      <c r="BH50" s="238"/>
-      <c r="BI50" s="238"/>
-      <c r="BJ50" s="238"/>
-      <c r="BK50" s="238"/>
-      <c r="BL50" s="238"/>
-      <c r="BM50" s="238"/>
-      <c r="BN50" s="238"/>
-      <c r="BO50" s="238"/>
-      <c r="BP50" s="238"/>
-      <c r="BQ50" s="238"/>
-      <c r="BR50" s="238"/>
-      <c r="BS50" s="238"/>
-      <c r="BT50" s="238"/>
-      <c r="BU50" s="238"/>
-      <c r="BV50" s="239"/>
+      <c r="B50" s="253"/>
+      <c r="C50" s="254"/>
+      <c r="D50" s="254"/>
+      <c r="E50" s="254"/>
+      <c r="F50" s="254"/>
+      <c r="G50" s="254"/>
+      <c r="H50" s="254"/>
+      <c r="I50" s="254"/>
+      <c r="J50" s="254"/>
+      <c r="K50" s="254"/>
+      <c r="L50" s="254"/>
+      <c r="M50" s="254"/>
+      <c r="N50" s="254"/>
+      <c r="O50" s="254"/>
+      <c r="P50" s="254"/>
+      <c r="Q50" s="254"/>
+      <c r="R50" s="254"/>
+      <c r="S50" s="254"/>
+      <c r="T50" s="254"/>
+      <c r="U50" s="254"/>
+      <c r="V50" s="254"/>
+      <c r="W50" s="254"/>
+      <c r="X50" s="254"/>
+      <c r="Y50" s="254"/>
+      <c r="Z50" s="254"/>
+      <c r="AA50" s="254"/>
+      <c r="AB50" s="254"/>
+      <c r="AC50" s="254"/>
+      <c r="AD50" s="254"/>
+      <c r="AE50" s="254"/>
+      <c r="AF50" s="254"/>
+      <c r="AG50" s="254"/>
+      <c r="AH50" s="254"/>
+      <c r="AI50" s="254"/>
+      <c r="AJ50" s="254"/>
+      <c r="AK50" s="254"/>
+      <c r="AL50" s="254"/>
+      <c r="AM50" s="254"/>
+      <c r="AN50" s="254"/>
+      <c r="AO50" s="254"/>
+      <c r="AP50" s="254"/>
+      <c r="AQ50" s="254"/>
+      <c r="AR50" s="254"/>
+      <c r="AS50" s="254"/>
+      <c r="AT50" s="254"/>
+      <c r="AU50" s="254"/>
+      <c r="AV50" s="254"/>
+      <c r="AW50" s="254"/>
+      <c r="AX50" s="254"/>
+      <c r="AY50" s="254"/>
+      <c r="AZ50" s="254"/>
+      <c r="BA50" s="254"/>
+      <c r="BB50" s="254"/>
+      <c r="BC50" s="254"/>
+      <c r="BD50" s="254"/>
+      <c r="BE50" s="254"/>
+      <c r="BF50" s="254"/>
+      <c r="BG50" s="254"/>
+      <c r="BH50" s="254"/>
+      <c r="BI50" s="254"/>
+      <c r="BJ50" s="254"/>
+      <c r="BK50" s="254"/>
+      <c r="BL50" s="254"/>
+      <c r="BM50" s="254"/>
+      <c r="BN50" s="254"/>
+      <c r="BO50" s="254"/>
+      <c r="BP50" s="254"/>
+      <c r="BQ50" s="254"/>
+      <c r="BR50" s="254"/>
+      <c r="BS50" s="254"/>
+      <c r="BT50" s="254"/>
+      <c r="BU50" s="254"/>
+      <c r="BV50" s="255"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="K3:K7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
     <mergeCell ref="BP8:BT8"/>
     <mergeCell ref="B50:BV50"/>
     <mergeCell ref="AL8:AP8"/>
@@ -16543,6 +17273,15 @@
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="K3:K7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
   </mergeCells>
   <conditionalFormatting sqref="L10">
     <cfRule type="dataBar" priority="3">
@@ -16781,7 +17520,7 @@
       <c r="H3" s="40"/>
       <c r="I3" s="40"/>
       <c r="J3" s="41"/>
-      <c r="K3" s="243" t="s">
+      <c r="K3" s="259" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="42" t="s">
@@ -16860,7 +17599,7 @@
       <c r="H4" s="40"/>
       <c r="I4" s="40"/>
       <c r="J4" s="41"/>
-      <c r="K4" s="244"/>
+      <c r="K4" s="260"/>
       <c r="L4" s="47" t="s">
         <v>3</v>
       </c>
@@ -16937,7 +17676,7 @@
       <c r="H5" s="37"/>
       <c r="I5" s="36"/>
       <c r="J5" s="37"/>
-      <c r="K5" s="244"/>
+      <c r="K5" s="260"/>
       <c r="L5" s="52" t="s">
         <v>4</v>
       </c>
@@ -17014,7 +17753,7 @@
       <c r="H6" s="37"/>
       <c r="I6" s="36"/>
       <c r="J6" s="37"/>
-      <c r="K6" s="244"/>
+      <c r="K6" s="260"/>
       <c r="L6" s="54" t="s">
         <v>5</v>
       </c>
@@ -17091,7 +17830,7 @@
       <c r="H7" s="37"/>
       <c r="I7" s="36"/>
       <c r="J7" s="37"/>
-      <c r="K7" s="245"/>
+      <c r="K7" s="261"/>
       <c r="L7" s="56" t="s">
         <v>6</v>
       </c>
@@ -17159,122 +17898,122 @@
       <c r="BV7" s="39"/>
     </row>
     <row r="8" spans="1:74" ht="23.1" customHeight="1" thickBot="1">
-      <c r="B8" s="260" t="s">
+      <c r="B8" s="242" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="268" t="s">
+      <c r="C8" s="251" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="264" t="s">
+      <c r="D8" s="246" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="240" t="s">
+      <c r="E8" s="256" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="241"/>
-      <c r="G8" s="242"/>
-      <c r="H8" s="262" t="s">
+      <c r="F8" s="257"/>
+      <c r="G8" s="258"/>
+      <c r="H8" s="244" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="266" t="s">
+      <c r="I8" s="248" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="267" t="s">
+      <c r="J8" s="249" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="246" t="s">
+      <c r="K8" s="262" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="248" t="s">
+      <c r="L8" s="263" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="250" t="s">
+      <c r="M8" s="265" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="251"/>
-      <c r="O8" s="251"/>
-      <c r="P8" s="251"/>
-      <c r="Q8" s="252"/>
-      <c r="R8" s="253" t="s">
+      <c r="N8" s="240"/>
+      <c r="O8" s="240"/>
+      <c r="P8" s="240"/>
+      <c r="Q8" s="241"/>
+      <c r="R8" s="266" t="s">
         <v>17</v>
       </c>
-      <c r="S8" s="251"/>
-      <c r="T8" s="251"/>
-      <c r="U8" s="251"/>
-      <c r="V8" s="252"/>
-      <c r="W8" s="253" t="s">
+      <c r="S8" s="240"/>
+      <c r="T8" s="240"/>
+      <c r="U8" s="240"/>
+      <c r="V8" s="241"/>
+      <c r="W8" s="266" t="s">
         <v>18</v>
       </c>
-      <c r="X8" s="251"/>
-      <c r="Y8" s="251"/>
-      <c r="Z8" s="251"/>
-      <c r="AA8" s="252"/>
-      <c r="AB8" s="255" t="s">
+      <c r="X8" s="240"/>
+      <c r="Y8" s="240"/>
+      <c r="Z8" s="240"/>
+      <c r="AA8" s="241"/>
+      <c r="AB8" s="268" t="s">
         <v>19</v>
       </c>
-      <c r="AC8" s="251"/>
-      <c r="AD8" s="251"/>
-      <c r="AE8" s="251"/>
-      <c r="AF8" s="252"/>
-      <c r="AG8" s="256" t="s">
+      <c r="AC8" s="240"/>
+      <c r="AD8" s="240"/>
+      <c r="AE8" s="240"/>
+      <c r="AF8" s="241"/>
+      <c r="AG8" s="269" t="s">
         <v>20</v>
       </c>
-      <c r="AH8" s="251"/>
-      <c r="AI8" s="251"/>
-      <c r="AJ8" s="251"/>
-      <c r="AK8" s="252"/>
-      <c r="AL8" s="256" t="s">
+      <c r="AH8" s="240"/>
+      <c r="AI8" s="240"/>
+      <c r="AJ8" s="240"/>
+      <c r="AK8" s="241"/>
+      <c r="AL8" s="269" t="s">
         <v>21</v>
       </c>
-      <c r="AM8" s="251"/>
-      <c r="AN8" s="251"/>
-      <c r="AO8" s="251"/>
-      <c r="AP8" s="252"/>
-      <c r="AQ8" s="254" t="s">
+      <c r="AM8" s="240"/>
+      <c r="AN8" s="240"/>
+      <c r="AO8" s="240"/>
+      <c r="AP8" s="241"/>
+      <c r="AQ8" s="267" t="s">
         <v>22</v>
       </c>
-      <c r="AR8" s="251"/>
-      <c r="AS8" s="251"/>
-      <c r="AT8" s="251"/>
-      <c r="AU8" s="252"/>
-      <c r="AV8" s="257" t="s">
+      <c r="AR8" s="240"/>
+      <c r="AS8" s="240"/>
+      <c r="AT8" s="240"/>
+      <c r="AU8" s="241"/>
+      <c r="AV8" s="270" t="s">
         <v>23</v>
       </c>
-      <c r="AW8" s="251"/>
-      <c r="AX8" s="251"/>
-      <c r="AY8" s="251"/>
-      <c r="AZ8" s="252"/>
-      <c r="BA8" s="257" t="s">
+      <c r="AW8" s="240"/>
+      <c r="AX8" s="240"/>
+      <c r="AY8" s="240"/>
+      <c r="AZ8" s="241"/>
+      <c r="BA8" s="270" t="s">
         <v>24</v>
       </c>
-      <c r="BB8" s="251"/>
-      <c r="BC8" s="251"/>
-      <c r="BD8" s="251"/>
-      <c r="BE8" s="252"/>
-      <c r="BF8" s="258" t="s">
+      <c r="BB8" s="240"/>
+      <c r="BC8" s="240"/>
+      <c r="BD8" s="240"/>
+      <c r="BE8" s="241"/>
+      <c r="BF8" s="271" t="s">
         <v>25</v>
       </c>
-      <c r="BG8" s="251"/>
-      <c r="BH8" s="251"/>
-      <c r="BI8" s="251"/>
-      <c r="BJ8" s="252"/>
-      <c r="BK8" s="259"/>
-      <c r="BL8" s="251"/>
-      <c r="BM8" s="251"/>
-      <c r="BN8" s="251"/>
-      <c r="BO8" s="252"/>
-      <c r="BP8" s="259"/>
-      <c r="BQ8" s="251"/>
-      <c r="BR8" s="251"/>
-      <c r="BS8" s="251"/>
-      <c r="BT8" s="252"/>
+      <c r="BG8" s="240"/>
+      <c r="BH8" s="240"/>
+      <c r="BI8" s="240"/>
+      <c r="BJ8" s="241"/>
+      <c r="BK8" s="239"/>
+      <c r="BL8" s="240"/>
+      <c r="BM8" s="240"/>
+      <c r="BN8" s="240"/>
+      <c r="BO8" s="241"/>
+      <c r="BP8" s="239"/>
+      <c r="BQ8" s="240"/>
+      <c r="BR8" s="240"/>
+      <c r="BS8" s="240"/>
+      <c r="BT8" s="241"/>
       <c r="BU8" s="38"/>
       <c r="BV8" s="39"/>
     </row>
     <row r="9" spans="1:74" ht="23.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B9" s="261"/>
-      <c r="C9" s="269"/>
-      <c r="D9" s="265"/>
+      <c r="B9" s="243"/>
+      <c r="C9" s="252"/>
+      <c r="D9" s="247"/>
       <c r="E9" s="58" t="s">
         <v>28</v>
       </c>
@@ -17284,11 +18023,11 @@
       <c r="G9" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="263"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="247"/>
-      <c r="K9" s="247"/>
-      <c r="L9" s="249"/>
+      <c r="H9" s="245"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="250"/>
+      <c r="K9" s="250"/>
+      <c r="L9" s="264"/>
       <c r="M9" s="61" t="s">
         <v>31</v>
       </c>
@@ -20283,91 +21022,82 @@
     <row r="41" spans="2:74" ht="381.95" customHeight="1"/>
     <row r="42" spans="2:74" ht="216.95" customHeight="1"/>
     <row r="44" spans="2:74" ht="50.1" customHeight="1">
-      <c r="B44" s="237"/>
-      <c r="C44" s="238"/>
-      <c r="D44" s="238"/>
-      <c r="E44" s="238"/>
-      <c r="F44" s="238"/>
-      <c r="G44" s="238"/>
-      <c r="H44" s="238"/>
-      <c r="I44" s="238"/>
-      <c r="J44" s="238"/>
-      <c r="K44" s="238"/>
-      <c r="L44" s="238"/>
-      <c r="M44" s="238"/>
-      <c r="N44" s="238"/>
-      <c r="O44" s="238"/>
-      <c r="P44" s="238"/>
-      <c r="Q44" s="238"/>
-      <c r="R44" s="238"/>
-      <c r="S44" s="238"/>
-      <c r="T44" s="238"/>
-      <c r="U44" s="238"/>
-      <c r="V44" s="238"/>
-      <c r="W44" s="238"/>
-      <c r="X44" s="238"/>
-      <c r="Y44" s="238"/>
-      <c r="Z44" s="238"/>
-      <c r="AA44" s="238"/>
-      <c r="AB44" s="238"/>
-      <c r="AC44" s="238"/>
-      <c r="AD44" s="238"/>
-      <c r="AE44" s="238"/>
-      <c r="AF44" s="238"/>
-      <c r="AG44" s="238"/>
-      <c r="AH44" s="238"/>
-      <c r="AI44" s="238"/>
-      <c r="AJ44" s="238"/>
-      <c r="AK44" s="238"/>
-      <c r="AL44" s="238"/>
-      <c r="AM44" s="238"/>
-      <c r="AN44" s="238"/>
-      <c r="AO44" s="238"/>
-      <c r="AP44" s="238"/>
-      <c r="AQ44" s="238"/>
-      <c r="AR44" s="238"/>
-      <c r="AS44" s="238"/>
-      <c r="AT44" s="238"/>
-      <c r="AU44" s="238"/>
-      <c r="AV44" s="238"/>
-      <c r="AW44" s="238"/>
-      <c r="AX44" s="238"/>
-      <c r="AY44" s="238"/>
-      <c r="AZ44" s="238"/>
-      <c r="BA44" s="238"/>
-      <c r="BB44" s="238"/>
-      <c r="BC44" s="238"/>
-      <c r="BD44" s="238"/>
-      <c r="BE44" s="238"/>
-      <c r="BF44" s="238"/>
-      <c r="BG44" s="238"/>
-      <c r="BH44" s="238"/>
-      <c r="BI44" s="238"/>
-      <c r="BJ44" s="238"/>
-      <c r="BK44" s="238"/>
-      <c r="BL44" s="238"/>
-      <c r="BM44" s="238"/>
-      <c r="BN44" s="238"/>
-      <c r="BO44" s="238"/>
-      <c r="BP44" s="238"/>
-      <c r="BQ44" s="238"/>
-      <c r="BR44" s="238"/>
-      <c r="BS44" s="238"/>
-      <c r="BT44" s="238"/>
-      <c r="BU44" s="238"/>
-      <c r="BV44" s="239"/>
+      <c r="B44" s="253"/>
+      <c r="C44" s="254"/>
+      <c r="D44" s="254"/>
+      <c r="E44" s="254"/>
+      <c r="F44" s="254"/>
+      <c r="G44" s="254"/>
+      <c r="H44" s="254"/>
+      <c r="I44" s="254"/>
+      <c r="J44" s="254"/>
+      <c r="K44" s="254"/>
+      <c r="L44" s="254"/>
+      <c r="M44" s="254"/>
+      <c r="N44" s="254"/>
+      <c r="O44" s="254"/>
+      <c r="P44" s="254"/>
+      <c r="Q44" s="254"/>
+      <c r="R44" s="254"/>
+      <c r="S44" s="254"/>
+      <c r="T44" s="254"/>
+      <c r="U44" s="254"/>
+      <c r="V44" s="254"/>
+      <c r="W44" s="254"/>
+      <c r="X44" s="254"/>
+      <c r="Y44" s="254"/>
+      <c r="Z44" s="254"/>
+      <c r="AA44" s="254"/>
+      <c r="AB44" s="254"/>
+      <c r="AC44" s="254"/>
+      <c r="AD44" s="254"/>
+      <c r="AE44" s="254"/>
+      <c r="AF44" s="254"/>
+      <c r="AG44" s="254"/>
+      <c r="AH44" s="254"/>
+      <c r="AI44" s="254"/>
+      <c r="AJ44" s="254"/>
+      <c r="AK44" s="254"/>
+      <c r="AL44" s="254"/>
+      <c r="AM44" s="254"/>
+      <c r="AN44" s="254"/>
+      <c r="AO44" s="254"/>
+      <c r="AP44" s="254"/>
+      <c r="AQ44" s="254"/>
+      <c r="AR44" s="254"/>
+      <c r="AS44" s="254"/>
+      <c r="AT44" s="254"/>
+      <c r="AU44" s="254"/>
+      <c r="AV44" s="254"/>
+      <c r="AW44" s="254"/>
+      <c r="AX44" s="254"/>
+      <c r="AY44" s="254"/>
+      <c r="AZ44" s="254"/>
+      <c r="BA44" s="254"/>
+      <c r="BB44" s="254"/>
+      <c r="BC44" s="254"/>
+      <c r="BD44" s="254"/>
+      <c r="BE44" s="254"/>
+      <c r="BF44" s="254"/>
+      <c r="BG44" s="254"/>
+      <c r="BH44" s="254"/>
+      <c r="BI44" s="254"/>
+      <c r="BJ44" s="254"/>
+      <c r="BK44" s="254"/>
+      <c r="BL44" s="254"/>
+      <c r="BM44" s="254"/>
+      <c r="BN44" s="254"/>
+      <c r="BO44" s="254"/>
+      <c r="BP44" s="254"/>
+      <c r="BQ44" s="254"/>
+      <c r="BR44" s="254"/>
+      <c r="BS44" s="254"/>
+      <c r="BT44" s="254"/>
+      <c r="BU44" s="254"/>
+      <c r="BV44" s="255"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="K3:K7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
     <mergeCell ref="BP8:BT8"/>
     <mergeCell ref="B44:BV44"/>
     <mergeCell ref="AL8:AP8"/>
@@ -20382,6 +21112,15 @@
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="K3:K7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
   </mergeCells>
   <conditionalFormatting sqref="L10:L33">
     <cfRule type="dataBar" priority="3">
@@ -20611,7 +21350,7 @@
       <c r="H3" s="40"/>
       <c r="I3" s="40"/>
       <c r="J3" s="41"/>
-      <c r="K3" s="243" t="s">
+      <c r="K3" s="259" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="42" t="s">
@@ -20690,7 +21429,7 @@
       <c r="H4" s="40"/>
       <c r="I4" s="40"/>
       <c r="J4" s="41"/>
-      <c r="K4" s="244"/>
+      <c r="K4" s="260"/>
       <c r="L4" s="47" t="s">
         <v>3</v>
       </c>
@@ -20767,7 +21506,7 @@
       <c r="H5" s="37"/>
       <c r="I5" s="36"/>
       <c r="J5" s="37"/>
-      <c r="K5" s="244"/>
+      <c r="K5" s="260"/>
       <c r="L5" s="52" t="s">
         <v>4</v>
       </c>
@@ -20844,7 +21583,7 @@
       <c r="H6" s="37"/>
       <c r="I6" s="36"/>
       <c r="J6" s="37"/>
-      <c r="K6" s="244"/>
+      <c r="K6" s="260"/>
       <c r="L6" s="54" t="s">
         <v>5</v>
       </c>
@@ -20921,7 +21660,7 @@
       <c r="H7" s="37"/>
       <c r="I7" s="36"/>
       <c r="J7" s="37"/>
-      <c r="K7" s="245"/>
+      <c r="K7" s="261"/>
       <c r="L7" s="56" t="s">
         <v>6</v>
       </c>
@@ -20989,122 +21728,122 @@
       <c r="BV7" s="39"/>
     </row>
     <row r="8" spans="1:74" ht="23.1" customHeight="1" thickBot="1">
-      <c r="B8" s="260" t="s">
+      <c r="B8" s="242" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="268" t="s">
+      <c r="C8" s="251" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="264" t="s">
+      <c r="D8" s="246" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="240" t="s">
+      <c r="E8" s="256" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="241"/>
-      <c r="G8" s="242"/>
-      <c r="H8" s="262" t="s">
+      <c r="F8" s="257"/>
+      <c r="G8" s="258"/>
+      <c r="H8" s="244" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="266" t="s">
+      <c r="I8" s="248" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="267" t="s">
+      <c r="J8" s="249" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="246" t="s">
+      <c r="K8" s="262" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="248" t="s">
+      <c r="L8" s="263" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="250" t="s">
+      <c r="M8" s="265" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="251"/>
-      <c r="O8" s="251"/>
-      <c r="P8" s="251"/>
-      <c r="Q8" s="252"/>
-      <c r="R8" s="253" t="s">
+      <c r="N8" s="240"/>
+      <c r="O8" s="240"/>
+      <c r="P8" s="240"/>
+      <c r="Q8" s="241"/>
+      <c r="R8" s="266" t="s">
         <v>17</v>
       </c>
-      <c r="S8" s="251"/>
-      <c r="T8" s="251"/>
-      <c r="U8" s="251"/>
-      <c r="V8" s="252"/>
-      <c r="W8" s="253" t="s">
+      <c r="S8" s="240"/>
+      <c r="T8" s="240"/>
+      <c r="U8" s="240"/>
+      <c r="V8" s="241"/>
+      <c r="W8" s="266" t="s">
         <v>18</v>
       </c>
-      <c r="X8" s="251"/>
-      <c r="Y8" s="251"/>
-      <c r="Z8" s="251"/>
-      <c r="AA8" s="252"/>
-      <c r="AB8" s="255" t="s">
+      <c r="X8" s="240"/>
+      <c r="Y8" s="240"/>
+      <c r="Z8" s="240"/>
+      <c r="AA8" s="241"/>
+      <c r="AB8" s="268" t="s">
         <v>19</v>
       </c>
-      <c r="AC8" s="251"/>
-      <c r="AD8" s="251"/>
-      <c r="AE8" s="251"/>
-      <c r="AF8" s="252"/>
-      <c r="AG8" s="256" t="s">
+      <c r="AC8" s="240"/>
+      <c r="AD8" s="240"/>
+      <c r="AE8" s="240"/>
+      <c r="AF8" s="241"/>
+      <c r="AG8" s="269" t="s">
         <v>20</v>
       </c>
-      <c r="AH8" s="251"/>
-      <c r="AI8" s="251"/>
-      <c r="AJ8" s="251"/>
-      <c r="AK8" s="252"/>
-      <c r="AL8" s="256" t="s">
+      <c r="AH8" s="240"/>
+      <c r="AI8" s="240"/>
+      <c r="AJ8" s="240"/>
+      <c r="AK8" s="241"/>
+      <c r="AL8" s="269" t="s">
         <v>21</v>
       </c>
-      <c r="AM8" s="251"/>
-      <c r="AN8" s="251"/>
-      <c r="AO8" s="251"/>
-      <c r="AP8" s="252"/>
-      <c r="AQ8" s="254" t="s">
+      <c r="AM8" s="240"/>
+      <c r="AN8" s="240"/>
+      <c r="AO8" s="240"/>
+      <c r="AP8" s="241"/>
+      <c r="AQ8" s="267" t="s">
         <v>22</v>
       </c>
-      <c r="AR8" s="251"/>
-      <c r="AS8" s="251"/>
-      <c r="AT8" s="251"/>
-      <c r="AU8" s="252"/>
-      <c r="AV8" s="257" t="s">
+      <c r="AR8" s="240"/>
+      <c r="AS8" s="240"/>
+      <c r="AT8" s="240"/>
+      <c r="AU8" s="241"/>
+      <c r="AV8" s="270" t="s">
         <v>23</v>
       </c>
-      <c r="AW8" s="251"/>
-      <c r="AX8" s="251"/>
-      <c r="AY8" s="251"/>
-      <c r="AZ8" s="252"/>
-      <c r="BA8" s="257" t="s">
+      <c r="AW8" s="240"/>
+      <c r="AX8" s="240"/>
+      <c r="AY8" s="240"/>
+      <c r="AZ8" s="241"/>
+      <c r="BA8" s="270" t="s">
         <v>24</v>
       </c>
-      <c r="BB8" s="251"/>
-      <c r="BC8" s="251"/>
-      <c r="BD8" s="251"/>
-      <c r="BE8" s="252"/>
-      <c r="BF8" s="258" t="s">
+      <c r="BB8" s="240"/>
+      <c r="BC8" s="240"/>
+      <c r="BD8" s="240"/>
+      <c r="BE8" s="241"/>
+      <c r="BF8" s="271" t="s">
         <v>25</v>
       </c>
-      <c r="BG8" s="251"/>
-      <c r="BH8" s="251"/>
-      <c r="BI8" s="251"/>
-      <c r="BJ8" s="252"/>
-      <c r="BK8" s="259"/>
-      <c r="BL8" s="251"/>
-      <c r="BM8" s="251"/>
-      <c r="BN8" s="251"/>
-      <c r="BO8" s="252"/>
-      <c r="BP8" s="259"/>
-      <c r="BQ8" s="251"/>
-      <c r="BR8" s="251"/>
-      <c r="BS8" s="251"/>
-      <c r="BT8" s="252"/>
+      <c r="BG8" s="240"/>
+      <c r="BH8" s="240"/>
+      <c r="BI8" s="240"/>
+      <c r="BJ8" s="241"/>
+      <c r="BK8" s="239"/>
+      <c r="BL8" s="240"/>
+      <c r="BM8" s="240"/>
+      <c r="BN8" s="240"/>
+      <c r="BO8" s="241"/>
+      <c r="BP8" s="239"/>
+      <c r="BQ8" s="240"/>
+      <c r="BR8" s="240"/>
+      <c r="BS8" s="240"/>
+      <c r="BT8" s="241"/>
       <c r="BU8" s="38"/>
       <c r="BV8" s="39"/>
     </row>
     <row r="9" spans="1:74" ht="23.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B9" s="261"/>
-      <c r="C9" s="269"/>
-      <c r="D9" s="265"/>
+      <c r="B9" s="243"/>
+      <c r="C9" s="252"/>
+      <c r="D9" s="247"/>
       <c r="E9" s="58" t="s">
         <v>28</v>
       </c>
@@ -21114,11 +21853,11 @@
       <c r="G9" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="263"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="247"/>
-      <c r="K9" s="247"/>
-      <c r="L9" s="249"/>
+      <c r="H9" s="245"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="250"/>
+      <c r="K9" s="250"/>
+      <c r="L9" s="264"/>
       <c r="M9" s="61" t="s">
         <v>31</v>
       </c>
@@ -21296,11 +22035,11 @@
       </c>
       <c r="F10" s="198">
         <f>SUM(F11:F13)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G10" s="199">
         <f>SUM(G11:G13)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H10" s="205"/>
       <c r="I10" s="206">
@@ -21315,7 +22054,7 @@
       </c>
       <c r="L10" s="201">
         <f t="shared" ref="L10:L41" si="0">IFERROR(F10/E10,"")</f>
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="M10" s="73"/>
       <c r="N10" s="74"/>
@@ -21394,11 +22133,11 @@
         <v>4</v>
       </c>
       <c r="F11" s="154">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G11" s="155">
         <f>E11-F11</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H11" s="156"/>
       <c r="I11" s="211"/>
@@ -21406,7 +22145,7 @@
       <c r="K11" s="213"/>
       <c r="L11" s="201">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M11" s="77"/>
       <c r="N11" s="78"/>
@@ -21484,10 +22223,12 @@
       <c r="E12" s="153">
         <v>2</v>
       </c>
-      <c r="F12" s="154"/>
+      <c r="F12" s="154">
+        <v>2</v>
+      </c>
       <c r="G12" s="155">
         <f>E12-F12</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" s="163"/>
       <c r="I12" s="211"/>
@@ -21495,7 +22236,7 @@
       <c r="K12" s="213"/>
       <c r="L12" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="77"/>
       <c r="N12" s="78"/>
@@ -21573,10 +22314,12 @@
       <c r="E13" s="153">
         <v>2</v>
       </c>
-      <c r="F13" s="154"/>
+      <c r="F13" s="154">
+        <v>2</v>
+      </c>
       <c r="G13" s="155">
         <f>E13-F13</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" s="156"/>
       <c r="I13" s="211"/>
@@ -21584,7 +22327,7 @@
       <c r="K13" s="213"/>
       <c r="L13" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="77"/>
       <c r="N13" s="78"/>
@@ -21663,11 +22406,11 @@
       </c>
       <c r="F14" s="198">
         <f>SUM(F15:F17)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G14" s="199">
         <f>SUM(G15:G17)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H14" s="200"/>
       <c r="I14" s="206">
@@ -21682,7 +22425,7 @@
       </c>
       <c r="L14" s="201">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M14" s="73"/>
       <c r="N14" s="74"/>
@@ -21761,11 +22504,11 @@
         <v>2</v>
       </c>
       <c r="F15" s="154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="155">
         <f>E15-F15</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="156"/>
       <c r="I15" s="187"/>
@@ -21773,7 +22516,7 @@
       <c r="K15" s="213"/>
       <c r="L15" s="201">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M15" s="77"/>
       <c r="N15" s="78"/>
@@ -21851,10 +22594,12 @@
       <c r="E16" s="153">
         <v>1</v>
       </c>
-      <c r="F16" s="154"/>
+      <c r="F16" s="154">
+        <v>1</v>
+      </c>
       <c r="G16" s="155">
         <f>E16-F16</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="156"/>
       <c r="I16" s="187"/>
@@ -21862,7 +22607,7 @@
       <c r="K16" s="213"/>
       <c r="L16" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="77"/>
       <c r="N16" s="78"/>
@@ -21940,10 +22685,12 @@
       <c r="E17" s="153">
         <v>1</v>
       </c>
-      <c r="F17" s="154"/>
+      <c r="F17" s="154">
+        <v>1</v>
+      </c>
       <c r="G17" s="155">
         <f>E17-F17</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="156"/>
       <c r="I17" s="187"/>
@@ -21951,7 +22698,7 @@
       <c r="K17" s="213"/>
       <c r="L17" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="77"/>
       <c r="N17" s="78"/>
@@ -22030,11 +22777,11 @@
       </c>
       <c r="F18" s="198">
         <f>SUM(F19:F21)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G18" s="199">
         <f>SUM(G19:G21)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H18" s="200"/>
       <c r="I18" s="206">
@@ -22049,7 +22796,7 @@
       </c>
       <c r="L18" s="201">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M18" s="73"/>
       <c r="N18" s="74"/>
@@ -22128,11 +22875,11 @@
         <v>4</v>
       </c>
       <c r="F19" s="154">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19" s="155">
         <f>E19-F19</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" s="156"/>
       <c r="I19" s="157"/>
@@ -22140,7 +22887,7 @@
       <c r="K19" s="213"/>
       <c r="L19" s="201">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M19" s="77"/>
       <c r="N19" s="78"/>
@@ -22218,10 +22965,12 @@
       <c r="E20" s="153">
         <v>3</v>
       </c>
-      <c r="F20" s="154"/>
+      <c r="F20" s="154">
+        <v>3</v>
+      </c>
       <c r="G20" s="155">
         <f>E20-F20</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H20" s="156"/>
       <c r="I20" s="157"/>
@@ -22229,7 +22978,7 @@
       <c r="K20" s="213"/>
       <c r="L20" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="77"/>
       <c r="N20" s="78"/>
@@ -22307,10 +23056,12 @@
       <c r="E21" s="153">
         <v>1</v>
       </c>
-      <c r="F21" s="154"/>
+      <c r="F21" s="154">
+        <v>1</v>
+      </c>
       <c r="G21" s="155">
         <f>E21-F21</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="163"/>
       <c r="I21" s="157"/>
@@ -22318,7 +23069,7 @@
       <c r="K21" s="213"/>
       <c r="L21" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="77"/>
       <c r="N21" s="78"/>
@@ -22397,11 +23148,11 @@
       </c>
       <c r="F22" s="198">
         <f>SUM(F23:F25)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G22" s="199">
         <f>SUM(G23:G25)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H22" s="200"/>
       <c r="I22" s="206">
@@ -22416,7 +23167,7 @@
       </c>
       <c r="L22" s="201">
         <f t="shared" si="0"/>
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="M22" s="73"/>
       <c r="N22" s="74"/>
@@ -22495,11 +23246,11 @@
         <v>4</v>
       </c>
       <c r="F23" s="154">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G23" s="155">
         <f>E23-F23</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23" s="156"/>
       <c r="I23" s="157"/>
@@ -22507,7 +23258,7 @@
       <c r="K23" s="213"/>
       <c r="L23" s="201">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M23" s="77"/>
       <c r="N23" s="78"/>
@@ -22585,10 +23336,12 @@
       <c r="E24" s="153">
         <v>3</v>
       </c>
-      <c r="F24" s="154"/>
+      <c r="F24" s="154">
+        <v>3</v>
+      </c>
       <c r="G24" s="155">
         <f>E24-F24</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H24" s="156"/>
       <c r="I24" s="157"/>
@@ -22596,7 +23349,7 @@
       <c r="K24" s="213"/>
       <c r="L24" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="77"/>
       <c r="N24" s="78"/>
@@ -22674,10 +23427,12 @@
       <c r="E25" s="153">
         <v>1</v>
       </c>
-      <c r="F25" s="154"/>
+      <c r="F25" s="154">
+        <v>1</v>
+      </c>
       <c r="G25" s="155">
         <f>E25-F25</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="156"/>
       <c r="I25" s="157"/>
@@ -22685,7 +23440,7 @@
       <c r="K25" s="213"/>
       <c r="L25" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="77"/>
       <c r="N25" s="78"/>
@@ -22764,11 +23519,11 @@
       </c>
       <c r="F26" s="198">
         <f>SUM(F27:F29)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G26" s="199">
         <f>SUM(G27:G29)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H26" s="200"/>
       <c r="I26" s="206">
@@ -22783,7 +23538,7 @@
       </c>
       <c r="L26" s="201">
         <f t="shared" si="0"/>
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="M26" s="73"/>
       <c r="N26" s="74"/>
@@ -22862,11 +23617,11 @@
         <v>4</v>
       </c>
       <c r="F27" s="154">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G27" s="155">
         <f>E27-F27</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H27" s="212"/>
       <c r="I27" s="157"/>
@@ -22874,7 +23629,7 @@
       <c r="K27" s="213"/>
       <c r="L27" s="201">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M27" s="73"/>
       <c r="N27" s="74"/>
@@ -22952,10 +23707,12 @@
       <c r="E28" s="153">
         <v>3</v>
       </c>
-      <c r="F28" s="154"/>
+      <c r="F28" s="154">
+        <v>3</v>
+      </c>
       <c r="G28" s="155">
         <f>E28-F28</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H28" s="212"/>
       <c r="I28" s="157"/>
@@ -22963,7 +23720,7 @@
       <c r="K28" s="213"/>
       <c r="L28" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="73"/>
       <c r="N28" s="74"/>
@@ -23041,10 +23798,12 @@
       <c r="E29" s="153">
         <v>1</v>
       </c>
-      <c r="F29" s="154"/>
+      <c r="F29" s="154">
+        <v>1</v>
+      </c>
       <c r="G29" s="155">
         <f>E29-F29</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="212"/>
       <c r="I29" s="157"/>
@@ -23052,7 +23811,7 @@
       <c r="K29" s="213"/>
       <c r="L29" s="201">
         <f>IFERROR(F29/E29,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="73"/>
       <c r="N29" s="74"/>
@@ -23131,11 +23890,11 @@
       </c>
       <c r="F30" s="198">
         <f>SUM(F31:F33)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G30" s="199">
         <f>SUM(G31:G33)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H30" s="200"/>
       <c r="I30" s="206">
@@ -23150,7 +23909,7 @@
       </c>
       <c r="L30" s="201">
         <f>IFERROR(F30/E30,"")</f>
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="M30" s="73"/>
       <c r="N30" s="74"/>
@@ -23229,11 +23988,11 @@
         <v>4</v>
       </c>
       <c r="F31" s="154">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G31" s="155">
         <f>E31-F31</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H31" s="212"/>
       <c r="I31" s="235"/>
@@ -23241,7 +24000,7 @@
       <c r="K31" s="236"/>
       <c r="L31" s="201">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M31" s="73"/>
       <c r="N31" s="74"/>
@@ -23319,10 +24078,12 @@
       <c r="E32" s="153">
         <v>3</v>
       </c>
-      <c r="F32" s="154"/>
+      <c r="F32" s="154">
+        <v>3</v>
+      </c>
       <c r="G32" s="155">
         <f t="shared" ref="G32:G33" si="1">E32-F32</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H32" s="212"/>
       <c r="I32" s="235"/>
@@ -23330,7 +24091,7 @@
       <c r="K32" s="236"/>
       <c r="L32" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="73"/>
       <c r="N32" s="74"/>
@@ -23408,10 +24169,12 @@
       <c r="E33" s="153">
         <v>1</v>
       </c>
-      <c r="F33" s="154"/>
+      <c r="F33" s="154">
+        <v>1</v>
+      </c>
       <c r="G33" s="155">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="212"/>
       <c r="I33" s="235"/>
@@ -23419,7 +24182,7 @@
       <c r="K33" s="236"/>
       <c r="L33" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="73"/>
       <c r="N33" s="74"/>
@@ -23498,11 +24261,11 @@
       </c>
       <c r="F34" s="198">
         <f>SUM(F35:F37)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G34" s="199">
         <f>SUM(G35:G37)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H34" s="200"/>
       <c r="I34" s="206">
@@ -23517,7 +24280,7 @@
       </c>
       <c r="L34" s="201">
         <f>IFERROR(F34/E34,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="73"/>
       <c r="N34" s="74"/>
@@ -23595,10 +24358,12 @@
       <c r="E35" s="153">
         <v>2</v>
       </c>
-      <c r="F35" s="154"/>
+      <c r="F35" s="154">
+        <v>2</v>
+      </c>
       <c r="G35" s="155">
         <f>E35-F35</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35" s="212"/>
       <c r="I35" s="235"/>
@@ -23606,7 +24371,7 @@
       <c r="K35" s="236"/>
       <c r="L35" s="201">
         <f>IFERROR(F35/E35,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="73"/>
       <c r="N35" s="74"/>
@@ -23684,10 +24449,12 @@
       <c r="E36" s="153">
         <v>1</v>
       </c>
-      <c r="F36" s="154"/>
+      <c r="F36" s="154">
+        <v>1</v>
+      </c>
       <c r="G36" s="155">
         <f>E36-F36</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="212"/>
       <c r="I36" s="235"/>
@@ -23695,7 +24462,7 @@
       <c r="K36" s="236"/>
       <c r="L36" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="73"/>
       <c r="N36" s="74"/>
@@ -23773,10 +24540,12 @@
       <c r="E37" s="153">
         <v>1</v>
       </c>
-      <c r="F37" s="154"/>
+      <c r="F37" s="154">
+        <v>1</v>
+      </c>
       <c r="G37" s="155">
-        <f t="shared" ref="G36:G37" si="2">E37-F37</f>
-        <v>1</v>
+        <f t="shared" ref="G37" si="2">E37-F37</f>
+        <v>0</v>
       </c>
       <c r="H37" s="212"/>
       <c r="I37" s="235"/>
@@ -23784,7 +24553,7 @@
       <c r="K37" s="236"/>
       <c r="L37" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="73"/>
       <c r="N37" s="74"/>
@@ -23863,11 +24632,11 @@
       </c>
       <c r="F38" s="198">
         <f>SUM(F39:F41)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G38" s="199">
         <f>SUM(G39:G41)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H38" s="200"/>
       <c r="I38" s="206">
@@ -23882,7 +24651,7 @@
       </c>
       <c r="L38" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="73"/>
       <c r="N38" s="74"/>
@@ -23960,10 +24729,12 @@
       <c r="E39" s="153">
         <v>2</v>
       </c>
-      <c r="F39" s="154"/>
+      <c r="F39" s="154">
+        <v>2</v>
+      </c>
       <c r="G39" s="155">
         <f>E39-F39</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H39" s="212"/>
       <c r="I39" s="157"/>
@@ -23971,7 +24742,7 @@
       <c r="K39" s="213"/>
       <c r="L39" s="201">
         <f>IFERROR(F39/E39,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="73"/>
       <c r="N39" s="74"/>
@@ -24049,10 +24820,12 @@
       <c r="E40" s="153">
         <v>1</v>
       </c>
-      <c r="F40" s="154"/>
+      <c r="F40" s="154">
+        <v>1</v>
+      </c>
       <c r="G40" s="155">
         <f>E40-F40</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="212"/>
       <c r="I40" s="157"/>
@@ -24060,7 +24833,7 @@
       <c r="K40" s="213"/>
       <c r="L40" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="73"/>
       <c r="N40" s="74"/>
@@ -24138,10 +24911,12 @@
       <c r="E41" s="153">
         <v>1</v>
       </c>
-      <c r="F41" s="154"/>
+      <c r="F41" s="154">
+        <v>1</v>
+      </c>
       <c r="G41" s="155">
         <f>E41-F41</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="212"/>
       <c r="I41" s="157"/>
@@ -24149,7 +24924,7 @@
       <c r="K41" s="213"/>
       <c r="L41" s="201">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="73"/>
       <c r="N41" s="74"/>
@@ -24313,11 +25088,11 @@
       </c>
       <c r="F43" s="216">
         <f>SUM(F11:F13,F15:F17,F19:F21,F23:F25,F27:F29,F39:F41)</f>
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="G43" s="216">
         <f>SUM(G11:G13,G15:G17,G19:G21,G23:G25,G27:G29,G39:G41)</f>
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H43" s="217">
         <v>7</v>
@@ -24536,23 +25311,23 @@
       </c>
       <c r="O45" s="97">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P45" s="97">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="Q45" s="97">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="R45" s="97">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="S45" s="97">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="T45" s="97"/>
       <c r="U45" s="97"/>
@@ -24610,7 +25385,7 @@
       <c r="BU45" s="38"/>
       <c r="BV45" s="139">
         <f>SUM(M45:BT45)</f>
-        <v>244</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="2:74" ht="23.1" customHeight="1">
@@ -24633,22 +25408,22 @@
         <v>6</v>
       </c>
       <c r="N46" s="76">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O46" s="76">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P46" s="76">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q46" s="76">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R46" s="76">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S46" s="76">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T46" s="76"/>
       <c r="U46" s="76"/>
@@ -24706,7 +25481,7 @@
       <c r="BU46" s="38"/>
       <c r="BV46" s="140">
         <f>SUM(M46:BT46)</f>
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="2:74" ht="23.1" customHeight="1">
@@ -24729,27 +25504,27 @@
       </c>
       <c r="N47" s="97">
         <f t="shared" si="4"/>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O47" s="97">
         <f t="shared" si="4"/>
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="P47" s="97">
         <f t="shared" si="4"/>
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="Q47" s="97">
         <f t="shared" si="4"/>
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="R47" s="97">
         <f t="shared" si="4"/>
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="S47" s="97">
         <f t="shared" si="4"/>
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="T47" s="97"/>
       <c r="U47" s="97"/>
@@ -24807,7 +25582,7 @@
       <c r="BU47" s="38"/>
       <c r="BV47" s="140">
         <f>SUM(M47:BT47)</f>
-        <v>238</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="2:74" ht="19.5" customHeight="1">
@@ -24819,91 +25594,82 @@
     <row r="49" spans="2:74" ht="381.95" customHeight="1"/>
     <row r="50" spans="2:74" ht="216.95" customHeight="1"/>
     <row r="52" spans="2:74" ht="50.1" customHeight="1">
-      <c r="B52" s="237"/>
-      <c r="C52" s="238"/>
-      <c r="D52" s="238"/>
-      <c r="E52" s="238"/>
-      <c r="F52" s="238"/>
-      <c r="G52" s="238"/>
-      <c r="H52" s="238"/>
-      <c r="I52" s="238"/>
-      <c r="J52" s="238"/>
-      <c r="K52" s="238"/>
-      <c r="L52" s="238"/>
-      <c r="M52" s="238"/>
-      <c r="N52" s="238"/>
-      <c r="O52" s="238"/>
-      <c r="P52" s="238"/>
-      <c r="Q52" s="238"/>
-      <c r="R52" s="238"/>
-      <c r="S52" s="238"/>
-      <c r="T52" s="238"/>
-      <c r="U52" s="238"/>
-      <c r="V52" s="238"/>
-      <c r="W52" s="238"/>
-      <c r="X52" s="238"/>
-      <c r="Y52" s="238"/>
-      <c r="Z52" s="238"/>
-      <c r="AA52" s="238"/>
-      <c r="AB52" s="238"/>
-      <c r="AC52" s="238"/>
-      <c r="AD52" s="238"/>
-      <c r="AE52" s="238"/>
-      <c r="AF52" s="238"/>
-      <c r="AG52" s="238"/>
-      <c r="AH52" s="238"/>
-      <c r="AI52" s="238"/>
-      <c r="AJ52" s="238"/>
-      <c r="AK52" s="238"/>
-      <c r="AL52" s="238"/>
-      <c r="AM52" s="238"/>
-      <c r="AN52" s="238"/>
-      <c r="AO52" s="238"/>
-      <c r="AP52" s="238"/>
-      <c r="AQ52" s="238"/>
-      <c r="AR52" s="238"/>
-      <c r="AS52" s="238"/>
-      <c r="AT52" s="238"/>
-      <c r="AU52" s="238"/>
-      <c r="AV52" s="238"/>
-      <c r="AW52" s="238"/>
-      <c r="AX52" s="238"/>
-      <c r="AY52" s="238"/>
-      <c r="AZ52" s="238"/>
-      <c r="BA52" s="238"/>
-      <c r="BB52" s="238"/>
-      <c r="BC52" s="238"/>
-      <c r="BD52" s="238"/>
-      <c r="BE52" s="238"/>
-      <c r="BF52" s="238"/>
-      <c r="BG52" s="238"/>
-      <c r="BH52" s="238"/>
-      <c r="BI52" s="238"/>
-      <c r="BJ52" s="238"/>
-      <c r="BK52" s="238"/>
-      <c r="BL52" s="238"/>
-      <c r="BM52" s="238"/>
-      <c r="BN52" s="238"/>
-      <c r="BO52" s="238"/>
-      <c r="BP52" s="238"/>
-      <c r="BQ52" s="238"/>
-      <c r="BR52" s="238"/>
-      <c r="BS52" s="238"/>
-      <c r="BT52" s="238"/>
-      <c r="BU52" s="238"/>
-      <c r="BV52" s="239"/>
+      <c r="B52" s="253"/>
+      <c r="C52" s="254"/>
+      <c r="D52" s="254"/>
+      <c r="E52" s="254"/>
+      <c r="F52" s="254"/>
+      <c r="G52" s="254"/>
+      <c r="H52" s="254"/>
+      <c r="I52" s="254"/>
+      <c r="J52" s="254"/>
+      <c r="K52" s="254"/>
+      <c r="L52" s="254"/>
+      <c r="M52" s="254"/>
+      <c r="N52" s="254"/>
+      <c r="O52" s="254"/>
+      <c r="P52" s="254"/>
+      <c r="Q52" s="254"/>
+      <c r="R52" s="254"/>
+      <c r="S52" s="254"/>
+      <c r="T52" s="254"/>
+      <c r="U52" s="254"/>
+      <c r="V52" s="254"/>
+      <c r="W52" s="254"/>
+      <c r="X52" s="254"/>
+      <c r="Y52" s="254"/>
+      <c r="Z52" s="254"/>
+      <c r="AA52" s="254"/>
+      <c r="AB52" s="254"/>
+      <c r="AC52" s="254"/>
+      <c r="AD52" s="254"/>
+      <c r="AE52" s="254"/>
+      <c r="AF52" s="254"/>
+      <c r="AG52" s="254"/>
+      <c r="AH52" s="254"/>
+      <c r="AI52" s="254"/>
+      <c r="AJ52" s="254"/>
+      <c r="AK52" s="254"/>
+      <c r="AL52" s="254"/>
+      <c r="AM52" s="254"/>
+      <c r="AN52" s="254"/>
+      <c r="AO52" s="254"/>
+      <c r="AP52" s="254"/>
+      <c r="AQ52" s="254"/>
+      <c r="AR52" s="254"/>
+      <c r="AS52" s="254"/>
+      <c r="AT52" s="254"/>
+      <c r="AU52" s="254"/>
+      <c r="AV52" s="254"/>
+      <c r="AW52" s="254"/>
+      <c r="AX52" s="254"/>
+      <c r="AY52" s="254"/>
+      <c r="AZ52" s="254"/>
+      <c r="BA52" s="254"/>
+      <c r="BB52" s="254"/>
+      <c r="BC52" s="254"/>
+      <c r="BD52" s="254"/>
+      <c r="BE52" s="254"/>
+      <c r="BF52" s="254"/>
+      <c r="BG52" s="254"/>
+      <c r="BH52" s="254"/>
+      <c r="BI52" s="254"/>
+      <c r="BJ52" s="254"/>
+      <c r="BK52" s="254"/>
+      <c r="BL52" s="254"/>
+      <c r="BM52" s="254"/>
+      <c r="BN52" s="254"/>
+      <c r="BO52" s="254"/>
+      <c r="BP52" s="254"/>
+      <c r="BQ52" s="254"/>
+      <c r="BR52" s="254"/>
+      <c r="BS52" s="254"/>
+      <c r="BT52" s="254"/>
+      <c r="BU52" s="254"/>
+      <c r="BV52" s="255"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="K3:K7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
     <mergeCell ref="BP8:BT8"/>
     <mergeCell ref="B52:BV52"/>
     <mergeCell ref="AL8:AP8"/>
@@ -24918,6 +25684,15 @@
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="K3:K7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
   </mergeCells>
   <phoneticPr fontId="34" type="noConversion"/>
   <conditionalFormatting sqref="L10:L29 L31:L33 L35:L41">
@@ -25194,6 +25969,3155 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{340FD0BA-F8F2-42DB-A27A-B771AECCDFC2}">
+  <sheetPr>
+    <tabColor theme="3"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BV36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.125" defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="237" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="237" customWidth="1"/>
+    <col min="3" max="3" width="30.25" style="237" customWidth="1"/>
+    <col min="4" max="4" width="22" style="237" customWidth="1"/>
+    <col min="5" max="8" width="9" style="237" customWidth="1"/>
+    <col min="9" max="10" width="10.875" style="237" customWidth="1"/>
+    <col min="11" max="11" width="9.75" style="237" customWidth="1"/>
+    <col min="12" max="12" width="15" style="237" customWidth="1"/>
+    <col min="13" max="72" width="3.875" style="237" customWidth="1"/>
+    <col min="73" max="73" width="1" style="237" customWidth="1"/>
+    <col min="74" max="74" width="8.5" style="238" customWidth="1"/>
+    <col min="75" max="75" width="3.25" style="237" customWidth="1"/>
+    <col min="76" max="16384" width="11.125" style="237"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:74" ht="45" customHeight="1">
+      <c r="A1" s="31"/>
+      <c r="B1" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+    </row>
+    <row r="2" spans="1:74" s="238" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
+      <c r="B2" s="106"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="39"/>
+      <c r="W2" s="39"/>
+      <c r="X2" s="39"/>
+      <c r="Y2" s="39"/>
+      <c r="Z2" s="39"/>
+      <c r="AA2" s="39"/>
+      <c r="AB2" s="39"/>
+      <c r="AC2" s="39"/>
+      <c r="AD2" s="39"/>
+      <c r="AE2" s="39"/>
+      <c r="AF2" s="39"/>
+      <c r="AG2" s="39"/>
+      <c r="AH2" s="39"/>
+      <c r="AI2" s="39"/>
+      <c r="AJ2" s="39"/>
+      <c r="AK2" s="39"/>
+      <c r="AL2" s="39"/>
+      <c r="AM2" s="39"/>
+      <c r="AN2" s="39"/>
+      <c r="AO2" s="39"/>
+      <c r="AP2" s="39"/>
+      <c r="AQ2" s="39"/>
+      <c r="AR2" s="39"/>
+      <c r="AS2" s="39"/>
+      <c r="AT2" s="39"/>
+      <c r="AU2" s="39"/>
+      <c r="AV2" s="39"/>
+      <c r="AW2" s="39"/>
+      <c r="AX2" s="39"/>
+      <c r="AY2" s="39"/>
+      <c r="AZ2" s="39"/>
+      <c r="BA2" s="39"/>
+      <c r="BB2" s="39"/>
+      <c r="BC2" s="39"/>
+      <c r="BD2" s="39"/>
+      <c r="BE2" s="39"/>
+      <c r="BF2" s="39"/>
+      <c r="BG2" s="39"/>
+      <c r="BH2" s="39"/>
+      <c r="BI2" s="39"/>
+      <c r="BJ2" s="39"/>
+      <c r="BK2" s="39"/>
+      <c r="BL2" s="39"/>
+      <c r="BM2" s="39"/>
+      <c r="BN2" s="39"/>
+      <c r="BO2" s="39"/>
+      <c r="BP2" s="39"/>
+      <c r="BQ2" s="39"/>
+      <c r="BR2" s="39"/>
+      <c r="BS2" s="39"/>
+      <c r="BT2" s="39"/>
+      <c r="BU2" s="39"/>
+      <c r="BV2" s="39"/>
+    </row>
+    <row r="3" spans="1:74" ht="23.1" customHeight="1">
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="259" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="44"/>
+      <c r="U3" s="44"/>
+      <c r="V3" s="44"/>
+      <c r="W3" s="44"/>
+      <c r="X3" s="44"/>
+      <c r="Y3" s="44"/>
+      <c r="Z3" s="44"/>
+      <c r="AA3" s="44"/>
+      <c r="AB3" s="44"/>
+      <c r="AC3" s="44"/>
+      <c r="AD3" s="44"/>
+      <c r="AE3" s="44"/>
+      <c r="AF3" s="44"/>
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="45"/>
+      <c r="AI3" s="45"/>
+      <c r="AJ3" s="45"/>
+      <c r="AK3" s="45"/>
+      <c r="AL3" s="45"/>
+      <c r="AM3" s="45"/>
+      <c r="AN3" s="45"/>
+      <c r="AO3" s="45"/>
+      <c r="AP3" s="45"/>
+      <c r="AQ3" s="45"/>
+      <c r="AR3" s="45"/>
+      <c r="AS3" s="45"/>
+      <c r="AT3" s="45"/>
+      <c r="AU3" s="45"/>
+      <c r="AV3" s="45"/>
+      <c r="AW3" s="45"/>
+      <c r="AX3" s="45"/>
+      <c r="AY3" s="45"/>
+      <c r="AZ3" s="45"/>
+      <c r="BA3" s="45"/>
+      <c r="BB3" s="45"/>
+      <c r="BC3" s="45"/>
+      <c r="BD3" s="45"/>
+      <c r="BE3" s="45"/>
+      <c r="BF3" s="45"/>
+      <c r="BG3" s="45"/>
+      <c r="BH3" s="45"/>
+      <c r="BI3" s="45"/>
+      <c r="BJ3" s="45"/>
+      <c r="BK3" s="45"/>
+      <c r="BL3" s="45"/>
+      <c r="BM3" s="45"/>
+      <c r="BN3" s="45"/>
+      <c r="BO3" s="45"/>
+      <c r="BP3" s="45"/>
+      <c r="BQ3" s="45"/>
+      <c r="BR3" s="45"/>
+      <c r="BS3" s="45"/>
+      <c r="BT3" s="46"/>
+      <c r="BU3" s="38"/>
+      <c r="BV3" s="39"/>
+    </row>
+    <row r="4" spans="1:74" ht="23.1" customHeight="1">
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="47" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="49"/>
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49"/>
+      <c r="U4" s="49"/>
+      <c r="V4" s="50"/>
+      <c r="W4" s="50"/>
+      <c r="X4" s="50"/>
+      <c r="Y4" s="50"/>
+      <c r="Z4" s="50"/>
+      <c r="AA4" s="50"/>
+      <c r="AB4" s="50"/>
+      <c r="AC4" s="50"/>
+      <c r="AD4" s="50"/>
+      <c r="AE4" s="50"/>
+      <c r="AF4" s="50"/>
+      <c r="AG4" s="50"/>
+      <c r="AH4" s="50"/>
+      <c r="AI4" s="49"/>
+      <c r="AJ4" s="49"/>
+      <c r="AK4" s="49"/>
+      <c r="AL4" s="49"/>
+      <c r="AM4" s="49"/>
+      <c r="AN4" s="49"/>
+      <c r="AO4" s="49"/>
+      <c r="AP4" s="49"/>
+      <c r="AQ4" s="49"/>
+      <c r="AR4" s="49"/>
+      <c r="AS4" s="49"/>
+      <c r="AT4" s="49"/>
+      <c r="AU4" s="49"/>
+      <c r="AV4" s="49"/>
+      <c r="AW4" s="49"/>
+      <c r="AX4" s="49"/>
+      <c r="AY4" s="49"/>
+      <c r="AZ4" s="49"/>
+      <c r="BA4" s="49"/>
+      <c r="BB4" s="49"/>
+      <c r="BC4" s="49"/>
+      <c r="BD4" s="49"/>
+      <c r="BE4" s="49"/>
+      <c r="BF4" s="49"/>
+      <c r="BG4" s="49"/>
+      <c r="BH4" s="49"/>
+      <c r="BI4" s="49"/>
+      <c r="BJ4" s="49"/>
+      <c r="BK4" s="49"/>
+      <c r="BL4" s="49"/>
+      <c r="BM4" s="49"/>
+      <c r="BN4" s="49"/>
+      <c r="BO4" s="49"/>
+      <c r="BP4" s="49"/>
+      <c r="BQ4" s="49"/>
+      <c r="BR4" s="49"/>
+      <c r="BS4" s="49"/>
+      <c r="BT4" s="51"/>
+      <c r="BU4" s="38"/>
+      <c r="BV4" s="39"/>
+    </row>
+    <row r="5" spans="1:74" ht="23.1" customHeight="1">
+      <c r="B5" s="36"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
+      <c r="W5" s="49"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="49"/>
+      <c r="Z5" s="49"/>
+      <c r="AA5" s="53"/>
+      <c r="AB5" s="53"/>
+      <c r="AC5" s="53"/>
+      <c r="AD5" s="53"/>
+      <c r="AE5" s="53"/>
+      <c r="AF5" s="53"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="49"/>
+      <c r="AK5" s="49"/>
+      <c r="AL5" s="49"/>
+      <c r="AM5" s="49"/>
+      <c r="AN5" s="49"/>
+      <c r="AO5" s="49"/>
+      <c r="AP5" s="49"/>
+      <c r="AQ5" s="49"/>
+      <c r="AR5" s="49"/>
+      <c r="AS5" s="49"/>
+      <c r="AT5" s="49"/>
+      <c r="AU5" s="49"/>
+      <c r="AV5" s="49"/>
+      <c r="AW5" s="49"/>
+      <c r="AX5" s="49"/>
+      <c r="AY5" s="49"/>
+      <c r="AZ5" s="49"/>
+      <c r="BA5" s="49"/>
+      <c r="BB5" s="49"/>
+      <c r="BC5" s="49"/>
+      <c r="BD5" s="49"/>
+      <c r="BE5" s="49"/>
+      <c r="BF5" s="49"/>
+      <c r="BG5" s="49"/>
+      <c r="BH5" s="49"/>
+      <c r="BI5" s="49"/>
+      <c r="BJ5" s="49"/>
+      <c r="BK5" s="49"/>
+      <c r="BL5" s="49"/>
+      <c r="BM5" s="49"/>
+      <c r="BN5" s="49"/>
+      <c r="BO5" s="49"/>
+      <c r="BP5" s="49"/>
+      <c r="BQ5" s="49"/>
+      <c r="BR5" s="49"/>
+      <c r="BS5" s="49"/>
+      <c r="BT5" s="51"/>
+      <c r="BU5" s="38"/>
+      <c r="BV5" s="39"/>
+    </row>
+    <row r="6" spans="1:74" ht="23.1" customHeight="1">
+      <c r="B6" s="36"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="260"/>
+      <c r="L6" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49"/>
+      <c r="T6" s="49"/>
+      <c r="U6" s="49"/>
+      <c r="V6" s="49"/>
+      <c r="W6" s="49"/>
+      <c r="X6" s="49"/>
+      <c r="Y6" s="49"/>
+      <c r="Z6" s="49"/>
+      <c r="AA6" s="49"/>
+      <c r="AB6" s="49"/>
+      <c r="AC6" s="49"/>
+      <c r="AD6" s="49"/>
+      <c r="AE6" s="49"/>
+      <c r="AF6" s="55"/>
+      <c r="AG6" s="55"/>
+      <c r="AH6" s="55"/>
+      <c r="AI6" s="55"/>
+      <c r="AJ6" s="55"/>
+      <c r="AK6" s="55"/>
+      <c r="AL6" s="55"/>
+      <c r="AM6" s="55"/>
+      <c r="AN6" s="55"/>
+      <c r="AO6" s="55"/>
+      <c r="AP6" s="55"/>
+      <c r="AQ6" s="55"/>
+      <c r="AR6" s="55"/>
+      <c r="AS6" s="55"/>
+      <c r="AT6" s="55"/>
+      <c r="AU6" s="55"/>
+      <c r="AV6" s="55"/>
+      <c r="AW6" s="49"/>
+      <c r="AX6" s="49"/>
+      <c r="AY6" s="49"/>
+      <c r="AZ6" s="49"/>
+      <c r="BA6" s="49"/>
+      <c r="BB6" s="49"/>
+      <c r="BC6" s="49"/>
+      <c r="BD6" s="49"/>
+      <c r="BE6" s="49"/>
+      <c r="BF6" s="49"/>
+      <c r="BG6" s="49"/>
+      <c r="BH6" s="49"/>
+      <c r="BI6" s="49"/>
+      <c r="BJ6" s="49"/>
+      <c r="BK6" s="49"/>
+      <c r="BL6" s="49"/>
+      <c r="BM6" s="49"/>
+      <c r="BN6" s="49"/>
+      <c r="BO6" s="49"/>
+      <c r="BP6" s="49"/>
+      <c r="BQ6" s="49"/>
+      <c r="BR6" s="49"/>
+      <c r="BS6" s="49"/>
+      <c r="BT6" s="51"/>
+      <c r="BU6" s="38"/>
+      <c r="BV6" s="39"/>
+    </row>
+    <row r="7" spans="1:74" ht="23.1" customHeight="1" thickBot="1">
+      <c r="B7" s="36"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="261"/>
+      <c r="L7" s="56" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="49"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="49"/>
+      <c r="W7" s="49"/>
+      <c r="X7" s="49"/>
+      <c r="Y7" s="49"/>
+      <c r="Z7" s="49"/>
+      <c r="AA7" s="49"/>
+      <c r="AB7" s="49"/>
+      <c r="AC7" s="49"/>
+      <c r="AD7" s="49"/>
+      <c r="AE7" s="49"/>
+      <c r="AF7" s="49"/>
+      <c r="AG7" s="49"/>
+      <c r="AH7" s="49"/>
+      <c r="AI7" s="49"/>
+      <c r="AJ7" s="49"/>
+      <c r="AK7" s="49"/>
+      <c r="AL7" s="49"/>
+      <c r="AM7" s="49"/>
+      <c r="AN7" s="49"/>
+      <c r="AO7" s="49"/>
+      <c r="AP7" s="49"/>
+      <c r="AQ7" s="49"/>
+      <c r="AR7" s="49"/>
+      <c r="AS7" s="49"/>
+      <c r="AT7" s="49"/>
+      <c r="AU7" s="49"/>
+      <c r="AV7" s="49"/>
+      <c r="AW7" s="57"/>
+      <c r="AX7" s="57"/>
+      <c r="AY7" s="57"/>
+      <c r="AZ7" s="57"/>
+      <c r="BA7" s="57"/>
+      <c r="BB7" s="57"/>
+      <c r="BC7" s="57"/>
+      <c r="BD7" s="57"/>
+      <c r="BE7" s="57"/>
+      <c r="BF7" s="49"/>
+      <c r="BG7" s="49"/>
+      <c r="BH7" s="49"/>
+      <c r="BI7" s="49"/>
+      <c r="BJ7" s="49"/>
+      <c r="BK7" s="49"/>
+      <c r="BL7" s="49"/>
+      <c r="BM7" s="49"/>
+      <c r="BN7" s="49"/>
+      <c r="BO7" s="49"/>
+      <c r="BP7" s="49"/>
+      <c r="BQ7" s="49"/>
+      <c r="BR7" s="49"/>
+      <c r="BS7" s="49"/>
+      <c r="BT7" s="51"/>
+      <c r="BU7" s="38"/>
+      <c r="BV7" s="39"/>
+    </row>
+    <row r="8" spans="1:74" ht="23.1" customHeight="1" thickBot="1">
+      <c r="B8" s="242" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="251" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="246" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="256" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="257"/>
+      <c r="G8" s="258"/>
+      <c r="H8" s="244" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="248" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="249" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="262" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8" s="263" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" s="265" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" s="240"/>
+      <c r="O8" s="240"/>
+      <c r="P8" s="240"/>
+      <c r="Q8" s="241"/>
+      <c r="R8" s="266" t="s">
+        <v>17</v>
+      </c>
+      <c r="S8" s="240"/>
+      <c r="T8" s="240"/>
+      <c r="U8" s="240"/>
+      <c r="V8" s="241"/>
+      <c r="W8" s="266" t="s">
+        <v>18</v>
+      </c>
+      <c r="X8" s="240"/>
+      <c r="Y8" s="240"/>
+      <c r="Z8" s="240"/>
+      <c r="AA8" s="241"/>
+      <c r="AB8" s="268" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC8" s="240"/>
+      <c r="AD8" s="240"/>
+      <c r="AE8" s="240"/>
+      <c r="AF8" s="241"/>
+      <c r="AG8" s="269" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH8" s="240"/>
+      <c r="AI8" s="240"/>
+      <c r="AJ8" s="240"/>
+      <c r="AK8" s="241"/>
+      <c r="AL8" s="269" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM8" s="240"/>
+      <c r="AN8" s="240"/>
+      <c r="AO8" s="240"/>
+      <c r="AP8" s="241"/>
+      <c r="AQ8" s="267" t="s">
+        <v>22</v>
+      </c>
+      <c r="AR8" s="240"/>
+      <c r="AS8" s="240"/>
+      <c r="AT8" s="240"/>
+      <c r="AU8" s="241"/>
+      <c r="AV8" s="270" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW8" s="240"/>
+      <c r="AX8" s="240"/>
+      <c r="AY8" s="240"/>
+      <c r="AZ8" s="241"/>
+      <c r="BA8" s="270" t="s">
+        <v>24</v>
+      </c>
+      <c r="BB8" s="240"/>
+      <c r="BC8" s="240"/>
+      <c r="BD8" s="240"/>
+      <c r="BE8" s="241"/>
+      <c r="BF8" s="271" t="s">
+        <v>25</v>
+      </c>
+      <c r="BG8" s="240"/>
+      <c r="BH8" s="240"/>
+      <c r="BI8" s="240"/>
+      <c r="BJ8" s="241"/>
+      <c r="BK8" s="239"/>
+      <c r="BL8" s="240"/>
+      <c r="BM8" s="240"/>
+      <c r="BN8" s="240"/>
+      <c r="BO8" s="241"/>
+      <c r="BP8" s="239"/>
+      <c r="BQ8" s="240"/>
+      <c r="BR8" s="240"/>
+      <c r="BS8" s="240"/>
+      <c r="BT8" s="241"/>
+      <c r="BU8" s="38"/>
+      <c r="BV8" s="39"/>
+    </row>
+    <row r="9" spans="1:74" ht="23.1" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B9" s="243"/>
+      <c r="C9" s="252"/>
+      <c r="D9" s="247"/>
+      <c r="E9" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="59" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="245"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="250"/>
+      <c r="K9" s="250"/>
+      <c r="L9" s="264"/>
+      <c r="M9" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="N9" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="P9" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q9" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="R9" s="62" t="s">
+        <v>31</v>
+      </c>
+      <c r="S9" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="U9" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="V9" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="W9" s="62" t="s">
+        <v>31</v>
+      </c>
+      <c r="X9" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y9" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z9" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA9" s="63" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB9" s="64" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC9" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD9" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE9" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF9" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG9" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH9" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI9" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ9" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK9" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL9" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="AM9" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN9" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO9" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP9" s="66" t="s">
+        <v>35</v>
+      </c>
+      <c r="AQ9" s="67" t="s">
+        <v>31</v>
+      </c>
+      <c r="AR9" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS9" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT9" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="AU9" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="AV9" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW9" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="AX9" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="AY9" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="AZ9" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="BA9" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="BB9" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="BC9" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD9" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="BE9" s="69" t="s">
+        <v>35</v>
+      </c>
+      <c r="BF9" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="BG9" s="71" t="s">
+        <v>32</v>
+      </c>
+      <c r="BH9" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="BI9" s="71" t="s">
+        <v>34</v>
+      </c>
+      <c r="BJ9" s="71" t="s">
+        <v>35</v>
+      </c>
+      <c r="BK9" s="188"/>
+      <c r="BL9" s="188"/>
+      <c r="BM9" s="188"/>
+      <c r="BN9" s="188"/>
+      <c r="BO9" s="188"/>
+      <c r="BP9" s="188"/>
+      <c r="BQ9" s="188"/>
+      <c r="BR9" s="188"/>
+      <c r="BS9" s="188"/>
+      <c r="BT9" s="189"/>
+      <c r="BU9" s="38"/>
+      <c r="BV9" s="39"/>
+    </row>
+    <row r="10" spans="1:74" ht="23.1" customHeight="1" thickTop="1">
+      <c r="B10" s="202">
+        <v>1</v>
+      </c>
+      <c r="C10" s="203" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="204"/>
+      <c r="E10" s="197">
+        <f>SUM(E11:E13)</f>
+        <v>8</v>
+      </c>
+      <c r="F10" s="197">
+        <f>SUM(F11:F13)</f>
+        <v>8</v>
+      </c>
+      <c r="G10" s="199">
+        <f>SUM(G11:G13)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="205"/>
+      <c r="I10" s="206">
+        <v>45943</v>
+      </c>
+      <c r="J10" s="206">
+        <v>45947</v>
+      </c>
+      <c r="K10" s="207">
+        <f>J10-I10+1</f>
+        <v>5</v>
+      </c>
+      <c r="L10" s="201">
+        <f t="shared" ref="L10:L25" si="0">IFERROR(F10/E10,"")</f>
+        <v>1</v>
+      </c>
+      <c r="M10" s="73"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="74"/>
+      <c r="P10" s="74"/>
+      <c r="Q10" s="74"/>
+      <c r="R10" s="74"/>
+      <c r="S10" s="74"/>
+      <c r="T10" s="74"/>
+      <c r="U10" s="74"/>
+      <c r="V10" s="74"/>
+      <c r="W10" s="74"/>
+      <c r="X10" s="74"/>
+      <c r="Y10" s="74"/>
+      <c r="Z10" s="74"/>
+      <c r="AA10" s="75"/>
+      <c r="AB10" s="73"/>
+      <c r="AC10" s="74"/>
+      <c r="AD10" s="74"/>
+      <c r="AE10" s="74"/>
+      <c r="AF10" s="74"/>
+      <c r="AG10" s="74"/>
+      <c r="AH10" s="74"/>
+      <c r="AI10" s="74"/>
+      <c r="AJ10" s="74"/>
+      <c r="AK10" s="74"/>
+      <c r="AL10" s="74"/>
+      <c r="AM10" s="74"/>
+      <c r="AN10" s="74"/>
+      <c r="AO10" s="74"/>
+      <c r="AP10" s="75"/>
+      <c r="AQ10" s="73"/>
+      <c r="AR10" s="74"/>
+      <c r="AS10" s="74"/>
+      <c r="AT10" s="74"/>
+      <c r="AU10" s="74"/>
+      <c r="AV10" s="74"/>
+      <c r="AW10" s="74"/>
+      <c r="AX10" s="74"/>
+      <c r="AY10" s="74"/>
+      <c r="AZ10" s="74"/>
+      <c r="BA10" s="74"/>
+      <c r="BB10" s="74"/>
+      <c r="BC10" s="74"/>
+      <c r="BD10" s="74"/>
+      <c r="BE10" s="75"/>
+      <c r="BF10" s="73"/>
+      <c r="BG10" s="74"/>
+      <c r="BH10" s="74"/>
+      <c r="BI10" s="74"/>
+      <c r="BJ10" s="74"/>
+      <c r="BK10" s="78"/>
+      <c r="BL10" s="78"/>
+      <c r="BM10" s="78"/>
+      <c r="BN10" s="78"/>
+      <c r="BO10" s="78"/>
+      <c r="BP10" s="78"/>
+      <c r="BQ10" s="78"/>
+      <c r="BR10" s="78"/>
+      <c r="BS10" s="78"/>
+      <c r="BT10" s="81"/>
+      <c r="BU10" s="38"/>
+      <c r="BV10" s="39"/>
+    </row>
+    <row r="11" spans="1:74" ht="23.1" customHeight="1">
+      <c r="B11" s="150" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D11" s="152" t="s">
+        <v>119</v>
+      </c>
+      <c r="E11" s="153">
+        <v>4</v>
+      </c>
+      <c r="F11" s="154">
+        <v>4</v>
+      </c>
+      <c r="G11" s="155">
+        <f>E11-F11</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="156"/>
+      <c r="I11" s="211"/>
+      <c r="J11" s="211"/>
+      <c r="K11" s="213"/>
+      <c r="L11" s="201">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M11" s="77"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="78"/>
+      <c r="P11" s="78"/>
+      <c r="Q11" s="79"/>
+      <c r="R11" s="79"/>
+      <c r="S11" s="79"/>
+      <c r="T11" s="79"/>
+      <c r="U11" s="80"/>
+      <c r="V11" s="80"/>
+      <c r="W11" s="78"/>
+      <c r="X11" s="78"/>
+      <c r="Y11" s="78"/>
+      <c r="Z11" s="78"/>
+      <c r="AA11" s="81"/>
+      <c r="AB11" s="77"/>
+      <c r="AC11" s="78"/>
+      <c r="AD11" s="78"/>
+      <c r="AE11" s="78"/>
+      <c r="AF11" s="78"/>
+      <c r="AG11" s="82"/>
+      <c r="AH11" s="82"/>
+      <c r="AI11" s="82"/>
+      <c r="AJ11" s="82"/>
+      <c r="AK11" s="82"/>
+      <c r="AL11" s="78"/>
+      <c r="AM11" s="78"/>
+      <c r="AN11" s="78"/>
+      <c r="AO11" s="78"/>
+      <c r="AP11" s="81"/>
+      <c r="AQ11" s="77"/>
+      <c r="AR11" s="78"/>
+      <c r="AS11" s="78"/>
+      <c r="AT11" s="78"/>
+      <c r="AU11" s="78"/>
+      <c r="AV11" s="83"/>
+      <c r="AW11" s="83"/>
+      <c r="AX11" s="83"/>
+      <c r="AY11" s="83"/>
+      <c r="AZ11" s="83"/>
+      <c r="BA11" s="78"/>
+      <c r="BB11" s="78"/>
+      <c r="BC11" s="78"/>
+      <c r="BD11" s="78"/>
+      <c r="BE11" s="81"/>
+      <c r="BF11" s="77"/>
+      <c r="BG11" s="78"/>
+      <c r="BH11" s="78"/>
+      <c r="BI11" s="78"/>
+      <c r="BJ11" s="78"/>
+      <c r="BK11" s="78"/>
+      <c r="BL11" s="78"/>
+      <c r="BM11" s="78"/>
+      <c r="BN11" s="78"/>
+      <c r="BO11" s="78"/>
+      <c r="BP11" s="78"/>
+      <c r="BQ11" s="78"/>
+      <c r="BR11" s="78"/>
+      <c r="BS11" s="78"/>
+      <c r="BT11" s="81"/>
+      <c r="BU11" s="38"/>
+      <c r="BV11" s="39"/>
+    </row>
+    <row r="12" spans="1:74" ht="23.1" customHeight="1">
+      <c r="B12" s="150" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" s="152" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="153">
+        <v>3</v>
+      </c>
+      <c r="F12" s="154">
+        <v>3</v>
+      </c>
+      <c r="G12" s="155">
+        <f>E12-F12</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="163"/>
+      <c r="I12" s="211"/>
+      <c r="J12" s="211"/>
+      <c r="K12" s="213"/>
+      <c r="L12" s="201">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M12" s="77"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="78"/>
+      <c r="P12" s="78"/>
+      <c r="Q12" s="78"/>
+      <c r="R12" s="80"/>
+      <c r="S12" s="80"/>
+      <c r="T12" s="79"/>
+      <c r="U12" s="79"/>
+      <c r="V12" s="80"/>
+      <c r="W12" s="78"/>
+      <c r="X12" s="78"/>
+      <c r="Y12" s="78"/>
+      <c r="Z12" s="78"/>
+      <c r="AA12" s="81"/>
+      <c r="AB12" s="77"/>
+      <c r="AC12" s="78"/>
+      <c r="AD12" s="78"/>
+      <c r="AE12" s="78"/>
+      <c r="AF12" s="78"/>
+      <c r="AG12" s="82"/>
+      <c r="AH12" s="82"/>
+      <c r="AI12" s="82"/>
+      <c r="AJ12" s="82"/>
+      <c r="AK12" s="82"/>
+      <c r="AL12" s="78"/>
+      <c r="AM12" s="78"/>
+      <c r="AN12" s="78"/>
+      <c r="AO12" s="78"/>
+      <c r="AP12" s="81"/>
+      <c r="AQ12" s="77"/>
+      <c r="AR12" s="78"/>
+      <c r="AS12" s="78"/>
+      <c r="AT12" s="78"/>
+      <c r="AU12" s="78"/>
+      <c r="AV12" s="83"/>
+      <c r="AW12" s="83"/>
+      <c r="AX12" s="83"/>
+      <c r="AY12" s="83"/>
+      <c r="AZ12" s="83"/>
+      <c r="BA12" s="78"/>
+      <c r="BB12" s="78"/>
+      <c r="BC12" s="78"/>
+      <c r="BD12" s="78"/>
+      <c r="BE12" s="81"/>
+      <c r="BF12" s="77"/>
+      <c r="BG12" s="78"/>
+      <c r="BH12" s="78"/>
+      <c r="BI12" s="78"/>
+      <c r="BJ12" s="78"/>
+      <c r="BK12" s="78"/>
+      <c r="BL12" s="78"/>
+      <c r="BM12" s="78"/>
+      <c r="BN12" s="78"/>
+      <c r="BO12" s="78"/>
+      <c r="BP12" s="78"/>
+      <c r="BQ12" s="78"/>
+      <c r="BR12" s="78"/>
+      <c r="BS12" s="78"/>
+      <c r="BT12" s="81"/>
+      <c r="BU12" s="38"/>
+      <c r="BV12" s="39"/>
+    </row>
+    <row r="13" spans="1:74" ht="23.1" customHeight="1">
+      <c r="B13" s="150" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" t="s">
+        <v>239</v>
+      </c>
+      <c r="D13" s="152" t="s">
+        <v>119</v>
+      </c>
+      <c r="E13" s="153">
+        <v>1</v>
+      </c>
+      <c r="F13" s="154">
+        <v>1</v>
+      </c>
+      <c r="G13" s="155">
+        <f>E13-F13</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="156"/>
+      <c r="I13" s="211"/>
+      <c r="J13" s="211"/>
+      <c r="K13" s="213"/>
+      <c r="L13" s="201">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M13" s="77"/>
+      <c r="N13" s="78"/>
+      <c r="O13" s="78"/>
+      <c r="P13" s="78"/>
+      <c r="Q13" s="78"/>
+      <c r="R13" s="80"/>
+      <c r="S13" s="80"/>
+      <c r="T13" s="79"/>
+      <c r="U13" s="79"/>
+      <c r="V13" s="79"/>
+      <c r="W13" s="79"/>
+      <c r="X13" s="79"/>
+      <c r="Y13" s="79"/>
+      <c r="Z13" s="79"/>
+      <c r="AA13" s="81"/>
+      <c r="AB13" s="77"/>
+      <c r="AC13" s="78"/>
+      <c r="AD13" s="78"/>
+      <c r="AE13" s="78"/>
+      <c r="AF13" s="78"/>
+      <c r="AG13" s="82"/>
+      <c r="AH13" s="82"/>
+      <c r="AI13" s="82"/>
+      <c r="AJ13" s="82"/>
+      <c r="AK13" s="82"/>
+      <c r="AL13" s="78"/>
+      <c r="AM13" s="78"/>
+      <c r="AN13" s="78"/>
+      <c r="AO13" s="78"/>
+      <c r="AP13" s="81"/>
+      <c r="AQ13" s="77"/>
+      <c r="AR13" s="78"/>
+      <c r="AS13" s="78"/>
+      <c r="AT13" s="78"/>
+      <c r="AU13" s="78"/>
+      <c r="AV13" s="83"/>
+      <c r="AW13" s="83"/>
+      <c r="AX13" s="83"/>
+      <c r="AY13" s="83"/>
+      <c r="AZ13" s="83"/>
+      <c r="BA13" s="78"/>
+      <c r="BB13" s="78"/>
+      <c r="BC13" s="78"/>
+      <c r="BD13" s="78"/>
+      <c r="BE13" s="81"/>
+      <c r="BF13" s="77"/>
+      <c r="BG13" s="78"/>
+      <c r="BH13" s="78"/>
+      <c r="BI13" s="78"/>
+      <c r="BJ13" s="78"/>
+      <c r="BK13" s="78"/>
+      <c r="BL13" s="78"/>
+      <c r="BM13" s="78"/>
+      <c r="BN13" s="78"/>
+      <c r="BO13" s="78"/>
+      <c r="BP13" s="78"/>
+      <c r="BQ13" s="78"/>
+      <c r="BR13" s="78"/>
+      <c r="BS13" s="78"/>
+      <c r="BT13" s="81"/>
+      <c r="BU13" s="38"/>
+      <c r="BV13" s="39"/>
+    </row>
+    <row r="14" spans="1:74" ht="23.1" customHeight="1">
+      <c r="B14" s="194" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="203" t="s">
+        <v>228</v>
+      </c>
+      <c r="D14" s="196"/>
+      <c r="E14" s="197">
+        <f>SUM(E15:E17)</f>
+        <v>8</v>
+      </c>
+      <c r="F14" s="197">
+        <f>SUM(F15:F17)</f>
+        <v>8</v>
+      </c>
+      <c r="G14" s="199">
+        <f>SUM(G15:G17)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="200"/>
+      <c r="I14" s="206">
+        <v>45943</v>
+      </c>
+      <c r="J14" s="206">
+        <v>45947</v>
+      </c>
+      <c r="K14" s="207">
+        <f>J14-I14+1</f>
+        <v>5</v>
+      </c>
+      <c r="L14" s="201">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="74"/>
+      <c r="P14" s="74"/>
+      <c r="Q14" s="74"/>
+      <c r="R14" s="74"/>
+      <c r="S14" s="74"/>
+      <c r="T14" s="74"/>
+      <c r="U14" s="74"/>
+      <c r="V14" s="74"/>
+      <c r="W14" s="74"/>
+      <c r="X14" s="74"/>
+      <c r="Y14" s="74"/>
+      <c r="Z14" s="74"/>
+      <c r="AA14" s="75"/>
+      <c r="AB14" s="73"/>
+      <c r="AC14" s="74"/>
+      <c r="AD14" s="74"/>
+      <c r="AE14" s="74"/>
+      <c r="AF14" s="74"/>
+      <c r="AG14" s="74"/>
+      <c r="AH14" s="74"/>
+      <c r="AI14" s="74"/>
+      <c r="AJ14" s="74"/>
+      <c r="AK14" s="74"/>
+      <c r="AL14" s="74"/>
+      <c r="AM14" s="74"/>
+      <c r="AN14" s="74"/>
+      <c r="AO14" s="74"/>
+      <c r="AP14" s="75"/>
+      <c r="AQ14" s="73"/>
+      <c r="AR14" s="74"/>
+      <c r="AS14" s="74"/>
+      <c r="AT14" s="74"/>
+      <c r="AU14" s="74"/>
+      <c r="AV14" s="74"/>
+      <c r="AW14" s="74"/>
+      <c r="AX14" s="74"/>
+      <c r="AY14" s="74"/>
+      <c r="AZ14" s="74"/>
+      <c r="BA14" s="74"/>
+      <c r="BB14" s="74"/>
+      <c r="BC14" s="74"/>
+      <c r="BD14" s="74"/>
+      <c r="BE14" s="75"/>
+      <c r="BF14" s="73"/>
+      <c r="BG14" s="74"/>
+      <c r="BH14" s="74"/>
+      <c r="BI14" s="74"/>
+      <c r="BJ14" s="74"/>
+      <c r="BK14" s="78"/>
+      <c r="BL14" s="78"/>
+      <c r="BM14" s="78"/>
+      <c r="BN14" s="78"/>
+      <c r="BO14" s="78"/>
+      <c r="BP14" s="78"/>
+      <c r="BQ14" s="78"/>
+      <c r="BR14" s="78"/>
+      <c r="BS14" s="78"/>
+      <c r="BT14" s="81"/>
+      <c r="BU14" s="38"/>
+      <c r="BV14" s="39"/>
+    </row>
+    <row r="15" spans="1:74" ht="23.1" customHeight="1">
+      <c r="B15" s="150">
+        <v>2.1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>233</v>
+      </c>
+      <c r="D15" s="152" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="153">
+        <v>4</v>
+      </c>
+      <c r="F15" s="154">
+        <v>4</v>
+      </c>
+      <c r="G15" s="155">
+        <f>E15-F15</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="156"/>
+      <c r="I15" s="187"/>
+      <c r="J15" s="187"/>
+      <c r="K15" s="213"/>
+      <c r="L15" s="201">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M15" s="77"/>
+      <c r="N15" s="78"/>
+      <c r="O15" s="78"/>
+      <c r="P15" s="78"/>
+      <c r="Q15" s="78"/>
+      <c r="R15" s="80"/>
+      <c r="S15" s="80"/>
+      <c r="T15" s="80"/>
+      <c r="U15" s="80"/>
+      <c r="V15" s="80"/>
+      <c r="W15" s="78"/>
+      <c r="X15" s="78"/>
+      <c r="Y15" s="78"/>
+      <c r="Z15" s="78"/>
+      <c r="AA15" s="81"/>
+      <c r="AB15" s="84"/>
+      <c r="AC15" s="85"/>
+      <c r="AD15" s="85"/>
+      <c r="AE15" s="85"/>
+      <c r="AF15" s="85"/>
+      <c r="AG15" s="82"/>
+      <c r="AH15" s="82"/>
+      <c r="AI15" s="82"/>
+      <c r="AJ15" s="82"/>
+      <c r="AK15" s="82"/>
+      <c r="AL15" s="78"/>
+      <c r="AM15" s="78"/>
+      <c r="AN15" s="78"/>
+      <c r="AO15" s="78"/>
+      <c r="AP15" s="81"/>
+      <c r="AQ15" s="77"/>
+      <c r="AR15" s="78"/>
+      <c r="AS15" s="78"/>
+      <c r="AT15" s="78"/>
+      <c r="AU15" s="78"/>
+      <c r="AV15" s="83"/>
+      <c r="AW15" s="83"/>
+      <c r="AX15" s="83"/>
+      <c r="AY15" s="83"/>
+      <c r="AZ15" s="83"/>
+      <c r="BA15" s="78"/>
+      <c r="BB15" s="78"/>
+      <c r="BC15" s="78"/>
+      <c r="BD15" s="78"/>
+      <c r="BE15" s="81"/>
+      <c r="BF15" s="77"/>
+      <c r="BG15" s="78"/>
+      <c r="BH15" s="78"/>
+      <c r="BI15" s="78"/>
+      <c r="BJ15" s="78"/>
+      <c r="BK15" s="78"/>
+      <c r="BL15" s="78"/>
+      <c r="BM15" s="78"/>
+      <c r="BN15" s="78"/>
+      <c r="BO15" s="78"/>
+      <c r="BP15" s="78"/>
+      <c r="BQ15" s="78"/>
+      <c r="BR15" s="78"/>
+      <c r="BS15" s="78"/>
+      <c r="BT15" s="81"/>
+      <c r="BU15" s="38"/>
+      <c r="BV15" s="39"/>
+    </row>
+    <row r="16" spans="1:74" ht="23.1" customHeight="1">
+      <c r="B16" s="150">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C16" t="s">
+        <v>234</v>
+      </c>
+      <c r="D16" s="152" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" s="153">
+        <v>3</v>
+      </c>
+      <c r="F16" s="154">
+        <v>3</v>
+      </c>
+      <c r="G16" s="155">
+        <f>E16-F16</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="156"/>
+      <c r="I16" s="187"/>
+      <c r="J16" s="187"/>
+      <c r="K16" s="213"/>
+      <c r="L16" s="201">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M16" s="77"/>
+      <c r="N16" s="78"/>
+      <c r="O16" s="78"/>
+      <c r="P16" s="78"/>
+      <c r="Q16" s="78"/>
+      <c r="R16" s="80"/>
+      <c r="S16" s="80"/>
+      <c r="T16" s="80"/>
+      <c r="U16" s="80"/>
+      <c r="V16" s="80"/>
+      <c r="W16" s="78"/>
+      <c r="X16" s="78"/>
+      <c r="Y16" s="78"/>
+      <c r="Z16" s="78"/>
+      <c r="AA16" s="81"/>
+      <c r="AB16" s="77"/>
+      <c r="AC16" s="78"/>
+      <c r="AD16" s="78"/>
+      <c r="AE16" s="78"/>
+      <c r="AF16" s="78"/>
+      <c r="AG16" s="85"/>
+      <c r="AH16" s="85"/>
+      <c r="AI16" s="85"/>
+      <c r="AJ16" s="85"/>
+      <c r="AK16" s="85"/>
+      <c r="AL16" s="78"/>
+      <c r="AM16" s="78"/>
+      <c r="AN16" s="78"/>
+      <c r="AO16" s="78"/>
+      <c r="AP16" s="81"/>
+      <c r="AQ16" s="77"/>
+      <c r="AR16" s="78"/>
+      <c r="AS16" s="78"/>
+      <c r="AT16" s="78"/>
+      <c r="AU16" s="78"/>
+      <c r="AV16" s="83"/>
+      <c r="AW16" s="83"/>
+      <c r="AX16" s="83"/>
+      <c r="AY16" s="83"/>
+      <c r="AZ16" s="83"/>
+      <c r="BA16" s="78"/>
+      <c r="BB16" s="78"/>
+      <c r="BC16" s="78"/>
+      <c r="BD16" s="78"/>
+      <c r="BE16" s="81"/>
+      <c r="BF16" s="77"/>
+      <c r="BG16" s="78"/>
+      <c r="BH16" s="78"/>
+      <c r="BI16" s="78"/>
+      <c r="BJ16" s="78"/>
+      <c r="BK16" s="78"/>
+      <c r="BL16" s="78"/>
+      <c r="BM16" s="78"/>
+      <c r="BN16" s="78"/>
+      <c r="BO16" s="78"/>
+      <c r="BP16" s="78"/>
+      <c r="BQ16" s="78"/>
+      <c r="BR16" s="78"/>
+      <c r="BS16" s="78"/>
+      <c r="BT16" s="81"/>
+      <c r="BU16" s="38"/>
+      <c r="BV16" s="39"/>
+    </row>
+    <row r="17" spans="2:74" ht="23.1" customHeight="1">
+      <c r="B17" s="150">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C17" t="s">
+        <v>240</v>
+      </c>
+      <c r="D17" s="152" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="153">
+        <v>1</v>
+      </c>
+      <c r="F17" s="154">
+        <v>1</v>
+      </c>
+      <c r="G17" s="155">
+        <f>E17-F17</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="156"/>
+      <c r="I17" s="187"/>
+      <c r="J17" s="187"/>
+      <c r="K17" s="213"/>
+      <c r="L17" s="201">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M17" s="77"/>
+      <c r="N17" s="78"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="78"/>
+      <c r="Q17" s="78"/>
+      <c r="R17" s="80"/>
+      <c r="S17" s="80"/>
+      <c r="T17" s="80"/>
+      <c r="U17" s="80"/>
+      <c r="V17" s="80"/>
+      <c r="W17" s="78"/>
+      <c r="X17" s="78"/>
+      <c r="Y17" s="78"/>
+      <c r="Z17" s="78"/>
+      <c r="AA17" s="81"/>
+      <c r="AB17" s="77"/>
+      <c r="AC17" s="78"/>
+      <c r="AD17" s="78"/>
+      <c r="AE17" s="78"/>
+      <c r="AF17" s="78"/>
+      <c r="AG17" s="82"/>
+      <c r="AH17" s="82"/>
+      <c r="AI17" s="82"/>
+      <c r="AJ17" s="82"/>
+      <c r="AK17" s="82"/>
+      <c r="AL17" s="78"/>
+      <c r="AM17" s="78"/>
+      <c r="AN17" s="78"/>
+      <c r="AO17" s="78"/>
+      <c r="AP17" s="81"/>
+      <c r="AQ17" s="77"/>
+      <c r="AR17" s="78"/>
+      <c r="AS17" s="78"/>
+      <c r="AT17" s="78"/>
+      <c r="AU17" s="78"/>
+      <c r="AV17" s="83"/>
+      <c r="AW17" s="83"/>
+      <c r="AX17" s="83"/>
+      <c r="AY17" s="83"/>
+      <c r="AZ17" s="83"/>
+      <c r="BA17" s="78"/>
+      <c r="BB17" s="78"/>
+      <c r="BC17" s="78"/>
+      <c r="BD17" s="78"/>
+      <c r="BE17" s="81"/>
+      <c r="BF17" s="77"/>
+      <c r="BG17" s="78"/>
+      <c r="BH17" s="78"/>
+      <c r="BI17" s="78"/>
+      <c r="BJ17" s="78"/>
+      <c r="BK17" s="78"/>
+      <c r="BL17" s="78"/>
+      <c r="BM17" s="78"/>
+      <c r="BN17" s="78"/>
+      <c r="BO17" s="78"/>
+      <c r="BP17" s="78"/>
+      <c r="BQ17" s="78"/>
+      <c r="BR17" s="78"/>
+      <c r="BS17" s="78"/>
+      <c r="BT17" s="81"/>
+      <c r="BU17" s="38"/>
+      <c r="BV17" s="39"/>
+    </row>
+    <row r="18" spans="2:74" ht="23.1" customHeight="1">
+      <c r="B18" s="194">
+        <v>3</v>
+      </c>
+      <c r="C18" s="203" t="s">
+        <v>229</v>
+      </c>
+      <c r="D18" s="196"/>
+      <c r="E18" s="197">
+        <f>SUM(E19:E21)</f>
+        <v>8</v>
+      </c>
+      <c r="F18" s="197">
+        <f>SUM(F19:F21)</f>
+        <v>8</v>
+      </c>
+      <c r="G18" s="199">
+        <f>SUM(G19:G21)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="200"/>
+      <c r="I18" s="206">
+        <v>45943</v>
+      </c>
+      <c r="J18" s="206">
+        <v>45947</v>
+      </c>
+      <c r="K18" s="207">
+        <f>J18-I18+1</f>
+        <v>5</v>
+      </c>
+      <c r="L18" s="201">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="74"/>
+      <c r="P18" s="74"/>
+      <c r="Q18" s="74"/>
+      <c r="R18" s="74"/>
+      <c r="S18" s="74"/>
+      <c r="T18" s="74"/>
+      <c r="U18" s="74"/>
+      <c r="V18" s="74"/>
+      <c r="W18" s="74"/>
+      <c r="X18" s="74"/>
+      <c r="Y18" s="74"/>
+      <c r="Z18" s="74"/>
+      <c r="AA18" s="75"/>
+      <c r="AB18" s="73"/>
+      <c r="AC18" s="74"/>
+      <c r="AD18" s="74"/>
+      <c r="AE18" s="74"/>
+      <c r="AF18" s="74"/>
+      <c r="AG18" s="74"/>
+      <c r="AH18" s="74"/>
+      <c r="AI18" s="74"/>
+      <c r="AJ18" s="74"/>
+      <c r="AK18" s="74"/>
+      <c r="AL18" s="74"/>
+      <c r="AM18" s="74"/>
+      <c r="AN18" s="74"/>
+      <c r="AO18" s="74"/>
+      <c r="AP18" s="75"/>
+      <c r="AQ18" s="73"/>
+      <c r="AR18" s="74"/>
+      <c r="AS18" s="74"/>
+      <c r="AT18" s="74"/>
+      <c r="AU18" s="74"/>
+      <c r="AV18" s="74"/>
+      <c r="AW18" s="74"/>
+      <c r="AX18" s="74"/>
+      <c r="AY18" s="74"/>
+      <c r="AZ18" s="74"/>
+      <c r="BA18" s="74"/>
+      <c r="BB18" s="74"/>
+      <c r="BC18" s="74"/>
+      <c r="BD18" s="74"/>
+      <c r="BE18" s="75"/>
+      <c r="BF18" s="73"/>
+      <c r="BG18" s="74"/>
+      <c r="BH18" s="74"/>
+      <c r="BI18" s="74"/>
+      <c r="BJ18" s="74"/>
+      <c r="BK18" s="78"/>
+      <c r="BL18" s="78"/>
+      <c r="BM18" s="78"/>
+      <c r="BN18" s="78"/>
+      <c r="BO18" s="78"/>
+      <c r="BP18" s="78"/>
+      <c r="BQ18" s="78"/>
+      <c r="BR18" s="78"/>
+      <c r="BS18" s="78"/>
+      <c r="BT18" s="81"/>
+      <c r="BU18" s="38"/>
+      <c r="BV18" s="39"/>
+    </row>
+    <row r="19" spans="2:74" ht="23.1" customHeight="1">
+      <c r="B19" s="150">
+        <v>3.1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>235</v>
+      </c>
+      <c r="D19" s="152" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="153">
+        <v>4</v>
+      </c>
+      <c r="F19" s="154">
+        <v>4</v>
+      </c>
+      <c r="G19" s="155">
+        <f>E19-F19</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="156"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="158"/>
+      <c r="K19" s="213"/>
+      <c r="L19" s="201">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M19" s="77"/>
+      <c r="N19" s="78"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="78"/>
+      <c r="Q19" s="78"/>
+      <c r="R19" s="80"/>
+      <c r="S19" s="80"/>
+      <c r="T19" s="80"/>
+      <c r="U19" s="80"/>
+      <c r="V19" s="80"/>
+      <c r="W19" s="78"/>
+      <c r="X19" s="78"/>
+      <c r="Y19" s="78"/>
+      <c r="Z19" s="78"/>
+      <c r="AA19" s="81"/>
+      <c r="AB19" s="77"/>
+      <c r="AC19" s="78"/>
+      <c r="AD19" s="78"/>
+      <c r="AE19" s="78"/>
+      <c r="AF19" s="78"/>
+      <c r="AG19" s="82"/>
+      <c r="AH19" s="82"/>
+      <c r="AI19" s="82"/>
+      <c r="AJ19" s="82"/>
+      <c r="AK19" s="82"/>
+      <c r="AL19" s="78"/>
+      <c r="AM19" s="78"/>
+      <c r="AN19" s="78"/>
+      <c r="AO19" s="78"/>
+      <c r="AP19" s="81"/>
+      <c r="AQ19" s="77"/>
+      <c r="AR19" s="78"/>
+      <c r="AS19" s="78"/>
+      <c r="AT19" s="78"/>
+      <c r="AU19" s="78"/>
+      <c r="AV19" s="83"/>
+      <c r="AW19" s="83"/>
+      <c r="AX19" s="83"/>
+      <c r="AY19" s="83"/>
+      <c r="AZ19" s="83"/>
+      <c r="BA19" s="78"/>
+      <c r="BB19" s="78"/>
+      <c r="BC19" s="78"/>
+      <c r="BD19" s="78"/>
+      <c r="BE19" s="81"/>
+      <c r="BF19" s="77"/>
+      <c r="BG19" s="78"/>
+      <c r="BH19" s="78"/>
+      <c r="BI19" s="78"/>
+      <c r="BJ19" s="78"/>
+      <c r="BK19" s="78"/>
+      <c r="BL19" s="78"/>
+      <c r="BM19" s="78"/>
+      <c r="BN19" s="78"/>
+      <c r="BO19" s="78"/>
+      <c r="BP19" s="78"/>
+      <c r="BQ19" s="78"/>
+      <c r="BR19" s="78"/>
+      <c r="BS19" s="78"/>
+      <c r="BT19" s="81"/>
+      <c r="BU19" s="38"/>
+      <c r="BV19" s="39"/>
+    </row>
+    <row r="20" spans="2:74" ht="23.1" customHeight="1">
+      <c r="B20" s="150">
+        <v>3.2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>236</v>
+      </c>
+      <c r="D20" s="152" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="153">
+        <v>2</v>
+      </c>
+      <c r="F20" s="154">
+        <v>2</v>
+      </c>
+      <c r="G20" s="155">
+        <f>E20-F20</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="156"/>
+      <c r="I20" s="157"/>
+      <c r="J20" s="158"/>
+      <c r="K20" s="213"/>
+      <c r="L20" s="201">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M20" s="77"/>
+      <c r="N20" s="78"/>
+      <c r="O20" s="78"/>
+      <c r="P20" s="78"/>
+      <c r="Q20" s="78"/>
+      <c r="R20" s="80"/>
+      <c r="S20" s="80"/>
+      <c r="T20" s="80"/>
+      <c r="U20" s="80"/>
+      <c r="V20" s="80"/>
+      <c r="W20" s="78"/>
+      <c r="X20" s="78"/>
+      <c r="Y20" s="78"/>
+      <c r="Z20" s="78"/>
+      <c r="AA20" s="81"/>
+      <c r="AB20" s="77"/>
+      <c r="AC20" s="78"/>
+      <c r="AD20" s="78"/>
+      <c r="AE20" s="78"/>
+      <c r="AF20" s="78"/>
+      <c r="AG20" s="82"/>
+      <c r="AH20" s="82"/>
+      <c r="AI20" s="82"/>
+      <c r="AJ20" s="82"/>
+      <c r="AK20" s="82"/>
+      <c r="AL20" s="78"/>
+      <c r="AM20" s="78"/>
+      <c r="AN20" s="78"/>
+      <c r="AO20" s="78"/>
+      <c r="AP20" s="81"/>
+      <c r="AQ20" s="77"/>
+      <c r="AR20" s="78"/>
+      <c r="AS20" s="78"/>
+      <c r="AT20" s="78"/>
+      <c r="AU20" s="78"/>
+      <c r="AV20" s="83"/>
+      <c r="AW20" s="83"/>
+      <c r="AX20" s="83"/>
+      <c r="AY20" s="83"/>
+      <c r="AZ20" s="83"/>
+      <c r="BA20" s="78"/>
+      <c r="BB20" s="78"/>
+      <c r="BC20" s="78"/>
+      <c r="BD20" s="78"/>
+      <c r="BE20" s="81"/>
+      <c r="BF20" s="77"/>
+      <c r="BG20" s="78"/>
+      <c r="BH20" s="78"/>
+      <c r="BI20" s="78"/>
+      <c r="BJ20" s="78"/>
+      <c r="BK20" s="78"/>
+      <c r="BL20" s="78"/>
+      <c r="BM20" s="78"/>
+      <c r="BN20" s="78"/>
+      <c r="BO20" s="78"/>
+      <c r="BP20" s="78"/>
+      <c r="BQ20" s="78"/>
+      <c r="BR20" s="78"/>
+      <c r="BS20" s="78"/>
+      <c r="BT20" s="81"/>
+      <c r="BU20" s="38"/>
+      <c r="BV20" s="39"/>
+    </row>
+    <row r="21" spans="2:74" ht="23.1" customHeight="1">
+      <c r="B21" s="150" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D21" s="152" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="153">
+        <v>2</v>
+      </c>
+      <c r="F21" s="154">
+        <v>2</v>
+      </c>
+      <c r="G21" s="155">
+        <f>E21-F21</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="163"/>
+      <c r="I21" s="157"/>
+      <c r="J21" s="158"/>
+      <c r="K21" s="213"/>
+      <c r="L21" s="201">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M21" s="77"/>
+      <c r="N21" s="78"/>
+      <c r="O21" s="78"/>
+      <c r="P21" s="78"/>
+      <c r="Q21" s="78"/>
+      <c r="R21" s="80"/>
+      <c r="S21" s="80"/>
+      <c r="T21" s="80"/>
+      <c r="U21" s="80"/>
+      <c r="V21" s="80"/>
+      <c r="W21" s="78"/>
+      <c r="X21" s="78"/>
+      <c r="Y21" s="78"/>
+      <c r="Z21" s="78"/>
+      <c r="AA21" s="81"/>
+      <c r="AB21" s="77"/>
+      <c r="AC21" s="78"/>
+      <c r="AD21" s="78"/>
+      <c r="AE21" s="78"/>
+      <c r="AF21" s="78"/>
+      <c r="AG21" s="82"/>
+      <c r="AH21" s="82"/>
+      <c r="AI21" s="82"/>
+      <c r="AJ21" s="82"/>
+      <c r="AK21" s="82"/>
+      <c r="AL21" s="78"/>
+      <c r="AM21" s="78"/>
+      <c r="AN21" s="78"/>
+      <c r="AO21" s="78"/>
+      <c r="AP21" s="81"/>
+      <c r="AQ21" s="77"/>
+      <c r="AR21" s="78"/>
+      <c r="AS21" s="78"/>
+      <c r="AT21" s="78"/>
+      <c r="AU21" s="78"/>
+      <c r="AV21" s="83"/>
+      <c r="AW21" s="83"/>
+      <c r="AX21" s="83"/>
+      <c r="AY21" s="83"/>
+      <c r="AZ21" s="83"/>
+      <c r="BA21" s="78"/>
+      <c r="BB21" s="78"/>
+      <c r="BC21" s="78"/>
+      <c r="BD21" s="78"/>
+      <c r="BE21" s="81"/>
+      <c r="BF21" s="77"/>
+      <c r="BG21" s="78"/>
+      <c r="BH21" s="78"/>
+      <c r="BI21" s="78"/>
+      <c r="BJ21" s="78"/>
+      <c r="BK21" s="78"/>
+      <c r="BL21" s="78"/>
+      <c r="BM21" s="78"/>
+      <c r="BN21" s="78"/>
+      <c r="BO21" s="78"/>
+      <c r="BP21" s="78"/>
+      <c r="BQ21" s="78"/>
+      <c r="BR21" s="78"/>
+      <c r="BS21" s="78"/>
+      <c r="BT21" s="81"/>
+      <c r="BU21" s="38"/>
+      <c r="BV21" s="39"/>
+    </row>
+    <row r="22" spans="2:74" ht="23.1" customHeight="1">
+      <c r="B22" s="194" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="203" t="s">
+        <v>230</v>
+      </c>
+      <c r="D22" s="196"/>
+      <c r="E22" s="197">
+        <f>SUM(E23:E25)</f>
+        <v>12</v>
+      </c>
+      <c r="F22" s="197">
+        <f>SUM(F23:F25)</f>
+        <v>12</v>
+      </c>
+      <c r="G22" s="199">
+        <f>SUM(G23:G25)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="200"/>
+      <c r="I22" s="206">
+        <v>45943</v>
+      </c>
+      <c r="J22" s="206">
+        <v>45947</v>
+      </c>
+      <c r="K22" s="207">
+        <f>J22-I22+1</f>
+        <v>5</v>
+      </c>
+      <c r="L22" s="201">
+        <f>IFERROR(F22/E22,"")</f>
+        <v>1</v>
+      </c>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="74"/>
+      <c r="P22" s="74"/>
+      <c r="Q22" s="74"/>
+      <c r="R22" s="74"/>
+      <c r="S22" s="74"/>
+      <c r="T22" s="74"/>
+      <c r="U22" s="74"/>
+      <c r="V22" s="74"/>
+      <c r="W22" s="74"/>
+      <c r="X22" s="74"/>
+      <c r="Y22" s="74"/>
+      <c r="Z22" s="74"/>
+      <c r="AA22" s="75"/>
+      <c r="AB22" s="73"/>
+      <c r="AC22" s="74"/>
+      <c r="AD22" s="74"/>
+      <c r="AE22" s="74"/>
+      <c r="AF22" s="74"/>
+      <c r="AG22" s="74"/>
+      <c r="AH22" s="74"/>
+      <c r="AI22" s="74"/>
+      <c r="AJ22" s="74"/>
+      <c r="AK22" s="74"/>
+      <c r="AL22" s="74"/>
+      <c r="AM22" s="74"/>
+      <c r="AN22" s="74"/>
+      <c r="AO22" s="74"/>
+      <c r="AP22" s="75"/>
+      <c r="AQ22" s="73"/>
+      <c r="AR22" s="74"/>
+      <c r="AS22" s="74"/>
+      <c r="AT22" s="74"/>
+      <c r="AU22" s="74"/>
+      <c r="AV22" s="74"/>
+      <c r="AW22" s="74"/>
+      <c r="AX22" s="74"/>
+      <c r="AY22" s="74"/>
+      <c r="AZ22" s="74"/>
+      <c r="BA22" s="74"/>
+      <c r="BB22" s="74"/>
+      <c r="BC22" s="74"/>
+      <c r="BD22" s="74"/>
+      <c r="BE22" s="75"/>
+      <c r="BF22" s="73"/>
+      <c r="BG22" s="74"/>
+      <c r="BH22" s="74"/>
+      <c r="BI22" s="74"/>
+      <c r="BJ22" s="74"/>
+      <c r="BK22" s="78"/>
+      <c r="BL22" s="78"/>
+      <c r="BM22" s="78"/>
+      <c r="BN22" s="78"/>
+      <c r="BO22" s="78"/>
+      <c r="BP22" s="78"/>
+      <c r="BQ22" s="78"/>
+      <c r="BR22" s="78"/>
+      <c r="BS22" s="78"/>
+      <c r="BT22" s="81"/>
+      <c r="BU22" s="38"/>
+      <c r="BV22" s="39"/>
+    </row>
+    <row r="23" spans="2:74" ht="23.1" customHeight="1">
+      <c r="B23" s="150" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>237</v>
+      </c>
+      <c r="D23" s="152" t="s">
+        <v>130</v>
+      </c>
+      <c r="E23" s="153">
+        <v>4</v>
+      </c>
+      <c r="F23" s="154">
+        <v>4</v>
+      </c>
+      <c r="G23" s="155">
+        <f>E23-F23</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="156"/>
+      <c r="I23" s="157"/>
+      <c r="J23" s="158"/>
+      <c r="K23" s="213"/>
+      <c r="L23" s="201">
+        <f>IFERROR(F23/E23,"")</f>
+        <v>1</v>
+      </c>
+      <c r="M23" s="77"/>
+      <c r="N23" s="78"/>
+      <c r="O23" s="78"/>
+      <c r="P23" s="78"/>
+      <c r="Q23" s="78"/>
+      <c r="R23" s="80"/>
+      <c r="S23" s="80"/>
+      <c r="T23" s="80"/>
+      <c r="U23" s="80"/>
+      <c r="V23" s="80"/>
+      <c r="W23" s="78"/>
+      <c r="X23" s="78"/>
+      <c r="Y23" s="78"/>
+      <c r="Z23" s="78"/>
+      <c r="AA23" s="81"/>
+      <c r="AB23" s="77"/>
+      <c r="AC23" s="78"/>
+      <c r="AD23" s="78"/>
+      <c r="AE23" s="78"/>
+      <c r="AF23" s="78"/>
+      <c r="AG23" s="82"/>
+      <c r="AH23" s="82"/>
+      <c r="AI23" s="82"/>
+      <c r="AJ23" s="82"/>
+      <c r="AK23" s="82"/>
+      <c r="AL23" s="78"/>
+      <c r="AM23" s="78"/>
+      <c r="AN23" s="78"/>
+      <c r="AO23" s="78"/>
+      <c r="AP23" s="81"/>
+      <c r="AQ23" s="77"/>
+      <c r="AR23" s="78"/>
+      <c r="AS23" s="78"/>
+      <c r="AT23" s="78"/>
+      <c r="AU23" s="78"/>
+      <c r="AV23" s="83"/>
+      <c r="AW23" s="83"/>
+      <c r="AX23" s="83"/>
+      <c r="AY23" s="83"/>
+      <c r="AZ23" s="83"/>
+      <c r="BA23" s="78"/>
+      <c r="BB23" s="78"/>
+      <c r="BC23" s="78"/>
+      <c r="BD23" s="78"/>
+      <c r="BE23" s="81"/>
+      <c r="BF23" s="77"/>
+      <c r="BG23" s="78"/>
+      <c r="BH23" s="78"/>
+      <c r="BI23" s="78"/>
+      <c r="BJ23" s="78"/>
+      <c r="BK23" s="78"/>
+      <c r="BL23" s="78"/>
+      <c r="BM23" s="78"/>
+      <c r="BN23" s="78"/>
+      <c r="BO23" s="78"/>
+      <c r="BP23" s="78"/>
+      <c r="BQ23" s="78"/>
+      <c r="BR23" s="78"/>
+      <c r="BS23" s="78"/>
+      <c r="BT23" s="81"/>
+      <c r="BU23" s="38"/>
+      <c r="BV23" s="39"/>
+    </row>
+    <row r="24" spans="2:74" ht="23.1" customHeight="1">
+      <c r="B24" s="150" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" t="s">
+        <v>238</v>
+      </c>
+      <c r="D24" s="152" t="s">
+        <v>130</v>
+      </c>
+      <c r="E24" s="153">
+        <v>4</v>
+      </c>
+      <c r="F24" s="154">
+        <v>4</v>
+      </c>
+      <c r="G24" s="155">
+        <f>E24-F24</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="156"/>
+      <c r="I24" s="157"/>
+      <c r="J24" s="158"/>
+      <c r="K24" s="213"/>
+      <c r="L24" s="201">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M24" s="77"/>
+      <c r="N24" s="78"/>
+      <c r="O24" s="78"/>
+      <c r="P24" s="78"/>
+      <c r="Q24" s="78"/>
+      <c r="R24" s="80"/>
+      <c r="S24" s="80"/>
+      <c r="T24" s="80"/>
+      <c r="U24" s="80"/>
+      <c r="V24" s="80"/>
+      <c r="W24" s="78"/>
+      <c r="X24" s="78"/>
+      <c r="Y24" s="78"/>
+      <c r="Z24" s="78"/>
+      <c r="AA24" s="81"/>
+      <c r="AB24" s="77"/>
+      <c r="AC24" s="78"/>
+      <c r="AD24" s="78"/>
+      <c r="AE24" s="78"/>
+      <c r="AF24" s="78"/>
+      <c r="AG24" s="82"/>
+      <c r="AH24" s="82"/>
+      <c r="AI24" s="82"/>
+      <c r="AJ24" s="82"/>
+      <c r="AK24" s="82"/>
+      <c r="AL24" s="78"/>
+      <c r="AM24" s="78"/>
+      <c r="AN24" s="78"/>
+      <c r="AO24" s="78"/>
+      <c r="AP24" s="81"/>
+      <c r="AQ24" s="77"/>
+      <c r="AR24" s="78"/>
+      <c r="AS24" s="78"/>
+      <c r="AT24" s="78"/>
+      <c r="AU24" s="78"/>
+      <c r="AV24" s="83"/>
+      <c r="AW24" s="83"/>
+      <c r="AX24" s="83"/>
+      <c r="AY24" s="83"/>
+      <c r="AZ24" s="83"/>
+      <c r="BA24" s="78"/>
+      <c r="BB24" s="78"/>
+      <c r="BC24" s="78"/>
+      <c r="BD24" s="78"/>
+      <c r="BE24" s="81"/>
+      <c r="BF24" s="77"/>
+      <c r="BG24" s="78"/>
+      <c r="BH24" s="78"/>
+      <c r="BI24" s="78"/>
+      <c r="BJ24" s="78"/>
+      <c r="BK24" s="78"/>
+      <c r="BL24" s="78"/>
+      <c r="BM24" s="78"/>
+      <c r="BN24" s="78"/>
+      <c r="BO24" s="78"/>
+      <c r="BP24" s="78"/>
+      <c r="BQ24" s="78"/>
+      <c r="BR24" s="78"/>
+      <c r="BS24" s="78"/>
+      <c r="BT24" s="81"/>
+      <c r="BU24" s="38"/>
+      <c r="BV24" s="39"/>
+    </row>
+    <row r="25" spans="2:74" ht="23.1" customHeight="1">
+      <c r="B25" s="150" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" t="s">
+        <v>242</v>
+      </c>
+      <c r="D25" s="152" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" s="153">
+        <v>4</v>
+      </c>
+      <c r="F25" s="154">
+        <v>4</v>
+      </c>
+      <c r="G25" s="155">
+        <f>E25-F25</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="156"/>
+      <c r="I25" s="157"/>
+      <c r="J25" s="158"/>
+      <c r="K25" s="213"/>
+      <c r="L25" s="201">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M25" s="77"/>
+      <c r="N25" s="78"/>
+      <c r="O25" s="78"/>
+      <c r="P25" s="78"/>
+      <c r="Q25" s="78"/>
+      <c r="R25" s="80"/>
+      <c r="S25" s="80"/>
+      <c r="T25" s="80"/>
+      <c r="U25" s="80"/>
+      <c r="V25" s="80"/>
+      <c r="W25" s="78"/>
+      <c r="X25" s="78"/>
+      <c r="Y25" s="78"/>
+      <c r="Z25" s="78"/>
+      <c r="AA25" s="81"/>
+      <c r="AB25" s="77"/>
+      <c r="AC25" s="78"/>
+      <c r="AD25" s="78"/>
+      <c r="AE25" s="78"/>
+      <c r="AF25" s="78"/>
+      <c r="AG25" s="82"/>
+      <c r="AH25" s="82"/>
+      <c r="AI25" s="82"/>
+      <c r="AJ25" s="82"/>
+      <c r="AK25" s="82"/>
+      <c r="AL25" s="78"/>
+      <c r="AM25" s="78"/>
+      <c r="AN25" s="78"/>
+      <c r="AO25" s="78"/>
+      <c r="AP25" s="81"/>
+      <c r="AQ25" s="77"/>
+      <c r="AR25" s="78"/>
+      <c r="AS25" s="78"/>
+      <c r="AT25" s="78"/>
+      <c r="AU25" s="78"/>
+      <c r="AV25" s="83"/>
+      <c r="AW25" s="83"/>
+      <c r="AX25" s="83"/>
+      <c r="AY25" s="83"/>
+      <c r="AZ25" s="83"/>
+      <c r="BA25" s="78"/>
+      <c r="BB25" s="78"/>
+      <c r="BC25" s="78"/>
+      <c r="BD25" s="78"/>
+      <c r="BE25" s="81"/>
+      <c r="BF25" s="77"/>
+      <c r="BG25" s="78"/>
+      <c r="BH25" s="78"/>
+      <c r="BI25" s="78"/>
+      <c r="BJ25" s="78"/>
+      <c r="BK25" s="78"/>
+      <c r="BL25" s="78"/>
+      <c r="BM25" s="78"/>
+      <c r="BN25" s="78"/>
+      <c r="BO25" s="78"/>
+      <c r="BP25" s="78"/>
+      <c r="BQ25" s="78"/>
+      <c r="BR25" s="78"/>
+      <c r="BS25" s="78"/>
+      <c r="BT25" s="81"/>
+      <c r="BU25" s="38"/>
+      <c r="BV25" s="39"/>
+    </row>
+    <row r="26" spans="2:74" ht="23.1" customHeight="1">
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="223"/>
+      <c r="E26" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" s="224" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="224" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26" s="224" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" s="224" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
+      <c r="S26" s="38"/>
+      <c r="T26" s="38"/>
+      <c r="U26" s="38"/>
+      <c r="V26" s="38"/>
+      <c r="W26" s="38"/>
+      <c r="X26" s="38"/>
+      <c r="Y26" s="38"/>
+      <c r="Z26" s="38"/>
+      <c r="AA26" s="38"/>
+      <c r="AB26" s="38"/>
+      <c r="AC26" s="38"/>
+      <c r="AD26" s="38"/>
+      <c r="AE26" s="38"/>
+      <c r="AF26" s="38"/>
+      <c r="AG26" s="38"/>
+      <c r="AH26" s="38"/>
+      <c r="AI26" s="38"/>
+      <c r="AJ26" s="38"/>
+      <c r="AK26" s="38"/>
+      <c r="AL26" s="38"/>
+      <c r="AM26" s="38"/>
+      <c r="AN26" s="38"/>
+      <c r="AO26" s="38"/>
+      <c r="AP26" s="38"/>
+      <c r="AQ26" s="38"/>
+      <c r="AR26" s="38"/>
+      <c r="AS26" s="38"/>
+      <c r="AT26" s="38"/>
+      <c r="AU26" s="38"/>
+      <c r="AV26" s="38"/>
+      <c r="AW26" s="38"/>
+      <c r="AX26" s="38"/>
+      <c r="AY26" s="38"/>
+      <c r="AZ26" s="38"/>
+      <c r="BA26" s="38"/>
+      <c r="BB26" s="38"/>
+      <c r="BC26" s="38"/>
+      <c r="BD26" s="38"/>
+      <c r="BE26" s="38"/>
+      <c r="BF26" s="38"/>
+      <c r="BG26" s="38"/>
+      <c r="BH26" s="38"/>
+      <c r="BI26" s="38"/>
+      <c r="BJ26" s="38"/>
+      <c r="BK26" s="38"/>
+      <c r="BL26" s="38"/>
+      <c r="BM26" s="38"/>
+      <c r="BN26" s="38"/>
+      <c r="BO26" s="38"/>
+      <c r="BP26" s="38"/>
+      <c r="BQ26" s="38"/>
+      <c r="BR26" s="38"/>
+      <c r="BS26" s="38"/>
+      <c r="BT26" s="38"/>
+      <c r="BU26" s="38"/>
+      <c r="BV26" s="39"/>
+    </row>
+    <row r="27" spans="2:74" ht="23.1" customHeight="1">
+      <c r="B27" s="38"/>
+      <c r="C27" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="215" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="216">
+        <f>SUM(E11:E13,E15:E17,E19:E21,E23:E25)</f>
+        <v>36</v>
+      </c>
+      <c r="F27" s="216">
+        <f>SUM(F11:F13,F15:F17,F19:F21,F23:F25)</f>
+        <v>36</v>
+      </c>
+      <c r="G27" s="216">
+        <f>SUM(G11:G13,G15:G17,G19:G21,G23:G25)</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="217">
+        <v>5</v>
+      </c>
+      <c r="I27" s="218">
+        <f>E27/H27</f>
+        <v>7.2</v>
+      </c>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="182" t="s">
+        <v>45</v>
+      </c>
+      <c r="M27" s="95">
+        <v>1</v>
+      </c>
+      <c r="N27" s="95">
+        <v>2</v>
+      </c>
+      <c r="O27" s="95">
+        <v>3</v>
+      </c>
+      <c r="P27" s="95">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="95">
+        <v>5</v>
+      </c>
+      <c r="R27" s="95"/>
+      <c r="S27" s="95"/>
+      <c r="T27" s="95"/>
+      <c r="U27" s="95"/>
+      <c r="V27" s="95"/>
+      <c r="W27" s="95"/>
+      <c r="X27" s="95"/>
+      <c r="Y27" s="95"/>
+      <c r="Z27" s="95"/>
+      <c r="AA27" s="95"/>
+      <c r="AB27" s="95"/>
+      <c r="AC27" s="95"/>
+      <c r="AD27" s="95"/>
+      <c r="AE27" s="95"/>
+      <c r="AF27" s="95"/>
+      <c r="AG27" s="95"/>
+      <c r="AH27" s="95"/>
+      <c r="AI27" s="95"/>
+      <c r="AJ27" s="95"/>
+      <c r="AK27" s="95"/>
+      <c r="AL27" s="95"/>
+      <c r="AM27" s="95"/>
+      <c r="AN27" s="95"/>
+      <c r="AO27" s="95"/>
+      <c r="AP27" s="95"/>
+      <c r="AQ27" s="95"/>
+      <c r="AR27" s="95"/>
+      <c r="AS27" s="95"/>
+      <c r="AT27" s="95"/>
+      <c r="AU27" s="95"/>
+      <c r="AV27" s="95"/>
+      <c r="AW27" s="95"/>
+      <c r="AX27" s="95"/>
+      <c r="AY27" s="95"/>
+      <c r="AZ27" s="95"/>
+      <c r="BA27" s="95"/>
+      <c r="BB27" s="95"/>
+      <c r="BC27" s="95"/>
+      <c r="BD27" s="95"/>
+      <c r="BE27" s="95"/>
+      <c r="BF27" s="95"/>
+      <c r="BG27" s="95"/>
+      <c r="BH27" s="95"/>
+      <c r="BI27" s="95"/>
+      <c r="BJ27" s="95"/>
+      <c r="BK27" s="95"/>
+      <c r="BL27" s="95"/>
+      <c r="BM27" s="95"/>
+      <c r="BN27" s="95"/>
+      <c r="BO27" s="95"/>
+      <c r="BP27" s="95"/>
+      <c r="BQ27" s="95"/>
+      <c r="BR27" s="95"/>
+      <c r="BS27" s="95"/>
+      <c r="BT27" s="95"/>
+      <c r="BU27" s="38"/>
+      <c r="BV27" s="137" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="2:74" ht="23.1" customHeight="1">
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="96" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="182" t="s">
+        <v>48</v>
+      </c>
+      <c r="M28" s="97">
+        <f>E27</f>
+        <v>36</v>
+      </c>
+      <c r="N28" s="98">
+        <f>M28-I27</f>
+        <v>28.8</v>
+      </c>
+      <c r="O28" s="98">
+        <f>N28-I27</f>
+        <v>21.6</v>
+      </c>
+      <c r="P28" s="98">
+        <f>O28-I27</f>
+        <v>14.400000000000002</v>
+      </c>
+      <c r="Q28" s="98">
+        <f>P28-I27</f>
+        <v>7.200000000000002</v>
+      </c>
+      <c r="R28" s="98"/>
+      <c r="S28" s="98"/>
+      <c r="T28" s="98"/>
+      <c r="U28" s="98"/>
+      <c r="V28" s="98"/>
+      <c r="W28" s="98"/>
+      <c r="X28" s="98"/>
+      <c r="Y28" s="98"/>
+      <c r="Z28" s="98"/>
+      <c r="AA28" s="98"/>
+      <c r="AB28" s="98"/>
+      <c r="AC28" s="98"/>
+      <c r="AD28" s="98"/>
+      <c r="AE28" s="98"/>
+      <c r="AF28" s="98"/>
+      <c r="AG28" s="98"/>
+      <c r="AH28" s="98"/>
+      <c r="AI28" s="98"/>
+      <c r="AJ28" s="98"/>
+      <c r="AK28" s="98"/>
+      <c r="AL28" s="98"/>
+      <c r="AM28" s="98"/>
+      <c r="AN28" s="98"/>
+      <c r="AO28" s="98"/>
+      <c r="AP28" s="98"/>
+      <c r="AQ28" s="98"/>
+      <c r="AR28" s="98"/>
+      <c r="AS28" s="98"/>
+      <c r="AT28" s="98"/>
+      <c r="AU28" s="98"/>
+      <c r="AV28" s="98"/>
+      <c r="AW28" s="98"/>
+      <c r="AX28" s="98"/>
+      <c r="AY28" s="98"/>
+      <c r="AZ28" s="98"/>
+      <c r="BA28" s="98"/>
+      <c r="BB28" s="98"/>
+      <c r="BC28" s="98"/>
+      <c r="BD28" s="98"/>
+      <c r="BE28" s="98"/>
+      <c r="BF28" s="98"/>
+      <c r="BG28" s="98"/>
+      <c r="BH28" s="98"/>
+      <c r="BI28" s="98"/>
+      <c r="BJ28" s="98"/>
+      <c r="BK28" s="98"/>
+      <c r="BL28" s="98"/>
+      <c r="BM28" s="98"/>
+      <c r="BN28" s="98"/>
+      <c r="BO28" s="98"/>
+      <c r="BP28" s="98"/>
+      <c r="BQ28" s="98"/>
+      <c r="BR28" s="98"/>
+      <c r="BS28" s="98"/>
+      <c r="BT28" s="98"/>
+      <c r="BU28" s="38"/>
+      <c r="BV28" s="138" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="2:74" ht="23.1" customHeight="1">
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
+      <c r="J29" s="38"/>
+      <c r="K29" s="38"/>
+      <c r="L29" s="182" t="s">
+        <v>28</v>
+      </c>
+      <c r="M29" s="97">
+        <f>E27</f>
+        <v>36</v>
+      </c>
+      <c r="N29" s="97">
+        <f t="shared" ref="N29:S29" si="1">M31</f>
+        <v>24</v>
+      </c>
+      <c r="O29" s="97">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="P29" s="97">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Q29" s="97">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R29" s="97"/>
+      <c r="S29" s="97"/>
+      <c r="T29" s="97"/>
+      <c r="U29" s="97"/>
+      <c r="V29" s="97"/>
+      <c r="W29" s="97"/>
+      <c r="X29" s="97"/>
+      <c r="Y29" s="97"/>
+      <c r="Z29" s="97"/>
+      <c r="AA29" s="97"/>
+      <c r="AB29" s="97"/>
+      <c r="AC29" s="97"/>
+      <c r="AD29" s="97"/>
+      <c r="AE29" s="97"/>
+      <c r="AF29" s="97"/>
+      <c r="AG29" s="97"/>
+      <c r="AH29" s="97"/>
+      <c r="AI29" s="97"/>
+      <c r="AJ29" s="97"/>
+      <c r="AK29" s="97"/>
+      <c r="AL29" s="97"/>
+      <c r="AM29" s="97"/>
+      <c r="AN29" s="97"/>
+      <c r="AO29" s="97"/>
+      <c r="AP29" s="97"/>
+      <c r="AQ29" s="97"/>
+      <c r="AR29" s="97"/>
+      <c r="AS29" s="97"/>
+      <c r="AT29" s="97"/>
+      <c r="AU29" s="97"/>
+      <c r="AV29" s="97"/>
+      <c r="AW29" s="97"/>
+      <c r="AX29" s="97"/>
+      <c r="AY29" s="97"/>
+      <c r="AZ29" s="97"/>
+      <c r="BA29" s="97"/>
+      <c r="BB29" s="97"/>
+      <c r="BC29" s="97"/>
+      <c r="BD29" s="97"/>
+      <c r="BE29" s="97"/>
+      <c r="BF29" s="97"/>
+      <c r="BG29" s="97"/>
+      <c r="BH29" s="97"/>
+      <c r="BI29" s="97"/>
+      <c r="BJ29" s="97"/>
+      <c r="BK29" s="97"/>
+      <c r="BL29" s="97"/>
+      <c r="BM29" s="97"/>
+      <c r="BN29" s="97"/>
+      <c r="BO29" s="97"/>
+      <c r="BP29" s="97"/>
+      <c r="BQ29" s="97"/>
+      <c r="BR29" s="97"/>
+      <c r="BS29" s="97"/>
+      <c r="BT29" s="97"/>
+      <c r="BU29" s="38"/>
+      <c r="BV29" s="139">
+        <f>SUM(M29:BT29)</f>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="2:74" ht="23.1" customHeight="1">
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="99" t="s">
+        <v>50</v>
+      </c>
+      <c r="L30" s="182" t="s">
+        <v>51</v>
+      </c>
+      <c r="M30" s="76">
+        <v>12</v>
+      </c>
+      <c r="N30" s="76">
+        <v>10</v>
+      </c>
+      <c r="O30" s="76">
+        <v>11</v>
+      </c>
+      <c r="P30" s="76">
+        <v>3</v>
+      </c>
+      <c r="Q30" s="76">
+        <v>0</v>
+      </c>
+      <c r="R30" s="76"/>
+      <c r="S30" s="76"/>
+      <c r="T30" s="76"/>
+      <c r="U30" s="76"/>
+      <c r="V30" s="76"/>
+      <c r="W30" s="76"/>
+      <c r="X30" s="76"/>
+      <c r="Y30" s="76"/>
+      <c r="Z30" s="76"/>
+      <c r="AA30" s="76"/>
+      <c r="AB30" s="76"/>
+      <c r="AC30" s="76"/>
+      <c r="AD30" s="76"/>
+      <c r="AE30" s="76"/>
+      <c r="AF30" s="76"/>
+      <c r="AG30" s="76"/>
+      <c r="AH30" s="76"/>
+      <c r="AI30" s="76"/>
+      <c r="AJ30" s="76"/>
+      <c r="AK30" s="76"/>
+      <c r="AL30" s="76"/>
+      <c r="AM30" s="76"/>
+      <c r="AN30" s="76"/>
+      <c r="AO30" s="76"/>
+      <c r="AP30" s="76"/>
+      <c r="AQ30" s="76"/>
+      <c r="AR30" s="76"/>
+      <c r="AS30" s="76"/>
+      <c r="AT30" s="76"/>
+      <c r="AU30" s="76"/>
+      <c r="AV30" s="76"/>
+      <c r="AW30" s="76"/>
+      <c r="AX30" s="76"/>
+      <c r="AY30" s="76"/>
+      <c r="AZ30" s="76"/>
+      <c r="BA30" s="76"/>
+      <c r="BB30" s="76"/>
+      <c r="BC30" s="76"/>
+      <c r="BD30" s="76"/>
+      <c r="BE30" s="76"/>
+      <c r="BF30" s="76"/>
+      <c r="BG30" s="76"/>
+      <c r="BH30" s="76"/>
+      <c r="BI30" s="76"/>
+      <c r="BJ30" s="76"/>
+      <c r="BK30" s="76"/>
+      <c r="BL30" s="76"/>
+      <c r="BM30" s="76"/>
+      <c r="BN30" s="76"/>
+      <c r="BO30" s="76"/>
+      <c r="BP30" s="76"/>
+      <c r="BQ30" s="76"/>
+      <c r="BR30" s="76"/>
+      <c r="BS30" s="76"/>
+      <c r="BT30" s="76"/>
+      <c r="BU30" s="38"/>
+      <c r="BV30" s="140">
+        <f>SUM(M30:BT30)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="2:74" ht="23.1" customHeight="1">
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="182" t="s">
+        <v>52</v>
+      </c>
+      <c r="M31" s="97">
+        <f t="shared" ref="M31:S31" si="2">M29-M30</f>
+        <v>24</v>
+      </c>
+      <c r="N31" s="97">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="O31" s="97">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="P31" s="97">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="97">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R31" s="97"/>
+      <c r="S31" s="97"/>
+      <c r="T31" s="97"/>
+      <c r="U31" s="97"/>
+      <c r="V31" s="97"/>
+      <c r="W31" s="97"/>
+      <c r="X31" s="97"/>
+      <c r="Y31" s="97"/>
+      <c r="Z31" s="97"/>
+      <c r="AA31" s="97"/>
+      <c r="AB31" s="97"/>
+      <c r="AC31" s="97"/>
+      <c r="AD31" s="97"/>
+      <c r="AE31" s="97"/>
+      <c r="AF31" s="97"/>
+      <c r="AG31" s="97"/>
+      <c r="AH31" s="97"/>
+      <c r="AI31" s="97"/>
+      <c r="AJ31" s="97"/>
+      <c r="AK31" s="97"/>
+      <c r="AL31" s="97"/>
+      <c r="AM31" s="97"/>
+      <c r="AN31" s="97"/>
+      <c r="AO31" s="97"/>
+      <c r="AP31" s="97"/>
+      <c r="AQ31" s="97"/>
+      <c r="AR31" s="97"/>
+      <c r="AS31" s="97"/>
+      <c r="AT31" s="97"/>
+      <c r="AU31" s="97"/>
+      <c r="AV31" s="97"/>
+      <c r="AW31" s="97"/>
+      <c r="AX31" s="97"/>
+      <c r="AY31" s="97"/>
+      <c r="AZ31" s="97"/>
+      <c r="BA31" s="97"/>
+      <c r="BB31" s="97"/>
+      <c r="BC31" s="97"/>
+      <c r="BD31" s="97"/>
+      <c r="BE31" s="97"/>
+      <c r="BF31" s="97"/>
+      <c r="BG31" s="97"/>
+      <c r="BH31" s="97"/>
+      <c r="BI31" s="97"/>
+      <c r="BJ31" s="97"/>
+      <c r="BK31" s="97"/>
+      <c r="BL31" s="97"/>
+      <c r="BM31" s="97"/>
+      <c r="BN31" s="97"/>
+      <c r="BO31" s="97"/>
+      <c r="BP31" s="97"/>
+      <c r="BQ31" s="97"/>
+      <c r="BR31" s="97"/>
+      <c r="BS31" s="97"/>
+      <c r="BT31" s="97"/>
+      <c r="BU31" s="38"/>
+      <c r="BV31" s="140">
+        <f>SUM(M31:BT31)</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="2:74" ht="19.5" customHeight="1">
+      <c r="C32" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="I32" s="210"/>
+    </row>
+    <row r="33" spans="2:74" ht="381.95" customHeight="1"/>
+    <row r="34" spans="2:74" ht="216.95" customHeight="1"/>
+    <row r="36" spans="2:74" ht="50.1" customHeight="1">
+      <c r="B36" s="253"/>
+      <c r="C36" s="254"/>
+      <c r="D36" s="254"/>
+      <c r="E36" s="254"/>
+      <c r="F36" s="254"/>
+      <c r="G36" s="254"/>
+      <c r="H36" s="254"/>
+      <c r="I36" s="254"/>
+      <c r="J36" s="254"/>
+      <c r="K36" s="254"/>
+      <c r="L36" s="254"/>
+      <c r="M36" s="254"/>
+      <c r="N36" s="254"/>
+      <c r="O36" s="254"/>
+      <c r="P36" s="254"/>
+      <c r="Q36" s="254"/>
+      <c r="R36" s="254"/>
+      <c r="S36" s="254"/>
+      <c r="T36" s="254"/>
+      <c r="U36" s="254"/>
+      <c r="V36" s="254"/>
+      <c r="W36" s="254"/>
+      <c r="X36" s="254"/>
+      <c r="Y36" s="254"/>
+      <c r="Z36" s="254"/>
+      <c r="AA36" s="254"/>
+      <c r="AB36" s="254"/>
+      <c r="AC36" s="254"/>
+      <c r="AD36" s="254"/>
+      <c r="AE36" s="254"/>
+      <c r="AF36" s="254"/>
+      <c r="AG36" s="254"/>
+      <c r="AH36" s="254"/>
+      <c r="AI36" s="254"/>
+      <c r="AJ36" s="254"/>
+      <c r="AK36" s="254"/>
+      <c r="AL36" s="254"/>
+      <c r="AM36" s="254"/>
+      <c r="AN36" s="254"/>
+      <c r="AO36" s="254"/>
+      <c r="AP36" s="254"/>
+      <c r="AQ36" s="254"/>
+      <c r="AR36" s="254"/>
+      <c r="AS36" s="254"/>
+      <c r="AT36" s="254"/>
+      <c r="AU36" s="254"/>
+      <c r="AV36" s="254"/>
+      <c r="AW36" s="254"/>
+      <c r="AX36" s="254"/>
+      <c r="AY36" s="254"/>
+      <c r="AZ36" s="254"/>
+      <c r="BA36" s="254"/>
+      <c r="BB36" s="254"/>
+      <c r="BC36" s="254"/>
+      <c r="BD36" s="254"/>
+      <c r="BE36" s="254"/>
+      <c r="BF36" s="254"/>
+      <c r="BG36" s="254"/>
+      <c r="BH36" s="254"/>
+      <c r="BI36" s="254"/>
+      <c r="BJ36" s="254"/>
+      <c r="BK36" s="254"/>
+      <c r="BL36" s="254"/>
+      <c r="BM36" s="254"/>
+      <c r="BN36" s="254"/>
+      <c r="BO36" s="254"/>
+      <c r="BP36" s="254"/>
+      <c r="BQ36" s="254"/>
+      <c r="BR36" s="254"/>
+      <c r="BS36" s="254"/>
+      <c r="BT36" s="254"/>
+      <c r="BU36" s="254"/>
+      <c r="BV36" s="255"/>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="BP8:BT8"/>
+    <mergeCell ref="B36:BV36"/>
+    <mergeCell ref="AL8:AP8"/>
+    <mergeCell ref="AQ8:AU8"/>
+    <mergeCell ref="AV8:AZ8"/>
+    <mergeCell ref="BA8:BE8"/>
+    <mergeCell ref="BF8:BJ8"/>
+    <mergeCell ref="BK8:BO8"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="W8:AA8"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="K3:K7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+  </mergeCells>
+  <conditionalFormatting sqref="L10">
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="100"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F468828E-F591-4F6E-8630-EE2E0E21BEB0}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L10">
+    <cfRule type="dataBar" priority="8">
+      <dataBar>
+        <cfvo type="percent" val="1"/>
+        <cfvo type="percent" val="100"/>
+        <color theme="8" tint="0.59999389629810485"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L10">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{7E70744F-559E-40BB-BD6F-66AC40CD7CCE}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8CF923FF-0E48-41D4-88A1-2CE472F5DE49}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L11:L25">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="100"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3B63E29E-37A6-45A1-B45B-41415DD0D82E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L11:L25">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="percent" val="1"/>
+        <cfvo type="percent" val="100"/>
+        <color theme="8" tint="0.59999389629810485"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L11:L25">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{522B54EB-BBBB-4C29-A65F-6D65D2F0E885}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{96E68EAF-F47B-4A5A-902A-9B4C903A3796}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0" footer="0"/>
+  <pageSetup scale="32" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{F468828E-F591-4F6E-8630-EE2E0E21BEB0}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L10</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{7E70744F-559E-40BB-BD6F-66AC40CD7CCE}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{8CF923FF-0E48-41D4-88A1-2CE472F5DE49}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L10</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{3B63E29E-37A6-45A1-B45B-41415DD0D82E}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L11:L25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{522B54EB-BBBB-4C29-A65F-6D65D2F0E885}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{96E68EAF-F47B-4A5A-902A-9B4C903A3796}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L11:L25</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{097109D2-447F-4F39-A4BD-92E74C4EFF49}">
   <dimension ref="B3:I9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
@@ -25294,7 +29218,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3" tint="0.39997558519241921"/>
@@ -25404,7 +29328,7 @@
       <c r="H2" s="40"/>
       <c r="I2" s="40"/>
       <c r="J2" s="41"/>
-      <c r="K2" s="243" t="s">
+      <c r="K2" s="259" t="s">
         <v>1</v>
       </c>
       <c r="L2" s="42" t="s">
@@ -25483,7 +29407,7 @@
       <c r="H3" s="40"/>
       <c r="I3" s="40"/>
       <c r="J3" s="41"/>
-      <c r="K3" s="244"/>
+      <c r="K3" s="260"/>
       <c r="L3" s="47" t="s">
         <v>3</v>
       </c>
@@ -25560,7 +29484,7 @@
       <c r="H4" s="37"/>
       <c r="I4" s="36"/>
       <c r="J4" s="37"/>
-      <c r="K4" s="244"/>
+      <c r="K4" s="260"/>
       <c r="L4" s="52" t="s">
         <v>4</v>
       </c>
@@ -25637,7 +29561,7 @@
       <c r="H5" s="37"/>
       <c r="I5" s="36"/>
       <c r="J5" s="37"/>
-      <c r="K5" s="244"/>
+      <c r="K5" s="260"/>
       <c r="L5" s="54" t="s">
         <v>5</v>
       </c>
@@ -25714,7 +29638,7 @@
       <c r="H6" s="37"/>
       <c r="I6" s="36"/>
       <c r="J6" s="37"/>
-      <c r="K6" s="245"/>
+      <c r="K6" s="261"/>
       <c r="L6" s="56" t="s">
         <v>6</v>
       </c>
@@ -25782,126 +29706,126 @@
       <c r="BV6" s="39"/>
     </row>
     <row r="7" spans="2:74" ht="23.1" customHeight="1">
-      <c r="B7" s="260" t="s">
+      <c r="B7" s="242" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="268" t="s">
+      <c r="C7" s="251" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="264" t="s">
+      <c r="D7" s="246" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="240" t="s">
+      <c r="E7" s="256" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="241"/>
-      <c r="G7" s="242"/>
-      <c r="H7" s="262" t="s">
+      <c r="F7" s="257"/>
+      <c r="G7" s="258"/>
+      <c r="H7" s="244" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="266" t="s">
+      <c r="I7" s="248" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="267" t="s">
+      <c r="J7" s="249" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="246" t="s">
+      <c r="K7" s="262" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="248" t="s">
+      <c r="L7" s="263" t="s">
         <v>15</v>
       </c>
-      <c r="M7" s="250" t="s">
+      <c r="M7" s="265" t="s">
         <v>16</v>
       </c>
-      <c r="N7" s="251"/>
-      <c r="O7" s="251"/>
-      <c r="P7" s="251"/>
-      <c r="Q7" s="252"/>
-      <c r="R7" s="253" t="s">
+      <c r="N7" s="240"/>
+      <c r="O7" s="240"/>
+      <c r="P7" s="240"/>
+      <c r="Q7" s="241"/>
+      <c r="R7" s="266" t="s">
         <v>17</v>
       </c>
-      <c r="S7" s="251"/>
-      <c r="T7" s="251"/>
-      <c r="U7" s="251"/>
-      <c r="V7" s="252"/>
-      <c r="W7" s="253" t="s">
+      <c r="S7" s="240"/>
+      <c r="T7" s="240"/>
+      <c r="U7" s="240"/>
+      <c r="V7" s="241"/>
+      <c r="W7" s="266" t="s">
         <v>18</v>
       </c>
-      <c r="X7" s="251"/>
-      <c r="Y7" s="251"/>
-      <c r="Z7" s="251"/>
-      <c r="AA7" s="252"/>
-      <c r="AB7" s="255" t="s">
+      <c r="X7" s="240"/>
+      <c r="Y7" s="240"/>
+      <c r="Z7" s="240"/>
+      <c r="AA7" s="241"/>
+      <c r="AB7" s="268" t="s">
         <v>19</v>
       </c>
-      <c r="AC7" s="251"/>
-      <c r="AD7" s="251"/>
-      <c r="AE7" s="251"/>
-      <c r="AF7" s="252"/>
-      <c r="AG7" s="256" t="s">
+      <c r="AC7" s="240"/>
+      <c r="AD7" s="240"/>
+      <c r="AE7" s="240"/>
+      <c r="AF7" s="241"/>
+      <c r="AG7" s="269" t="s">
         <v>20</v>
       </c>
-      <c r="AH7" s="251"/>
-      <c r="AI7" s="251"/>
-      <c r="AJ7" s="251"/>
-      <c r="AK7" s="252"/>
-      <c r="AL7" s="256" t="s">
+      <c r="AH7" s="240"/>
+      <c r="AI7" s="240"/>
+      <c r="AJ7" s="240"/>
+      <c r="AK7" s="241"/>
+      <c r="AL7" s="269" t="s">
         <v>21</v>
       </c>
-      <c r="AM7" s="251"/>
-      <c r="AN7" s="251"/>
-      <c r="AO7" s="251"/>
-      <c r="AP7" s="252"/>
-      <c r="AQ7" s="254" t="s">
+      <c r="AM7" s="240"/>
+      <c r="AN7" s="240"/>
+      <c r="AO7" s="240"/>
+      <c r="AP7" s="241"/>
+      <c r="AQ7" s="267" t="s">
         <v>22</v>
       </c>
-      <c r="AR7" s="251"/>
-      <c r="AS7" s="251"/>
-      <c r="AT7" s="251"/>
-      <c r="AU7" s="252"/>
-      <c r="AV7" s="257" t="s">
+      <c r="AR7" s="240"/>
+      <c r="AS7" s="240"/>
+      <c r="AT7" s="240"/>
+      <c r="AU7" s="241"/>
+      <c r="AV7" s="270" t="s">
         <v>23</v>
       </c>
-      <c r="AW7" s="251"/>
-      <c r="AX7" s="251"/>
-      <c r="AY7" s="251"/>
-      <c r="AZ7" s="252"/>
-      <c r="BA7" s="257" t="s">
+      <c r="AW7" s="240"/>
+      <c r="AX7" s="240"/>
+      <c r="AY7" s="240"/>
+      <c r="AZ7" s="241"/>
+      <c r="BA7" s="270" t="s">
         <v>24</v>
       </c>
-      <c r="BB7" s="251"/>
-      <c r="BC7" s="251"/>
-      <c r="BD7" s="251"/>
-      <c r="BE7" s="252"/>
-      <c r="BF7" s="258" t="s">
+      <c r="BB7" s="240"/>
+      <c r="BC7" s="240"/>
+      <c r="BD7" s="240"/>
+      <c r="BE7" s="241"/>
+      <c r="BF7" s="271" t="s">
         <v>25</v>
       </c>
-      <c r="BG7" s="251"/>
-      <c r="BH7" s="251"/>
-      <c r="BI7" s="251"/>
-      <c r="BJ7" s="252"/>
-      <c r="BK7" s="270" t="s">
+      <c r="BG7" s="240"/>
+      <c r="BH7" s="240"/>
+      <c r="BI7" s="240"/>
+      <c r="BJ7" s="241"/>
+      <c r="BK7" s="272" t="s">
         <v>26</v>
       </c>
-      <c r="BL7" s="251"/>
-      <c r="BM7" s="251"/>
-      <c r="BN7" s="251"/>
-      <c r="BO7" s="252"/>
-      <c r="BP7" s="270" t="s">
+      <c r="BL7" s="240"/>
+      <c r="BM7" s="240"/>
+      <c r="BN7" s="240"/>
+      <c r="BO7" s="241"/>
+      <c r="BP7" s="272" t="s">
         <v>27</v>
       </c>
-      <c r="BQ7" s="251"/>
-      <c r="BR7" s="251"/>
-      <c r="BS7" s="251"/>
-      <c r="BT7" s="252"/>
+      <c r="BQ7" s="240"/>
+      <c r="BR7" s="240"/>
+      <c r="BS7" s="240"/>
+      <c r="BT7" s="241"/>
       <c r="BU7" s="38"/>
       <c r="BV7" s="39"/>
     </row>
     <row r="8" spans="2:74" ht="23.1" customHeight="1" thickBot="1">
-      <c r="B8" s="261"/>
-      <c r="C8" s="269"/>
-      <c r="D8" s="265"/>
+      <c r="B8" s="243"/>
+      <c r="C8" s="252"/>
+      <c r="D8" s="247"/>
       <c r="E8" s="58" t="s">
         <v>28</v>
       </c>
@@ -25911,11 +29835,11 @@
       <c r="G8" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="263"/>
-      <c r="I8" s="252"/>
-      <c r="J8" s="247"/>
-      <c r="K8" s="247"/>
-      <c r="L8" s="249"/>
+      <c r="H8" s="245"/>
+      <c r="I8" s="241"/>
+      <c r="J8" s="250"/>
+      <c r="K8" s="250"/>
+      <c r="L8" s="264"/>
       <c r="M8" s="61" t="s">
         <v>31</v>
       </c>
@@ -29435,6 +33359,13 @@
     <row r="42" spans="2:74" ht="216.95" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="BP7:BT7"/>
+    <mergeCell ref="AL7:AP7"/>
+    <mergeCell ref="AQ7:AU7"/>
+    <mergeCell ref="AV7:AZ7"/>
+    <mergeCell ref="BA7:BE7"/>
+    <mergeCell ref="BF7:BJ7"/>
+    <mergeCell ref="BK7:BO7"/>
     <mergeCell ref="AG7:AK7"/>
     <mergeCell ref="K2:K6"/>
     <mergeCell ref="B7:B8"/>
@@ -29450,13 +33381,6 @@
     <mergeCell ref="R7:V7"/>
     <mergeCell ref="W7:AA7"/>
     <mergeCell ref="AB7:AF7"/>
-    <mergeCell ref="BP7:BT7"/>
-    <mergeCell ref="AL7:AP7"/>
-    <mergeCell ref="AQ7:AU7"/>
-    <mergeCell ref="AV7:AZ7"/>
-    <mergeCell ref="BA7:BE7"/>
-    <mergeCell ref="BF7:BJ7"/>
-    <mergeCell ref="BK7:BO7"/>
   </mergeCells>
   <conditionalFormatting sqref="L9:L33">
     <cfRule type="dataBar" priority="1">
@@ -29473,7 +33397,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
@@ -30203,7 +34127,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3" tint="0.79998168889431442"/>

--- a/Scrum-Project-Management.xlsx
+++ b/Scrum-Project-Management.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\IDEA-PROYECTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA5EA38-1FF2-4922-B283-80E448E7C4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2DD5F8-A332-472D-B51C-4E33F356CE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 1" sheetId="1" r:id="rId1"/>
@@ -18,19 +18,20 @@
     <sheet name="Sprint 3" sheetId="8" r:id="rId3"/>
     <sheet name="Sprint 4" sheetId="9" r:id="rId4"/>
     <sheet name="Sprint 5" sheetId="10" r:id="rId5"/>
-    <sheet name="Post-It" sheetId="6" r:id="rId6"/>
-    <sheet name="a de Gantt en blanco y burndown" sheetId="2" r:id="rId7"/>
-    <sheet name="Backlog de lanzamientos" sheetId="3" r:id="rId8"/>
-    <sheet name="Historias de usuario o tareas" sheetId="4" r:id="rId9"/>
+    <sheet name="RUTA CRITICA" sheetId="11" r:id="rId6"/>
+    <sheet name="Post-It" sheetId="6" r:id="rId7"/>
+    <sheet name="a de Gantt en blanco y burndown" sheetId="2" r:id="rId8"/>
+    <sheet name="Backlog de lanzamientos" sheetId="3" r:id="rId9"/>
+    <sheet name="Historias de usuario o tareas" sheetId="4" r:id="rId10"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId10"/>
     <externalReference r:id="rId11"/>
+    <externalReference r:id="rId12"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'a de Gantt en blanco y burndown'!$B$1:$BV$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Backlog de lanzamientos'!$B$1:$J$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Historias de usuario o tareas'!$B$1:$E$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'a de Gantt en blanco y burndown'!$B$1:$BV$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Backlog de lanzamientos'!$B$1:$J$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Historias de usuario o tareas'!$B$1:$E$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Sprint 1'!$B$1:$BV$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Sprint 2'!$B$1:$BV$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Sprint 3'!$B$1:$BV$42</definedName>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="249">
   <si>
     <t>DIAGRAMA DE GANTT Y BURNDOWN</t>
   </si>
@@ -786,6 +787,24 @@
   <si>
     <t>Crear diagrama final del sistema y anexar resultados finales.</t>
   </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
 </sst>
 </file>
 
@@ -797,9 +816,16 @@
     <numFmt numFmtId="166" formatCode="0.00000"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="42">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Corbel"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Corbel"/>
       <family val="2"/>
@@ -1051,8 +1077,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aparajita"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aparajita"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1262,8 +1306,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="73">
+  <borders count="87">
     <border>
       <left/>
       <right/>
@@ -2245,230 +2295,377 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="32" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="32" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="273">
+  <cellXfs count="300">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="23" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="24" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="25" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="25" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="25" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="25" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2476,291 +2673,294 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="17" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="17" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="19" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="14" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="14" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="17" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="17" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="19" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="23" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="23" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="17" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="19" fillId="17" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="23" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="23" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2769,59 +2969,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="35" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="33" borderId="72" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="33" borderId="72" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2833,92 +3033,127 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="36" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="36" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="39" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Entrada" xfId="6" builtinId="20"/>
@@ -5197,10 +5432,10 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5289,25 +5524,25 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0" formatCode="General">
-                  <c:v>40</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>34.285714285714285</c:v>
+                  <c:v>44.571428571428569</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>28.571428571428569</c:v>
+                  <c:v>37.142857142857139</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>22.857142857142854</c:v>
+                  <c:v>29.714285714285708</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>17.142857142857139</c:v>
+                  <c:v>22.285714285714278</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.428571428571423</c:v>
+                  <c:v>14.857142857142849</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.7142857142857091</c:v>
+                  <c:v>7.4285714285714199</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5382,25 +5617,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>40</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>34</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>24</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5475,22 +5710,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>34</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>24</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -8750,7 +8985,7 @@
       <c r="H3" s="40"/>
       <c r="I3" s="40"/>
       <c r="J3" s="41"/>
-      <c r="K3" s="259" t="s">
+      <c r="K3" s="245" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="42" t="s">
@@ -8829,7 +9064,7 @@
       <c r="H4" s="40"/>
       <c r="I4" s="40"/>
       <c r="J4" s="41"/>
-      <c r="K4" s="260"/>
+      <c r="K4" s="246"/>
       <c r="L4" s="47" t="s">
         <v>3</v>
       </c>
@@ -8906,7 +9141,7 @@
       <c r="H5" s="37"/>
       <c r="I5" s="36"/>
       <c r="J5" s="37"/>
-      <c r="K5" s="260"/>
+      <c r="K5" s="246"/>
       <c r="L5" s="52" t="s">
         <v>4</v>
       </c>
@@ -8983,7 +9218,7 @@
       <c r="H6" s="37"/>
       <c r="I6" s="36"/>
       <c r="J6" s="37"/>
-      <c r="K6" s="260"/>
+      <c r="K6" s="246"/>
       <c r="L6" s="54" t="s">
         <v>5</v>
       </c>
@@ -9060,7 +9295,7 @@
       <c r="H7" s="37"/>
       <c r="I7" s="36"/>
       <c r="J7" s="37"/>
-      <c r="K7" s="261"/>
+      <c r="K7" s="247"/>
       <c r="L7" s="56" t="s">
         <v>6</v>
       </c>
@@ -9128,122 +9363,122 @@
       <c r="BV7" s="39"/>
     </row>
     <row r="8" spans="1:74" ht="23.1" customHeight="1">
-      <c r="B8" s="242" t="s">
+      <c r="B8" s="262" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="251" t="s">
+      <c r="C8" s="270" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="246" t="s">
+      <c r="D8" s="266" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="256" t="s">
+      <c r="E8" s="242" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="257"/>
-      <c r="G8" s="258"/>
-      <c r="H8" s="244" t="s">
+      <c r="F8" s="243"/>
+      <c r="G8" s="244"/>
+      <c r="H8" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="248" t="s">
+      <c r="I8" s="268" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="249" t="s">
+      <c r="J8" s="269" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="262" t="s">
+      <c r="K8" s="248" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="263" t="s">
+      <c r="L8" s="250" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="265" t="s">
+      <c r="M8" s="252" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="240"/>
-      <c r="O8" s="240"/>
-      <c r="P8" s="240"/>
-      <c r="Q8" s="241"/>
-      <c r="R8" s="266" t="s">
+      <c r="N8" s="253"/>
+      <c r="O8" s="253"/>
+      <c r="P8" s="253"/>
+      <c r="Q8" s="254"/>
+      <c r="R8" s="255" t="s">
         <v>17</v>
       </c>
-      <c r="S8" s="240"/>
-      <c r="T8" s="240"/>
-      <c r="U8" s="240"/>
-      <c r="V8" s="241"/>
-      <c r="W8" s="266" t="s">
+      <c r="S8" s="253"/>
+      <c r="T8" s="253"/>
+      <c r="U8" s="253"/>
+      <c r="V8" s="254"/>
+      <c r="W8" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="X8" s="240"/>
-      <c r="Y8" s="240"/>
-      <c r="Z8" s="240"/>
-      <c r="AA8" s="241"/>
-      <c r="AB8" s="268" t="s">
+      <c r="X8" s="253"/>
+      <c r="Y8" s="253"/>
+      <c r="Z8" s="253"/>
+      <c r="AA8" s="254"/>
+      <c r="AB8" s="257" t="s">
         <v>19</v>
       </c>
-      <c r="AC8" s="240"/>
-      <c r="AD8" s="240"/>
-      <c r="AE8" s="240"/>
-      <c r="AF8" s="241"/>
-      <c r="AG8" s="269" t="s">
+      <c r="AC8" s="253"/>
+      <c r="AD8" s="253"/>
+      <c r="AE8" s="253"/>
+      <c r="AF8" s="254"/>
+      <c r="AG8" s="258" t="s">
         <v>20</v>
       </c>
-      <c r="AH8" s="240"/>
-      <c r="AI8" s="240"/>
-      <c r="AJ8" s="240"/>
-      <c r="AK8" s="241"/>
-      <c r="AL8" s="269" t="s">
+      <c r="AH8" s="253"/>
+      <c r="AI8" s="253"/>
+      <c r="AJ8" s="253"/>
+      <c r="AK8" s="254"/>
+      <c r="AL8" s="258" t="s">
         <v>21</v>
       </c>
-      <c r="AM8" s="240"/>
-      <c r="AN8" s="240"/>
-      <c r="AO8" s="240"/>
-      <c r="AP8" s="241"/>
-      <c r="AQ8" s="267" t="s">
+      <c r="AM8" s="253"/>
+      <c r="AN8" s="253"/>
+      <c r="AO8" s="253"/>
+      <c r="AP8" s="254"/>
+      <c r="AQ8" s="256" t="s">
         <v>22</v>
       </c>
-      <c r="AR8" s="240"/>
-      <c r="AS8" s="240"/>
-      <c r="AT8" s="240"/>
-      <c r="AU8" s="241"/>
-      <c r="AV8" s="270" t="s">
+      <c r="AR8" s="253"/>
+      <c r="AS8" s="253"/>
+      <c r="AT8" s="253"/>
+      <c r="AU8" s="254"/>
+      <c r="AV8" s="259" t="s">
         <v>23</v>
       </c>
-      <c r="AW8" s="240"/>
-      <c r="AX8" s="240"/>
-      <c r="AY8" s="240"/>
-      <c r="AZ8" s="241"/>
-      <c r="BA8" s="270" t="s">
+      <c r="AW8" s="253"/>
+      <c r="AX8" s="253"/>
+      <c r="AY8" s="253"/>
+      <c r="AZ8" s="254"/>
+      <c r="BA8" s="259" t="s">
         <v>24</v>
       </c>
-      <c r="BB8" s="240"/>
-      <c r="BC8" s="240"/>
-      <c r="BD8" s="240"/>
-      <c r="BE8" s="241"/>
-      <c r="BF8" s="271" t="s">
+      <c r="BB8" s="253"/>
+      <c r="BC8" s="253"/>
+      <c r="BD8" s="253"/>
+      <c r="BE8" s="254"/>
+      <c r="BF8" s="260" t="s">
         <v>25</v>
       </c>
-      <c r="BG8" s="240"/>
-      <c r="BH8" s="240"/>
-      <c r="BI8" s="240"/>
-      <c r="BJ8" s="241"/>
-      <c r="BK8" s="239"/>
-      <c r="BL8" s="240"/>
-      <c r="BM8" s="240"/>
-      <c r="BN8" s="240"/>
-      <c r="BO8" s="241"/>
-      <c r="BP8" s="239"/>
-      <c r="BQ8" s="240"/>
-      <c r="BR8" s="240"/>
-      <c r="BS8" s="240"/>
-      <c r="BT8" s="241"/>
+      <c r="BG8" s="253"/>
+      <c r="BH8" s="253"/>
+      <c r="BI8" s="253"/>
+      <c r="BJ8" s="254"/>
+      <c r="BK8" s="261"/>
+      <c r="BL8" s="253"/>
+      <c r="BM8" s="253"/>
+      <c r="BN8" s="253"/>
+      <c r="BO8" s="254"/>
+      <c r="BP8" s="261"/>
+      <c r="BQ8" s="253"/>
+      <c r="BR8" s="253"/>
+      <c r="BS8" s="253"/>
+      <c r="BT8" s="254"/>
       <c r="BU8" s="38"/>
       <c r="BV8" s="39"/>
     </row>
     <row r="9" spans="1:74" ht="23.1" customHeight="1" thickBot="1">
-      <c r="B9" s="243"/>
-      <c r="C9" s="252"/>
-      <c r="D9" s="247"/>
+      <c r="B9" s="263"/>
+      <c r="C9" s="271"/>
+      <c r="D9" s="267"/>
       <c r="E9" s="58" t="s">
         <v>28</v>
       </c>
@@ -9253,11 +9488,11 @@
       <c r="G9" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="245"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="250"/>
-      <c r="K9" s="250"/>
-      <c r="L9" s="264"/>
+      <c r="H9" s="265"/>
+      <c r="I9" s="254"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="251"/>
       <c r="M9" s="61" t="s">
         <v>31</v>
       </c>
@@ -12798,82 +13033,89 @@
     <row r="47" spans="2:74" ht="381.95" customHeight="1"/>
     <row r="48" spans="2:74" ht="216.95" customHeight="1"/>
     <row r="50" spans="2:74" ht="50.1" customHeight="1">
-      <c r="B50" s="253"/>
-      <c r="C50" s="254"/>
-      <c r="D50" s="254"/>
-      <c r="E50" s="254"/>
-      <c r="F50" s="254"/>
-      <c r="G50" s="254"/>
-      <c r="H50" s="254"/>
-      <c r="I50" s="254"/>
-      <c r="J50" s="254"/>
-      <c r="K50" s="254"/>
-      <c r="L50" s="254"/>
-      <c r="M50" s="254"/>
-      <c r="N50" s="254"/>
-      <c r="O50" s="254"/>
-      <c r="P50" s="254"/>
-      <c r="Q50" s="254"/>
-      <c r="R50" s="254"/>
-      <c r="S50" s="254"/>
-      <c r="T50" s="254"/>
-      <c r="U50" s="254"/>
-      <c r="V50" s="254"/>
-      <c r="W50" s="254"/>
-      <c r="X50" s="254"/>
-      <c r="Y50" s="254"/>
-      <c r="Z50" s="254"/>
-      <c r="AA50" s="254"/>
-      <c r="AB50" s="254"/>
-      <c r="AC50" s="254"/>
-      <c r="AD50" s="254"/>
-      <c r="AE50" s="254"/>
-      <c r="AF50" s="254"/>
-      <c r="AG50" s="254"/>
-      <c r="AH50" s="254"/>
-      <c r="AI50" s="254"/>
-      <c r="AJ50" s="254"/>
-      <c r="AK50" s="254"/>
-      <c r="AL50" s="254"/>
-      <c r="AM50" s="254"/>
-      <c r="AN50" s="254"/>
-      <c r="AO50" s="254"/>
-      <c r="AP50" s="254"/>
-      <c r="AQ50" s="254"/>
-      <c r="AR50" s="254"/>
-      <c r="AS50" s="254"/>
-      <c r="AT50" s="254"/>
-      <c r="AU50" s="254"/>
-      <c r="AV50" s="254"/>
-      <c r="AW50" s="254"/>
-      <c r="AX50" s="254"/>
-      <c r="AY50" s="254"/>
-      <c r="AZ50" s="254"/>
-      <c r="BA50" s="254"/>
-      <c r="BB50" s="254"/>
-      <c r="BC50" s="254"/>
-      <c r="BD50" s="254"/>
-      <c r="BE50" s="254"/>
-      <c r="BF50" s="254"/>
-      <c r="BG50" s="254"/>
-      <c r="BH50" s="254"/>
-      <c r="BI50" s="254"/>
-      <c r="BJ50" s="254"/>
-      <c r="BK50" s="254"/>
-      <c r="BL50" s="254"/>
-      <c r="BM50" s="254"/>
-      <c r="BN50" s="254"/>
-      <c r="BO50" s="254"/>
-      <c r="BP50" s="254"/>
-      <c r="BQ50" s="254"/>
-      <c r="BR50" s="254"/>
-      <c r="BS50" s="254"/>
-      <c r="BT50" s="254"/>
-      <c r="BU50" s="254"/>
-      <c r="BV50" s="255"/>
+      <c r="B50" s="239"/>
+      <c r="C50" s="240"/>
+      <c r="D50" s="240"/>
+      <c r="E50" s="240"/>
+      <c r="F50" s="240"/>
+      <c r="G50" s="240"/>
+      <c r="H50" s="240"/>
+      <c r="I50" s="240"/>
+      <c r="J50" s="240"/>
+      <c r="K50" s="240"/>
+      <c r="L50" s="240"/>
+      <c r="M50" s="240"/>
+      <c r="N50" s="240"/>
+      <c r="O50" s="240"/>
+      <c r="P50" s="240"/>
+      <c r="Q50" s="240"/>
+      <c r="R50" s="240"/>
+      <c r="S50" s="240"/>
+      <c r="T50" s="240"/>
+      <c r="U50" s="240"/>
+      <c r="V50" s="240"/>
+      <c r="W50" s="240"/>
+      <c r="X50" s="240"/>
+      <c r="Y50" s="240"/>
+      <c r="Z50" s="240"/>
+      <c r="AA50" s="240"/>
+      <c r="AB50" s="240"/>
+      <c r="AC50" s="240"/>
+      <c r="AD50" s="240"/>
+      <c r="AE50" s="240"/>
+      <c r="AF50" s="240"/>
+      <c r="AG50" s="240"/>
+      <c r="AH50" s="240"/>
+      <c r="AI50" s="240"/>
+      <c r="AJ50" s="240"/>
+      <c r="AK50" s="240"/>
+      <c r="AL50" s="240"/>
+      <c r="AM50" s="240"/>
+      <c r="AN50" s="240"/>
+      <c r="AO50" s="240"/>
+      <c r="AP50" s="240"/>
+      <c r="AQ50" s="240"/>
+      <c r="AR50" s="240"/>
+      <c r="AS50" s="240"/>
+      <c r="AT50" s="240"/>
+      <c r="AU50" s="240"/>
+      <c r="AV50" s="240"/>
+      <c r="AW50" s="240"/>
+      <c r="AX50" s="240"/>
+      <c r="AY50" s="240"/>
+      <c r="AZ50" s="240"/>
+      <c r="BA50" s="240"/>
+      <c r="BB50" s="240"/>
+      <c r="BC50" s="240"/>
+      <c r="BD50" s="240"/>
+      <c r="BE50" s="240"/>
+      <c r="BF50" s="240"/>
+      <c r="BG50" s="240"/>
+      <c r="BH50" s="240"/>
+      <c r="BI50" s="240"/>
+      <c r="BJ50" s="240"/>
+      <c r="BK50" s="240"/>
+      <c r="BL50" s="240"/>
+      <c r="BM50" s="240"/>
+      <c r="BN50" s="240"/>
+      <c r="BO50" s="240"/>
+      <c r="BP50" s="240"/>
+      <c r="BQ50" s="240"/>
+      <c r="BR50" s="240"/>
+      <c r="BS50" s="240"/>
+      <c r="BT50" s="240"/>
+      <c r="BU50" s="240"/>
+      <c r="BV50" s="241"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="BP8:BT8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="C8:C9"/>
     <mergeCell ref="B50:BV50"/>
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="K3:K7"/>
@@ -12890,15 +13132,8 @@
     <mergeCell ref="BA8:BE8"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="BK8:BO8"/>
-    <mergeCell ref="BP8:BT8"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="C8:C9"/>
   </mergeCells>
-  <phoneticPr fontId="34" type="noConversion"/>
+  <phoneticPr fontId="35" type="noConversion"/>
   <conditionalFormatting sqref="L10">
     <cfRule type="dataBar" priority="3">
       <dataBar>
@@ -13007,6 +13242,274 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <tabColor theme="3" tint="0.79998168889431442"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:F39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.125" defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="3.25" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="65.875" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="13.875" customWidth="1"/>
+    <col min="6" max="6" width="3.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="35.1" customHeight="1" thickBot="1">
+      <c r="B1" s="106" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="15"/>
+    </row>
+    <row r="2" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B2" s="128" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="128" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="129" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="130" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B3" s="100"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="104"/>
+    </row>
+    <row r="4" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B4" s="100"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="104"/>
+    </row>
+    <row r="5" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="104"/>
+    </row>
+    <row r="6" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="104"/>
+    </row>
+    <row r="7" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="101"/>
+      <c r="E7" s="104"/>
+    </row>
+    <row r="8" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B8" s="100"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="104"/>
+    </row>
+    <row r="9" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B9" s="100"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="104"/>
+    </row>
+    <row r="10" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B10" s="100"/>
+      <c r="C10" s="100"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="104"/>
+    </row>
+    <row r="11" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="100"/>
+      <c r="C11" s="100"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="104"/>
+    </row>
+    <row r="12" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="100"/>
+      <c r="C12" s="100"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="104"/>
+    </row>
+    <row r="13" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="100"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="101"/>
+      <c r="E13" s="104"/>
+    </row>
+    <row r="14" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B14" s="100"/>
+      <c r="C14" s="100"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="104"/>
+    </row>
+    <row r="15" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B15" s="100"/>
+      <c r="C15" s="100"/>
+      <c r="D15" s="101"/>
+      <c r="E15" s="104"/>
+    </row>
+    <row r="16" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B16" s="100"/>
+      <c r="C16" s="100"/>
+      <c r="D16" s="101"/>
+      <c r="E16" s="104"/>
+    </row>
+    <row r="17" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B17" s="100"/>
+      <c r="C17" s="100"/>
+      <c r="D17" s="101"/>
+      <c r="E17" s="104"/>
+    </row>
+    <row r="18" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B18" s="100"/>
+      <c r="C18" s="100"/>
+      <c r="D18" s="101"/>
+      <c r="E18" s="104"/>
+    </row>
+    <row r="19" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B19" s="100"/>
+      <c r="C19" s="100"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="104"/>
+    </row>
+    <row r="20" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B20" s="100"/>
+      <c r="C20" s="100"/>
+      <c r="D20" s="101"/>
+      <c r="E20" s="104"/>
+    </row>
+    <row r="21" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B21" s="100"/>
+      <c r="C21" s="100"/>
+      <c r="D21" s="101"/>
+      <c r="E21" s="104"/>
+    </row>
+    <row r="22" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B22" s="100"/>
+      <c r="C22" s="100"/>
+      <c r="D22" s="101"/>
+      <c r="E22" s="104"/>
+    </row>
+    <row r="23" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B23" s="100"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="101"/>
+      <c r="E23" s="104"/>
+    </row>
+    <row r="24" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B24" s="100"/>
+      <c r="C24" s="100"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="104"/>
+    </row>
+    <row r="25" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B25" s="100"/>
+      <c r="C25" s="100"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="104"/>
+    </row>
+    <row r="26" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B26" s="100"/>
+      <c r="C26" s="100"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="104"/>
+    </row>
+    <row r="27" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B27" s="100"/>
+      <c r="C27" s="100"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="104"/>
+    </row>
+    <row r="28" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B28" s="100"/>
+      <c r="C28" s="100"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="104"/>
+    </row>
+    <row r="29" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B29" s="100"/>
+      <c r="C29" s="100"/>
+      <c r="D29" s="101"/>
+      <c r="E29" s="104"/>
+    </row>
+    <row r="30" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B30" s="100"/>
+      <c r="C30" s="100"/>
+      <c r="D30" s="101"/>
+      <c r="E30" s="104"/>
+    </row>
+    <row r="31" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B31" s="100"/>
+      <c r="C31" s="100"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="104"/>
+    </row>
+    <row r="32" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B32" s="100"/>
+      <c r="C32" s="100"/>
+      <c r="D32" s="101"/>
+      <c r="E32" s="104"/>
+    </row>
+    <row r="33" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B33" s="100"/>
+      <c r="C33" s="100"/>
+      <c r="D33" s="101"/>
+      <c r="E33" s="104"/>
+    </row>
+    <row r="34" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B34" s="100"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="101"/>
+      <c r="E34" s="104"/>
+    </row>
+    <row r="35" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B35" s="100"/>
+      <c r="C35" s="100"/>
+      <c r="D35" s="101"/>
+      <c r="E35" s="104"/>
+    </row>
+    <row r="36" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B36" s="100"/>
+      <c r="C36" s="100"/>
+      <c r="D36" s="101"/>
+      <c r="E36" s="104"/>
+    </row>
+    <row r="37" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B37" s="100"/>
+      <c r="C37" s="100"/>
+      <c r="D37" s="101"/>
+      <c r="E37" s="104"/>
+    </row>
+    <row r="38" spans="2:5" ht="20.100000000000001" customHeight="1">
+      <c r="B38" s="100"/>
+      <c r="C38" s="100"/>
+      <c r="D38" s="101"/>
+      <c r="E38" s="104"/>
+    </row>
+    <row r="39" spans="2:5" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="B39" s="102"/>
+      <c r="C39" s="102"/>
+      <c r="D39" s="103"/>
+      <c r="E39" s="105"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0" footer="0"/>
+  <pageSetup scale="97" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1791EA0A-735B-4159-80FB-DA2EA9EA0655}">
   <sheetPr>
@@ -13136,7 +13639,7 @@
       <c r="H3" s="40"/>
       <c r="I3" s="40"/>
       <c r="J3" s="41"/>
-      <c r="K3" s="259" t="s">
+      <c r="K3" s="245" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="42" t="s">
@@ -13215,7 +13718,7 @@
       <c r="H4" s="40"/>
       <c r="I4" s="40"/>
       <c r="J4" s="41"/>
-      <c r="K4" s="260"/>
+      <c r="K4" s="246"/>
       <c r="L4" s="47" t="s">
         <v>3</v>
       </c>
@@ -13292,7 +13795,7 @@
       <c r="H5" s="37"/>
       <c r="I5" s="36"/>
       <c r="J5" s="37"/>
-      <c r="K5" s="260"/>
+      <c r="K5" s="246"/>
       <c r="L5" s="52" t="s">
         <v>4</v>
       </c>
@@ -13369,7 +13872,7 @@
       <c r="H6" s="37"/>
       <c r="I6" s="36"/>
       <c r="J6" s="37"/>
-      <c r="K6" s="260"/>
+      <c r="K6" s="246"/>
       <c r="L6" s="54" t="s">
         <v>5</v>
       </c>
@@ -13446,7 +13949,7 @@
       <c r="H7" s="37"/>
       <c r="I7" s="36"/>
       <c r="J7" s="37"/>
-      <c r="K7" s="261"/>
+      <c r="K7" s="247"/>
       <c r="L7" s="56" t="s">
         <v>6</v>
       </c>
@@ -13514,122 +14017,122 @@
       <c r="BV7" s="39"/>
     </row>
     <row r="8" spans="1:74" ht="23.1" customHeight="1" thickBot="1">
-      <c r="B8" s="242" t="s">
+      <c r="B8" s="262" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="251" t="s">
+      <c r="C8" s="270" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="246" t="s">
+      <c r="D8" s="266" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="256" t="s">
+      <c r="E8" s="242" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="257"/>
-      <c r="G8" s="258"/>
-      <c r="H8" s="244" t="s">
+      <c r="F8" s="243"/>
+      <c r="G8" s="244"/>
+      <c r="H8" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="248" t="s">
+      <c r="I8" s="268" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="249" t="s">
+      <c r="J8" s="269" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="262" t="s">
+      <c r="K8" s="248" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="263" t="s">
+      <c r="L8" s="250" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="265" t="s">
+      <c r="M8" s="252" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="240"/>
-      <c r="O8" s="240"/>
-      <c r="P8" s="240"/>
-      <c r="Q8" s="241"/>
-      <c r="R8" s="266" t="s">
+      <c r="N8" s="253"/>
+      <c r="O8" s="253"/>
+      <c r="P8" s="253"/>
+      <c r="Q8" s="254"/>
+      <c r="R8" s="255" t="s">
         <v>17</v>
       </c>
-      <c r="S8" s="240"/>
-      <c r="T8" s="240"/>
-      <c r="U8" s="240"/>
-      <c r="V8" s="241"/>
-      <c r="W8" s="266" t="s">
+      <c r="S8" s="253"/>
+      <c r="T8" s="253"/>
+      <c r="U8" s="253"/>
+      <c r="V8" s="254"/>
+      <c r="W8" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="X8" s="240"/>
-      <c r="Y8" s="240"/>
-      <c r="Z8" s="240"/>
-      <c r="AA8" s="241"/>
-      <c r="AB8" s="268" t="s">
+      <c r="X8" s="253"/>
+      <c r="Y8" s="253"/>
+      <c r="Z8" s="253"/>
+      <c r="AA8" s="254"/>
+      <c r="AB8" s="257" t="s">
         <v>19</v>
       </c>
-      <c r="AC8" s="240"/>
-      <c r="AD8" s="240"/>
-      <c r="AE8" s="240"/>
-      <c r="AF8" s="241"/>
-      <c r="AG8" s="269" t="s">
+      <c r="AC8" s="253"/>
+      <c r="AD8" s="253"/>
+      <c r="AE8" s="253"/>
+      <c r="AF8" s="254"/>
+      <c r="AG8" s="258" t="s">
         <v>20</v>
       </c>
-      <c r="AH8" s="240"/>
-      <c r="AI8" s="240"/>
-      <c r="AJ8" s="240"/>
-      <c r="AK8" s="241"/>
-      <c r="AL8" s="269" t="s">
+      <c r="AH8" s="253"/>
+      <c r="AI8" s="253"/>
+      <c r="AJ8" s="253"/>
+      <c r="AK8" s="254"/>
+      <c r="AL8" s="258" t="s">
         <v>21</v>
       </c>
-      <c r="AM8" s="240"/>
-      <c r="AN8" s="240"/>
-      <c r="AO8" s="240"/>
-      <c r="AP8" s="241"/>
-      <c r="AQ8" s="267" t="s">
+      <c r="AM8" s="253"/>
+      <c r="AN8" s="253"/>
+      <c r="AO8" s="253"/>
+      <c r="AP8" s="254"/>
+      <c r="AQ8" s="256" t="s">
         <v>22</v>
       </c>
-      <c r="AR8" s="240"/>
-      <c r="AS8" s="240"/>
-      <c r="AT8" s="240"/>
-      <c r="AU8" s="241"/>
-      <c r="AV8" s="270" t="s">
+      <c r="AR8" s="253"/>
+      <c r="AS8" s="253"/>
+      <c r="AT8" s="253"/>
+      <c r="AU8" s="254"/>
+      <c r="AV8" s="259" t="s">
         <v>23</v>
       </c>
-      <c r="AW8" s="240"/>
-      <c r="AX8" s="240"/>
-      <c r="AY8" s="240"/>
-      <c r="AZ8" s="241"/>
-      <c r="BA8" s="270" t="s">
+      <c r="AW8" s="253"/>
+      <c r="AX8" s="253"/>
+      <c r="AY8" s="253"/>
+      <c r="AZ8" s="254"/>
+      <c r="BA8" s="259" t="s">
         <v>24</v>
       </c>
-      <c r="BB8" s="240"/>
-      <c r="BC8" s="240"/>
-      <c r="BD8" s="240"/>
-      <c r="BE8" s="241"/>
-      <c r="BF8" s="271" t="s">
+      <c r="BB8" s="253"/>
+      <c r="BC8" s="253"/>
+      <c r="BD8" s="253"/>
+      <c r="BE8" s="254"/>
+      <c r="BF8" s="260" t="s">
         <v>25</v>
       </c>
-      <c r="BG8" s="240"/>
-      <c r="BH8" s="240"/>
-      <c r="BI8" s="240"/>
-      <c r="BJ8" s="241"/>
-      <c r="BK8" s="239"/>
-      <c r="BL8" s="240"/>
-      <c r="BM8" s="240"/>
-      <c r="BN8" s="240"/>
-      <c r="BO8" s="241"/>
-      <c r="BP8" s="239"/>
-      <c r="BQ8" s="240"/>
-      <c r="BR8" s="240"/>
-      <c r="BS8" s="240"/>
-      <c r="BT8" s="241"/>
+      <c r="BG8" s="253"/>
+      <c r="BH8" s="253"/>
+      <c r="BI8" s="253"/>
+      <c r="BJ8" s="254"/>
+      <c r="BK8" s="261"/>
+      <c r="BL8" s="253"/>
+      <c r="BM8" s="253"/>
+      <c r="BN8" s="253"/>
+      <c r="BO8" s="254"/>
+      <c r="BP8" s="261"/>
+      <c r="BQ8" s="253"/>
+      <c r="BR8" s="253"/>
+      <c r="BS8" s="253"/>
+      <c r="BT8" s="254"/>
       <c r="BU8" s="38"/>
       <c r="BV8" s="39"/>
     </row>
     <row r="9" spans="1:74" ht="23.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B9" s="243"/>
-      <c r="C9" s="252"/>
-      <c r="D9" s="247"/>
+      <c r="B9" s="263"/>
+      <c r="C9" s="271"/>
+      <c r="D9" s="267"/>
       <c r="E9" s="58" t="s">
         <v>28</v>
       </c>
@@ -13639,11 +14142,11 @@
       <c r="G9" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="245"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="250"/>
-      <c r="K9" s="250"/>
-      <c r="L9" s="264"/>
+      <c r="H9" s="265"/>
+      <c r="I9" s="254"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="251"/>
       <c r="M9" s="61" t="s">
         <v>31</v>
       </c>
@@ -17183,82 +17686,91 @@
     <row r="47" spans="2:74" ht="381.95" customHeight="1"/>
     <row r="48" spans="2:74" ht="216.95" customHeight="1"/>
     <row r="50" spans="2:74" ht="50.1" customHeight="1">
-      <c r="B50" s="253"/>
-      <c r="C50" s="254"/>
-      <c r="D50" s="254"/>
-      <c r="E50" s="254"/>
-      <c r="F50" s="254"/>
-      <c r="G50" s="254"/>
-      <c r="H50" s="254"/>
-      <c r="I50" s="254"/>
-      <c r="J50" s="254"/>
-      <c r="K50" s="254"/>
-      <c r="L50" s="254"/>
-      <c r="M50" s="254"/>
-      <c r="N50" s="254"/>
-      <c r="O50" s="254"/>
-      <c r="P50" s="254"/>
-      <c r="Q50" s="254"/>
-      <c r="R50" s="254"/>
-      <c r="S50" s="254"/>
-      <c r="T50" s="254"/>
-      <c r="U50" s="254"/>
-      <c r="V50" s="254"/>
-      <c r="W50" s="254"/>
-      <c r="X50" s="254"/>
-      <c r="Y50" s="254"/>
-      <c r="Z50" s="254"/>
-      <c r="AA50" s="254"/>
-      <c r="AB50" s="254"/>
-      <c r="AC50" s="254"/>
-      <c r="AD50" s="254"/>
-      <c r="AE50" s="254"/>
-      <c r="AF50" s="254"/>
-      <c r="AG50" s="254"/>
-      <c r="AH50" s="254"/>
-      <c r="AI50" s="254"/>
-      <c r="AJ50" s="254"/>
-      <c r="AK50" s="254"/>
-      <c r="AL50" s="254"/>
-      <c r="AM50" s="254"/>
-      <c r="AN50" s="254"/>
-      <c r="AO50" s="254"/>
-      <c r="AP50" s="254"/>
-      <c r="AQ50" s="254"/>
-      <c r="AR50" s="254"/>
-      <c r="AS50" s="254"/>
-      <c r="AT50" s="254"/>
-      <c r="AU50" s="254"/>
-      <c r="AV50" s="254"/>
-      <c r="AW50" s="254"/>
-      <c r="AX50" s="254"/>
-      <c r="AY50" s="254"/>
-      <c r="AZ50" s="254"/>
-      <c r="BA50" s="254"/>
-      <c r="BB50" s="254"/>
-      <c r="BC50" s="254"/>
-      <c r="BD50" s="254"/>
-      <c r="BE50" s="254"/>
-      <c r="BF50" s="254"/>
-      <c r="BG50" s="254"/>
-      <c r="BH50" s="254"/>
-      <c r="BI50" s="254"/>
-      <c r="BJ50" s="254"/>
-      <c r="BK50" s="254"/>
-      <c r="BL50" s="254"/>
-      <c r="BM50" s="254"/>
-      <c r="BN50" s="254"/>
-      <c r="BO50" s="254"/>
-      <c r="BP50" s="254"/>
-      <c r="BQ50" s="254"/>
-      <c r="BR50" s="254"/>
-      <c r="BS50" s="254"/>
-      <c r="BT50" s="254"/>
-      <c r="BU50" s="254"/>
-      <c r="BV50" s="255"/>
+      <c r="B50" s="239"/>
+      <c r="C50" s="240"/>
+      <c r="D50" s="240"/>
+      <c r="E50" s="240"/>
+      <c r="F50" s="240"/>
+      <c r="G50" s="240"/>
+      <c r="H50" s="240"/>
+      <c r="I50" s="240"/>
+      <c r="J50" s="240"/>
+      <c r="K50" s="240"/>
+      <c r="L50" s="240"/>
+      <c r="M50" s="240"/>
+      <c r="N50" s="240"/>
+      <c r="O50" s="240"/>
+      <c r="P50" s="240"/>
+      <c r="Q50" s="240"/>
+      <c r="R50" s="240"/>
+      <c r="S50" s="240"/>
+      <c r="T50" s="240"/>
+      <c r="U50" s="240"/>
+      <c r="V50" s="240"/>
+      <c r="W50" s="240"/>
+      <c r="X50" s="240"/>
+      <c r="Y50" s="240"/>
+      <c r="Z50" s="240"/>
+      <c r="AA50" s="240"/>
+      <c r="AB50" s="240"/>
+      <c r="AC50" s="240"/>
+      <c r="AD50" s="240"/>
+      <c r="AE50" s="240"/>
+      <c r="AF50" s="240"/>
+      <c r="AG50" s="240"/>
+      <c r="AH50" s="240"/>
+      <c r="AI50" s="240"/>
+      <c r="AJ50" s="240"/>
+      <c r="AK50" s="240"/>
+      <c r="AL50" s="240"/>
+      <c r="AM50" s="240"/>
+      <c r="AN50" s="240"/>
+      <c r="AO50" s="240"/>
+      <c r="AP50" s="240"/>
+      <c r="AQ50" s="240"/>
+      <c r="AR50" s="240"/>
+      <c r="AS50" s="240"/>
+      <c r="AT50" s="240"/>
+      <c r="AU50" s="240"/>
+      <c r="AV50" s="240"/>
+      <c r="AW50" s="240"/>
+      <c r="AX50" s="240"/>
+      <c r="AY50" s="240"/>
+      <c r="AZ50" s="240"/>
+      <c r="BA50" s="240"/>
+      <c r="BB50" s="240"/>
+      <c r="BC50" s="240"/>
+      <c r="BD50" s="240"/>
+      <c r="BE50" s="240"/>
+      <c r="BF50" s="240"/>
+      <c r="BG50" s="240"/>
+      <c r="BH50" s="240"/>
+      <c r="BI50" s="240"/>
+      <c r="BJ50" s="240"/>
+      <c r="BK50" s="240"/>
+      <c r="BL50" s="240"/>
+      <c r="BM50" s="240"/>
+      <c r="BN50" s="240"/>
+      <c r="BO50" s="240"/>
+      <c r="BP50" s="240"/>
+      <c r="BQ50" s="240"/>
+      <c r="BR50" s="240"/>
+      <c r="BS50" s="240"/>
+      <c r="BT50" s="240"/>
+      <c r="BU50" s="240"/>
+      <c r="BV50" s="241"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="K3:K7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
     <mergeCell ref="BP8:BT8"/>
     <mergeCell ref="B50:BV50"/>
     <mergeCell ref="AL8:AP8"/>
@@ -17273,15 +17785,6 @@
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="K3:K7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
   </mergeCells>
   <conditionalFormatting sqref="L10">
     <cfRule type="dataBar" priority="3">
@@ -17520,7 +18023,7 @@
       <c r="H3" s="40"/>
       <c r="I3" s="40"/>
       <c r="J3" s="41"/>
-      <c r="K3" s="259" t="s">
+      <c r="K3" s="245" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="42" t="s">
@@ -17599,7 +18102,7 @@
       <c r="H4" s="40"/>
       <c r="I4" s="40"/>
       <c r="J4" s="41"/>
-      <c r="K4" s="260"/>
+      <c r="K4" s="246"/>
       <c r="L4" s="47" t="s">
         <v>3</v>
       </c>
@@ -17676,7 +18179,7 @@
       <c r="H5" s="37"/>
       <c r="I5" s="36"/>
       <c r="J5" s="37"/>
-      <c r="K5" s="260"/>
+      <c r="K5" s="246"/>
       <c r="L5" s="52" t="s">
         <v>4</v>
       </c>
@@ -17753,7 +18256,7 @@
       <c r="H6" s="37"/>
       <c r="I6" s="36"/>
       <c r="J6" s="37"/>
-      <c r="K6" s="260"/>
+      <c r="K6" s="246"/>
       <c r="L6" s="54" t="s">
         <v>5</v>
       </c>
@@ -17830,7 +18333,7 @@
       <c r="H7" s="37"/>
       <c r="I7" s="36"/>
       <c r="J7" s="37"/>
-      <c r="K7" s="261"/>
+      <c r="K7" s="247"/>
       <c r="L7" s="56" t="s">
         <v>6</v>
       </c>
@@ -17898,122 +18401,122 @@
       <c r="BV7" s="39"/>
     </row>
     <row r="8" spans="1:74" ht="23.1" customHeight="1" thickBot="1">
-      <c r="B8" s="242" t="s">
+      <c r="B8" s="262" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="251" t="s">
+      <c r="C8" s="270" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="246" t="s">
+      <c r="D8" s="266" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="256" t="s">
+      <c r="E8" s="242" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="257"/>
-      <c r="G8" s="258"/>
-      <c r="H8" s="244" t="s">
+      <c r="F8" s="243"/>
+      <c r="G8" s="244"/>
+      <c r="H8" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="248" t="s">
+      <c r="I8" s="268" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="249" t="s">
+      <c r="J8" s="269" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="262" t="s">
+      <c r="K8" s="248" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="263" t="s">
+      <c r="L8" s="250" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="265" t="s">
+      <c r="M8" s="252" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="240"/>
-      <c r="O8" s="240"/>
-      <c r="P8" s="240"/>
-      <c r="Q8" s="241"/>
-      <c r="R8" s="266" t="s">
+      <c r="N8" s="253"/>
+      <c r="O8" s="253"/>
+      <c r="P8" s="253"/>
+      <c r="Q8" s="254"/>
+      <c r="R8" s="255" t="s">
         <v>17</v>
       </c>
-      <c r="S8" s="240"/>
-      <c r="T8" s="240"/>
-      <c r="U8" s="240"/>
-      <c r="V8" s="241"/>
-      <c r="W8" s="266" t="s">
+      <c r="S8" s="253"/>
+      <c r="T8" s="253"/>
+      <c r="U8" s="253"/>
+      <c r="V8" s="254"/>
+      <c r="W8" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="X8" s="240"/>
-      <c r="Y8" s="240"/>
-      <c r="Z8" s="240"/>
-      <c r="AA8" s="241"/>
-      <c r="AB8" s="268" t="s">
+      <c r="X8" s="253"/>
+      <c r="Y8" s="253"/>
+      <c r="Z8" s="253"/>
+      <c r="AA8" s="254"/>
+      <c r="AB8" s="257" t="s">
         <v>19</v>
       </c>
-      <c r="AC8" s="240"/>
-      <c r="AD8" s="240"/>
-      <c r="AE8" s="240"/>
-      <c r="AF8" s="241"/>
-      <c r="AG8" s="269" t="s">
+      <c r="AC8" s="253"/>
+      <c r="AD8" s="253"/>
+      <c r="AE8" s="253"/>
+      <c r="AF8" s="254"/>
+      <c r="AG8" s="258" t="s">
         <v>20</v>
       </c>
-      <c r="AH8" s="240"/>
-      <c r="AI8" s="240"/>
-      <c r="AJ8" s="240"/>
-      <c r="AK8" s="241"/>
-      <c r="AL8" s="269" t="s">
+      <c r="AH8" s="253"/>
+      <c r="AI8" s="253"/>
+      <c r="AJ8" s="253"/>
+      <c r="AK8" s="254"/>
+      <c r="AL8" s="258" t="s">
         <v>21</v>
       </c>
-      <c r="AM8" s="240"/>
-      <c r="AN8" s="240"/>
-      <c r="AO8" s="240"/>
-      <c r="AP8" s="241"/>
-      <c r="AQ8" s="267" t="s">
+      <c r="AM8" s="253"/>
+      <c r="AN8" s="253"/>
+      <c r="AO8" s="253"/>
+      <c r="AP8" s="254"/>
+      <c r="AQ8" s="256" t="s">
         <v>22</v>
       </c>
-      <c r="AR8" s="240"/>
-      <c r="AS8" s="240"/>
-      <c r="AT8" s="240"/>
-      <c r="AU8" s="241"/>
-      <c r="AV8" s="270" t="s">
+      <c r="AR8" s="253"/>
+      <c r="AS8" s="253"/>
+      <c r="AT8" s="253"/>
+      <c r="AU8" s="254"/>
+      <c r="AV8" s="259" t="s">
         <v>23</v>
       </c>
-      <c r="AW8" s="240"/>
-      <c r="AX8" s="240"/>
-      <c r="AY8" s="240"/>
-      <c r="AZ8" s="241"/>
-      <c r="BA8" s="270" t="s">
+      <c r="AW8" s="253"/>
+      <c r="AX8" s="253"/>
+      <c r="AY8" s="253"/>
+      <c r="AZ8" s="254"/>
+      <c r="BA8" s="259" t="s">
         <v>24</v>
       </c>
-      <c r="BB8" s="240"/>
-      <c r="BC8" s="240"/>
-      <c r="BD8" s="240"/>
-      <c r="BE8" s="241"/>
-      <c r="BF8" s="271" t="s">
+      <c r="BB8" s="253"/>
+      <c r="BC8" s="253"/>
+      <c r="BD8" s="253"/>
+      <c r="BE8" s="254"/>
+      <c r="BF8" s="260" t="s">
         <v>25</v>
       </c>
-      <c r="BG8" s="240"/>
-      <c r="BH8" s="240"/>
-      <c r="BI8" s="240"/>
-      <c r="BJ8" s="241"/>
-      <c r="BK8" s="239"/>
-      <c r="BL8" s="240"/>
-      <c r="BM8" s="240"/>
-      <c r="BN8" s="240"/>
-      <c r="BO8" s="241"/>
-      <c r="BP8" s="239"/>
-      <c r="BQ8" s="240"/>
-      <c r="BR8" s="240"/>
-      <c r="BS8" s="240"/>
-      <c r="BT8" s="241"/>
+      <c r="BG8" s="253"/>
+      <c r="BH8" s="253"/>
+      <c r="BI8" s="253"/>
+      <c r="BJ8" s="254"/>
+      <c r="BK8" s="261"/>
+      <c r="BL8" s="253"/>
+      <c r="BM8" s="253"/>
+      <c r="BN8" s="253"/>
+      <c r="BO8" s="254"/>
+      <c r="BP8" s="261"/>
+      <c r="BQ8" s="253"/>
+      <c r="BR8" s="253"/>
+      <c r="BS8" s="253"/>
+      <c r="BT8" s="254"/>
       <c r="BU8" s="38"/>
       <c r="BV8" s="39"/>
     </row>
     <row r="9" spans="1:74" ht="23.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B9" s="243"/>
-      <c r="C9" s="252"/>
-      <c r="D9" s="247"/>
+      <c r="B9" s="263"/>
+      <c r="C9" s="271"/>
+      <c r="D9" s="267"/>
       <c r="E9" s="58" t="s">
         <v>28</v>
       </c>
@@ -18023,11 +18526,11 @@
       <c r="G9" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="245"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="250"/>
-      <c r="K9" s="250"/>
-      <c r="L9" s="264"/>
+      <c r="H9" s="265"/>
+      <c r="I9" s="254"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="251"/>
       <c r="M9" s="61" t="s">
         <v>31</v>
       </c>
@@ -21022,82 +21525,91 @@
     <row r="41" spans="2:74" ht="381.95" customHeight="1"/>
     <row r="42" spans="2:74" ht="216.95" customHeight="1"/>
     <row r="44" spans="2:74" ht="50.1" customHeight="1">
-      <c r="B44" s="253"/>
-      <c r="C44" s="254"/>
-      <c r="D44" s="254"/>
-      <c r="E44" s="254"/>
-      <c r="F44" s="254"/>
-      <c r="G44" s="254"/>
-      <c r="H44" s="254"/>
-      <c r="I44" s="254"/>
-      <c r="J44" s="254"/>
-      <c r="K44" s="254"/>
-      <c r="L44" s="254"/>
-      <c r="M44" s="254"/>
-      <c r="N44" s="254"/>
-      <c r="O44" s="254"/>
-      <c r="P44" s="254"/>
-      <c r="Q44" s="254"/>
-      <c r="R44" s="254"/>
-      <c r="S44" s="254"/>
-      <c r="T44" s="254"/>
-      <c r="U44" s="254"/>
-      <c r="V44" s="254"/>
-      <c r="W44" s="254"/>
-      <c r="X44" s="254"/>
-      <c r="Y44" s="254"/>
-      <c r="Z44" s="254"/>
-      <c r="AA44" s="254"/>
-      <c r="AB44" s="254"/>
-      <c r="AC44" s="254"/>
-      <c r="AD44" s="254"/>
-      <c r="AE44" s="254"/>
-      <c r="AF44" s="254"/>
-      <c r="AG44" s="254"/>
-      <c r="AH44" s="254"/>
-      <c r="AI44" s="254"/>
-      <c r="AJ44" s="254"/>
-      <c r="AK44" s="254"/>
-      <c r="AL44" s="254"/>
-      <c r="AM44" s="254"/>
-      <c r="AN44" s="254"/>
-      <c r="AO44" s="254"/>
-      <c r="AP44" s="254"/>
-      <c r="AQ44" s="254"/>
-      <c r="AR44" s="254"/>
-      <c r="AS44" s="254"/>
-      <c r="AT44" s="254"/>
-      <c r="AU44" s="254"/>
-      <c r="AV44" s="254"/>
-      <c r="AW44" s="254"/>
-      <c r="AX44" s="254"/>
-      <c r="AY44" s="254"/>
-      <c r="AZ44" s="254"/>
-      <c r="BA44" s="254"/>
-      <c r="BB44" s="254"/>
-      <c r="BC44" s="254"/>
-      <c r="BD44" s="254"/>
-      <c r="BE44" s="254"/>
-      <c r="BF44" s="254"/>
-      <c r="BG44" s="254"/>
-      <c r="BH44" s="254"/>
-      <c r="BI44" s="254"/>
-      <c r="BJ44" s="254"/>
-      <c r="BK44" s="254"/>
-      <c r="BL44" s="254"/>
-      <c r="BM44" s="254"/>
-      <c r="BN44" s="254"/>
-      <c r="BO44" s="254"/>
-      <c r="BP44" s="254"/>
-      <c r="BQ44" s="254"/>
-      <c r="BR44" s="254"/>
-      <c r="BS44" s="254"/>
-      <c r="BT44" s="254"/>
-      <c r="BU44" s="254"/>
-      <c r="BV44" s="255"/>
+      <c r="B44" s="239"/>
+      <c r="C44" s="240"/>
+      <c r="D44" s="240"/>
+      <c r="E44" s="240"/>
+      <c r="F44" s="240"/>
+      <c r="G44" s="240"/>
+      <c r="H44" s="240"/>
+      <c r="I44" s="240"/>
+      <c r="J44" s="240"/>
+      <c r="K44" s="240"/>
+      <c r="L44" s="240"/>
+      <c r="M44" s="240"/>
+      <c r="N44" s="240"/>
+      <c r="O44" s="240"/>
+      <c r="P44" s="240"/>
+      <c r="Q44" s="240"/>
+      <c r="R44" s="240"/>
+      <c r="S44" s="240"/>
+      <c r="T44" s="240"/>
+      <c r="U44" s="240"/>
+      <c r="V44" s="240"/>
+      <c r="W44" s="240"/>
+      <c r="X44" s="240"/>
+      <c r="Y44" s="240"/>
+      <c r="Z44" s="240"/>
+      <c r="AA44" s="240"/>
+      <c r="AB44" s="240"/>
+      <c r="AC44" s="240"/>
+      <c r="AD44" s="240"/>
+      <c r="AE44" s="240"/>
+      <c r="AF44" s="240"/>
+      <c r="AG44" s="240"/>
+      <c r="AH44" s="240"/>
+      <c r="AI44" s="240"/>
+      <c r="AJ44" s="240"/>
+      <c r="AK44" s="240"/>
+      <c r="AL44" s="240"/>
+      <c r="AM44" s="240"/>
+      <c r="AN44" s="240"/>
+      <c r="AO44" s="240"/>
+      <c r="AP44" s="240"/>
+      <c r="AQ44" s="240"/>
+      <c r="AR44" s="240"/>
+      <c r="AS44" s="240"/>
+      <c r="AT44" s="240"/>
+      <c r="AU44" s="240"/>
+      <c r="AV44" s="240"/>
+      <c r="AW44" s="240"/>
+      <c r="AX44" s="240"/>
+      <c r="AY44" s="240"/>
+      <c r="AZ44" s="240"/>
+      <c r="BA44" s="240"/>
+      <c r="BB44" s="240"/>
+      <c r="BC44" s="240"/>
+      <c r="BD44" s="240"/>
+      <c r="BE44" s="240"/>
+      <c r="BF44" s="240"/>
+      <c r="BG44" s="240"/>
+      <c r="BH44" s="240"/>
+      <c r="BI44" s="240"/>
+      <c r="BJ44" s="240"/>
+      <c r="BK44" s="240"/>
+      <c r="BL44" s="240"/>
+      <c r="BM44" s="240"/>
+      <c r="BN44" s="240"/>
+      <c r="BO44" s="240"/>
+      <c r="BP44" s="240"/>
+      <c r="BQ44" s="240"/>
+      <c r="BR44" s="240"/>
+      <c r="BS44" s="240"/>
+      <c r="BT44" s="240"/>
+      <c r="BU44" s="240"/>
+      <c r="BV44" s="241"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="K3:K7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
     <mergeCell ref="BP8:BT8"/>
     <mergeCell ref="B44:BV44"/>
     <mergeCell ref="AL8:AP8"/>
@@ -21112,15 +21624,6 @@
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="K3:K7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
   </mergeCells>
   <conditionalFormatting sqref="L10:L33">
     <cfRule type="dataBar" priority="3">
@@ -21350,7 +21853,7 @@
       <c r="H3" s="40"/>
       <c r="I3" s="40"/>
       <c r="J3" s="41"/>
-      <c r="K3" s="259" t="s">
+      <c r="K3" s="245" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="42" t="s">
@@ -21429,7 +21932,7 @@
       <c r="H4" s="40"/>
       <c r="I4" s="40"/>
       <c r="J4" s="41"/>
-      <c r="K4" s="260"/>
+      <c r="K4" s="246"/>
       <c r="L4" s="47" t="s">
         <v>3</v>
       </c>
@@ -21506,7 +22009,7 @@
       <c r="H5" s="37"/>
       <c r="I5" s="36"/>
       <c r="J5" s="37"/>
-      <c r="K5" s="260"/>
+      <c r="K5" s="246"/>
       <c r="L5" s="52" t="s">
         <v>4</v>
       </c>
@@ -21583,7 +22086,7 @@
       <c r="H6" s="37"/>
       <c r="I6" s="36"/>
       <c r="J6" s="37"/>
-      <c r="K6" s="260"/>
+      <c r="K6" s="246"/>
       <c r="L6" s="54" t="s">
         <v>5</v>
       </c>
@@ -21660,7 +22163,7 @@
       <c r="H7" s="37"/>
       <c r="I7" s="36"/>
       <c r="J7" s="37"/>
-      <c r="K7" s="261"/>
+      <c r="K7" s="247"/>
       <c r="L7" s="56" t="s">
         <v>6</v>
       </c>
@@ -21728,122 +22231,122 @@
       <c r="BV7" s="39"/>
     </row>
     <row r="8" spans="1:74" ht="23.1" customHeight="1" thickBot="1">
-      <c r="B8" s="242" t="s">
+      <c r="B8" s="262" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="251" t="s">
+      <c r="C8" s="270" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="246" t="s">
+      <c r="D8" s="266" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="256" t="s">
+      <c r="E8" s="242" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="257"/>
-      <c r="G8" s="258"/>
-      <c r="H8" s="244" t="s">
+      <c r="F8" s="243"/>
+      <c r="G8" s="244"/>
+      <c r="H8" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="248" t="s">
+      <c r="I8" s="268" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="249" t="s">
+      <c r="J8" s="269" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="262" t="s">
+      <c r="K8" s="248" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="263" t="s">
+      <c r="L8" s="250" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="265" t="s">
+      <c r="M8" s="252" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="240"/>
-      <c r="O8" s="240"/>
-      <c r="P8" s="240"/>
-      <c r="Q8" s="241"/>
-      <c r="R8" s="266" t="s">
+      <c r="N8" s="253"/>
+      <c r="O8" s="253"/>
+      <c r="P8" s="253"/>
+      <c r="Q8" s="254"/>
+      <c r="R8" s="255" t="s">
         <v>17</v>
       </c>
-      <c r="S8" s="240"/>
-      <c r="T8" s="240"/>
-      <c r="U8" s="240"/>
-      <c r="V8" s="241"/>
-      <c r="W8" s="266" t="s">
+      <c r="S8" s="253"/>
+      <c r="T8" s="253"/>
+      <c r="U8" s="253"/>
+      <c r="V8" s="254"/>
+      <c r="W8" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="X8" s="240"/>
-      <c r="Y8" s="240"/>
-      <c r="Z8" s="240"/>
-      <c r="AA8" s="241"/>
-      <c r="AB8" s="268" t="s">
+      <c r="X8" s="253"/>
+      <c r="Y8" s="253"/>
+      <c r="Z8" s="253"/>
+      <c r="AA8" s="254"/>
+      <c r="AB8" s="257" t="s">
         <v>19</v>
       </c>
-      <c r="AC8" s="240"/>
-      <c r="AD8" s="240"/>
-      <c r="AE8" s="240"/>
-      <c r="AF8" s="241"/>
-      <c r="AG8" s="269" t="s">
+      <c r="AC8" s="253"/>
+      <c r="AD8" s="253"/>
+      <c r="AE8" s="253"/>
+      <c r="AF8" s="254"/>
+      <c r="AG8" s="258" t="s">
         <v>20</v>
       </c>
-      <c r="AH8" s="240"/>
-      <c r="AI8" s="240"/>
-      <c r="AJ8" s="240"/>
-      <c r="AK8" s="241"/>
-      <c r="AL8" s="269" t="s">
+      <c r="AH8" s="253"/>
+      <c r="AI8" s="253"/>
+      <c r="AJ8" s="253"/>
+      <c r="AK8" s="254"/>
+      <c r="AL8" s="258" t="s">
         <v>21</v>
       </c>
-      <c r="AM8" s="240"/>
-      <c r="AN8" s="240"/>
-      <c r="AO8" s="240"/>
-      <c r="AP8" s="241"/>
-      <c r="AQ8" s="267" t="s">
+      <c r="AM8" s="253"/>
+      <c r="AN8" s="253"/>
+      <c r="AO8" s="253"/>
+      <c r="AP8" s="254"/>
+      <c r="AQ8" s="256" t="s">
         <v>22</v>
       </c>
-      <c r="AR8" s="240"/>
-      <c r="AS8" s="240"/>
-      <c r="AT8" s="240"/>
-      <c r="AU8" s="241"/>
-      <c r="AV8" s="270" t="s">
+      <c r="AR8" s="253"/>
+      <c r="AS8" s="253"/>
+      <c r="AT8" s="253"/>
+      <c r="AU8" s="254"/>
+      <c r="AV8" s="259" t="s">
         <v>23</v>
       </c>
-      <c r="AW8" s="240"/>
-      <c r="AX8" s="240"/>
-      <c r="AY8" s="240"/>
-      <c r="AZ8" s="241"/>
-      <c r="BA8" s="270" t="s">
+      <c r="AW8" s="253"/>
+      <c r="AX8" s="253"/>
+      <c r="AY8" s="253"/>
+      <c r="AZ8" s="254"/>
+      <c r="BA8" s="259" t="s">
         <v>24</v>
       </c>
-      <c r="BB8" s="240"/>
-      <c r="BC8" s="240"/>
-      <c r="BD8" s="240"/>
-      <c r="BE8" s="241"/>
-      <c r="BF8" s="271" t="s">
+      <c r="BB8" s="253"/>
+      <c r="BC8" s="253"/>
+      <c r="BD8" s="253"/>
+      <c r="BE8" s="254"/>
+      <c r="BF8" s="260" t="s">
         <v>25</v>
       </c>
-      <c r="BG8" s="240"/>
-      <c r="BH8" s="240"/>
-      <c r="BI8" s="240"/>
-      <c r="BJ8" s="241"/>
-      <c r="BK8" s="239"/>
-      <c r="BL8" s="240"/>
-      <c r="BM8" s="240"/>
-      <c r="BN8" s="240"/>
-      <c r="BO8" s="241"/>
-      <c r="BP8" s="239"/>
-      <c r="BQ8" s="240"/>
-      <c r="BR8" s="240"/>
-      <c r="BS8" s="240"/>
-      <c r="BT8" s="241"/>
+      <c r="BG8" s="253"/>
+      <c r="BH8" s="253"/>
+      <c r="BI8" s="253"/>
+      <c r="BJ8" s="254"/>
+      <c r="BK8" s="261"/>
+      <c r="BL8" s="253"/>
+      <c r="BM8" s="253"/>
+      <c r="BN8" s="253"/>
+      <c r="BO8" s="254"/>
+      <c r="BP8" s="261"/>
+      <c r="BQ8" s="253"/>
+      <c r="BR8" s="253"/>
+      <c r="BS8" s="253"/>
+      <c r="BT8" s="254"/>
       <c r="BU8" s="38"/>
       <c r="BV8" s="39"/>
     </row>
     <row r="9" spans="1:74" ht="23.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B9" s="243"/>
-      <c r="C9" s="252"/>
-      <c r="D9" s="247"/>
+      <c r="B9" s="263"/>
+      <c r="C9" s="271"/>
+      <c r="D9" s="267"/>
       <c r="E9" s="58" t="s">
         <v>28</v>
       </c>
@@ -21853,11 +22356,11 @@
       <c r="G9" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="245"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="250"/>
-      <c r="K9" s="250"/>
-      <c r="L9" s="264"/>
+      <c r="H9" s="265"/>
+      <c r="I9" s="254"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="251"/>
       <c r="M9" s="61" t="s">
         <v>31</v>
       </c>
@@ -25083,12 +25586,12 @@
         <v>44</v>
       </c>
       <c r="E43" s="216">
-        <f>SUM(E11:E13,E15:E17,E19:E21,E23:E25,E27:E29,E39:E41)</f>
-        <v>40</v>
+        <f>SUM(E11:E13,E15:E17,E19:E21,E23:E25,E27:E29,E39:E41,E31:E33,E35:E37)</f>
+        <v>52</v>
       </c>
       <c r="F43" s="216">
-        <f>SUM(F11:F13,F15:F17,F19:F21,F23:F25,F27:F29,F39:F41)</f>
-        <v>40</v>
+        <f>SUM(F11:F13,F15:F17,F19:F21,F23:F25,F27:F29,F39:F41,F35:F37,F31:F33)</f>
+        <v>52</v>
       </c>
       <c r="G43" s="216">
         <f>SUM(G11:G13,G15:G17,G19:G21,G23:G25,G27:G29,G39:G41)</f>
@@ -25099,7 +25602,7 @@
       </c>
       <c r="I43" s="218">
         <f>E43/H43</f>
-        <v>5.7142857142857144</v>
+        <v>7.4285714285714288</v>
       </c>
       <c r="J43" s="38"/>
       <c r="K43" s="38"/>
@@ -25203,31 +25706,31 @@
       </c>
       <c r="M44" s="97">
         <f>E43</f>
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="N44" s="98">
         <f>M44-I43</f>
-        <v>34.285714285714285</v>
+        <v>44.571428571428569</v>
       </c>
       <c r="O44" s="98">
         <f>N44-I43</f>
-        <v>28.571428571428569</v>
+        <v>37.142857142857139</v>
       </c>
       <c r="P44" s="98">
         <f>O44-I43</f>
-        <v>22.857142857142854</v>
+        <v>29.714285714285708</v>
       </c>
       <c r="Q44" s="98">
         <f>P44-I43</f>
-        <v>17.142857142857139</v>
+        <v>22.285714285714278</v>
       </c>
       <c r="R44" s="98">
         <f>Q44-I43</f>
-        <v>11.428571428571423</v>
+        <v>14.857142857142849</v>
       </c>
       <c r="S44" s="98">
         <f>R44-I43</f>
-        <v>5.7142857142857091</v>
+        <v>7.4285714285714199</v>
       </c>
       <c r="T44" s="98"/>
       <c r="U44" s="98"/>
@@ -25303,31 +25806,31 @@
       </c>
       <c r="M45" s="97">
         <f>E43</f>
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="N45" s="97">
         <f t="shared" ref="N45:S45" si="3">M47</f>
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="O45" s="97">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="P45" s="97">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Q45" s="97">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="R45" s="97">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="S45" s="97">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T45" s="97"/>
       <c r="U45" s="97"/>
@@ -25385,7 +25888,7 @@
       <c r="BU45" s="38"/>
       <c r="BV45" s="139">
         <f>SUM(M45:BT45)</f>
-        <v>161</v>
+        <v>240</v>
       </c>
     </row>
     <row r="46" spans="2:74" ht="23.1" customHeight="1">
@@ -25420,10 +25923,10 @@
         <v>4</v>
       </c>
       <c r="R46" s="76">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="S46" s="76">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T46" s="76"/>
       <c r="U46" s="76"/>
@@ -25481,7 +25984,7 @@
       <c r="BU46" s="38"/>
       <c r="BV46" s="140">
         <f>SUM(M46:BT46)</f>
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="2:74" ht="23.1" customHeight="1">
@@ -25500,27 +26003,27 @@
       </c>
       <c r="M47" s="97">
         <f t="shared" ref="M47:S47" si="4">M45-M46</f>
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="N47" s="97">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="O47" s="97">
         <f t="shared" si="4"/>
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="P47" s="97">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Q47" s="97">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="R47" s="97">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S47" s="97">
         <f t="shared" si="4"/>
@@ -25582,7 +26085,7 @@
       <c r="BU47" s="38"/>
       <c r="BV47" s="140">
         <f>SUM(M47:BT47)</f>
-        <v>121</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="2:74" ht="19.5" customHeight="1">
@@ -25594,82 +26097,91 @@
     <row r="49" spans="2:74" ht="381.95" customHeight="1"/>
     <row r="50" spans="2:74" ht="216.95" customHeight="1"/>
     <row r="52" spans="2:74" ht="50.1" customHeight="1">
-      <c r="B52" s="253"/>
-      <c r="C52" s="254"/>
-      <c r="D52" s="254"/>
-      <c r="E52" s="254"/>
-      <c r="F52" s="254"/>
-      <c r="G52" s="254"/>
-      <c r="H52" s="254"/>
-      <c r="I52" s="254"/>
-      <c r="J52" s="254"/>
-      <c r="K52" s="254"/>
-      <c r="L52" s="254"/>
-      <c r="M52" s="254"/>
-      <c r="N52" s="254"/>
-      <c r="O52" s="254"/>
-      <c r="P52" s="254"/>
-      <c r="Q52" s="254"/>
-      <c r="R52" s="254"/>
-      <c r="S52" s="254"/>
-      <c r="T52" s="254"/>
-      <c r="U52" s="254"/>
-      <c r="V52" s="254"/>
-      <c r="W52" s="254"/>
-      <c r="X52" s="254"/>
-      <c r="Y52" s="254"/>
-      <c r="Z52" s="254"/>
-      <c r="AA52" s="254"/>
-      <c r="AB52" s="254"/>
-      <c r="AC52" s="254"/>
-      <c r="AD52" s="254"/>
-      <c r="AE52" s="254"/>
-      <c r="AF52" s="254"/>
-      <c r="AG52" s="254"/>
-      <c r="AH52" s="254"/>
-      <c r="AI52" s="254"/>
-      <c r="AJ52" s="254"/>
-      <c r="AK52" s="254"/>
-      <c r="AL52" s="254"/>
-      <c r="AM52" s="254"/>
-      <c r="AN52" s="254"/>
-      <c r="AO52" s="254"/>
-      <c r="AP52" s="254"/>
-      <c r="AQ52" s="254"/>
-      <c r="AR52" s="254"/>
-      <c r="AS52" s="254"/>
-      <c r="AT52" s="254"/>
-      <c r="AU52" s="254"/>
-      <c r="AV52" s="254"/>
-      <c r="AW52" s="254"/>
-      <c r="AX52" s="254"/>
-      <c r="AY52" s="254"/>
-      <c r="AZ52" s="254"/>
-      <c r="BA52" s="254"/>
-      <c r="BB52" s="254"/>
-      <c r="BC52" s="254"/>
-      <c r="BD52" s="254"/>
-      <c r="BE52" s="254"/>
-      <c r="BF52" s="254"/>
-      <c r="BG52" s="254"/>
-      <c r="BH52" s="254"/>
-      <c r="BI52" s="254"/>
-      <c r="BJ52" s="254"/>
-      <c r="BK52" s="254"/>
-      <c r="BL52" s="254"/>
-      <c r="BM52" s="254"/>
-      <c r="BN52" s="254"/>
-      <c r="BO52" s="254"/>
-      <c r="BP52" s="254"/>
-      <c r="BQ52" s="254"/>
-      <c r="BR52" s="254"/>
-      <c r="BS52" s="254"/>
-      <c r="BT52" s="254"/>
-      <c r="BU52" s="254"/>
-      <c r="BV52" s="255"/>
+      <c r="B52" s="239"/>
+      <c r="C52" s="240"/>
+      <c r="D52" s="240"/>
+      <c r="E52" s="240"/>
+      <c r="F52" s="240"/>
+      <c r="G52" s="240"/>
+      <c r="H52" s="240"/>
+      <c r="I52" s="240"/>
+      <c r="J52" s="240"/>
+      <c r="K52" s="240"/>
+      <c r="L52" s="240"/>
+      <c r="M52" s="240"/>
+      <c r="N52" s="240"/>
+      <c r="O52" s="240"/>
+      <c r="P52" s="240"/>
+      <c r="Q52" s="240"/>
+      <c r="R52" s="240"/>
+      <c r="S52" s="240"/>
+      <c r="T52" s="240"/>
+      <c r="U52" s="240"/>
+      <c r="V52" s="240"/>
+      <c r="W52" s="240"/>
+      <c r="X52" s="240"/>
+      <c r="Y52" s="240"/>
+      <c r="Z52" s="240"/>
+      <c r="AA52" s="240"/>
+      <c r="AB52" s="240"/>
+      <c r="AC52" s="240"/>
+      <c r="AD52" s="240"/>
+      <c r="AE52" s="240"/>
+      <c r="AF52" s="240"/>
+      <c r="AG52" s="240"/>
+      <c r="AH52" s="240"/>
+      <c r="AI52" s="240"/>
+      <c r="AJ52" s="240"/>
+      <c r="AK52" s="240"/>
+      <c r="AL52" s="240"/>
+      <c r="AM52" s="240"/>
+      <c r="AN52" s="240"/>
+      <c r="AO52" s="240"/>
+      <c r="AP52" s="240"/>
+      <c r="AQ52" s="240"/>
+      <c r="AR52" s="240"/>
+      <c r="AS52" s="240"/>
+      <c r="AT52" s="240"/>
+      <c r="AU52" s="240"/>
+      <c r="AV52" s="240"/>
+      <c r="AW52" s="240"/>
+      <c r="AX52" s="240"/>
+      <c r="AY52" s="240"/>
+      <c r="AZ52" s="240"/>
+      <c r="BA52" s="240"/>
+      <c r="BB52" s="240"/>
+      <c r="BC52" s="240"/>
+      <c r="BD52" s="240"/>
+      <c r="BE52" s="240"/>
+      <c r="BF52" s="240"/>
+      <c r="BG52" s="240"/>
+      <c r="BH52" s="240"/>
+      <c r="BI52" s="240"/>
+      <c r="BJ52" s="240"/>
+      <c r="BK52" s="240"/>
+      <c r="BL52" s="240"/>
+      <c r="BM52" s="240"/>
+      <c r="BN52" s="240"/>
+      <c r="BO52" s="240"/>
+      <c r="BP52" s="240"/>
+      <c r="BQ52" s="240"/>
+      <c r="BR52" s="240"/>
+      <c r="BS52" s="240"/>
+      <c r="BT52" s="240"/>
+      <c r="BU52" s="240"/>
+      <c r="BV52" s="241"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="K3:K7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
     <mergeCell ref="BP8:BT8"/>
     <mergeCell ref="B52:BV52"/>
     <mergeCell ref="AL8:AP8"/>
@@ -25684,17 +26196,8 @@
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="K3:K7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
   </mergeCells>
-  <phoneticPr fontId="34" type="noConversion"/>
+  <phoneticPr fontId="35" type="noConversion"/>
   <conditionalFormatting sqref="L10:L29 L31:L33 L35:L41">
     <cfRule type="dataBar" priority="11">
       <dataBar>
@@ -25979,7 +26482,7 @@
   <cols>
     <col min="1" max="1" width="3.25" style="237" customWidth="1"/>
     <col min="2" max="2" width="10.5" style="237" customWidth="1"/>
-    <col min="3" max="3" width="30.25" style="237" customWidth="1"/>
+    <col min="3" max="3" width="51.25" style="237" customWidth="1"/>
     <col min="4" max="4" width="22" style="237" customWidth="1"/>
     <col min="5" max="8" width="9" style="237" customWidth="1"/>
     <col min="9" max="10" width="10.875" style="237" customWidth="1"/>
@@ -26097,7 +26600,7 @@
       <c r="H3" s="40"/>
       <c r="I3" s="40"/>
       <c r="J3" s="41"/>
-      <c r="K3" s="259" t="s">
+      <c r="K3" s="245" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="42" t="s">
@@ -26176,7 +26679,7 @@
       <c r="H4" s="40"/>
       <c r="I4" s="40"/>
       <c r="J4" s="41"/>
-      <c r="K4" s="260"/>
+      <c r="K4" s="246"/>
       <c r="L4" s="47" t="s">
         <v>3</v>
       </c>
@@ -26253,7 +26756,7 @@
       <c r="H5" s="37"/>
       <c r="I5" s="36"/>
       <c r="J5" s="37"/>
-      <c r="K5" s="260"/>
+      <c r="K5" s="246"/>
       <c r="L5" s="52" t="s">
         <v>4</v>
       </c>
@@ -26330,7 +26833,7 @@
       <c r="H6" s="37"/>
       <c r="I6" s="36"/>
       <c r="J6" s="37"/>
-      <c r="K6" s="260"/>
+      <c r="K6" s="246"/>
       <c r="L6" s="54" t="s">
         <v>5</v>
       </c>
@@ -26407,7 +26910,7 @@
       <c r="H7" s="37"/>
       <c r="I7" s="36"/>
       <c r="J7" s="37"/>
-      <c r="K7" s="261"/>
+      <c r="K7" s="247"/>
       <c r="L7" s="56" t="s">
         <v>6</v>
       </c>
@@ -26475,122 +26978,122 @@
       <c r="BV7" s="39"/>
     </row>
     <row r="8" spans="1:74" ht="23.1" customHeight="1" thickBot="1">
-      <c r="B8" s="242" t="s">
+      <c r="B8" s="262" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="251" t="s">
+      <c r="C8" s="270" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="246" t="s">
+      <c r="D8" s="266" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="256" t="s">
+      <c r="E8" s="242" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="257"/>
-      <c r="G8" s="258"/>
-      <c r="H8" s="244" t="s">
+      <c r="F8" s="243"/>
+      <c r="G8" s="244"/>
+      <c r="H8" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="248" t="s">
+      <c r="I8" s="268" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="249" t="s">
+      <c r="J8" s="269" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="262" t="s">
+      <c r="K8" s="248" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="263" t="s">
+      <c r="L8" s="250" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="265" t="s">
+      <c r="M8" s="252" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="240"/>
-      <c r="O8" s="240"/>
-      <c r="P8" s="240"/>
-      <c r="Q8" s="241"/>
-      <c r="R8" s="266" t="s">
+      <c r="N8" s="253"/>
+      <c r="O8" s="253"/>
+      <c r="P8" s="253"/>
+      <c r="Q8" s="254"/>
+      <c r="R8" s="255" t="s">
         <v>17</v>
       </c>
-      <c r="S8" s="240"/>
-      <c r="T8" s="240"/>
-      <c r="U8" s="240"/>
-      <c r="V8" s="241"/>
-      <c r="W8" s="266" t="s">
+      <c r="S8" s="253"/>
+      <c r="T8" s="253"/>
+      <c r="U8" s="253"/>
+      <c r="V8" s="254"/>
+      <c r="W8" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="X8" s="240"/>
-      <c r="Y8" s="240"/>
-      <c r="Z8" s="240"/>
-      <c r="AA8" s="241"/>
-      <c r="AB8" s="268" t="s">
+      <c r="X8" s="253"/>
+      <c r="Y8" s="253"/>
+      <c r="Z8" s="253"/>
+      <c r="AA8" s="254"/>
+      <c r="AB8" s="257" t="s">
         <v>19</v>
       </c>
-      <c r="AC8" s="240"/>
-      <c r="AD8" s="240"/>
-      <c r="AE8" s="240"/>
-      <c r="AF8" s="241"/>
-      <c r="AG8" s="269" t="s">
+      <c r="AC8" s="253"/>
+      <c r="AD8" s="253"/>
+      <c r="AE8" s="253"/>
+      <c r="AF8" s="254"/>
+      <c r="AG8" s="258" t="s">
         <v>20</v>
       </c>
-      <c r="AH8" s="240"/>
-      <c r="AI8" s="240"/>
-      <c r="AJ8" s="240"/>
-      <c r="AK8" s="241"/>
-      <c r="AL8" s="269" t="s">
+      <c r="AH8" s="253"/>
+      <c r="AI8" s="253"/>
+      <c r="AJ8" s="253"/>
+      <c r="AK8" s="254"/>
+      <c r="AL8" s="258" t="s">
         <v>21</v>
       </c>
-      <c r="AM8" s="240"/>
-      <c r="AN8" s="240"/>
-      <c r="AO8" s="240"/>
-      <c r="AP8" s="241"/>
-      <c r="AQ8" s="267" t="s">
+      <c r="AM8" s="253"/>
+      <c r="AN8" s="253"/>
+      <c r="AO8" s="253"/>
+      <c r="AP8" s="254"/>
+      <c r="AQ8" s="256" t="s">
         <v>22</v>
       </c>
-      <c r="AR8" s="240"/>
-      <c r="AS8" s="240"/>
-      <c r="AT8" s="240"/>
-      <c r="AU8" s="241"/>
-      <c r="AV8" s="270" t="s">
+      <c r="AR8" s="253"/>
+      <c r="AS8" s="253"/>
+      <c r="AT8" s="253"/>
+      <c r="AU8" s="254"/>
+      <c r="AV8" s="259" t="s">
         <v>23</v>
       </c>
-      <c r="AW8" s="240"/>
-      <c r="AX8" s="240"/>
-      <c r="AY8" s="240"/>
-      <c r="AZ8" s="241"/>
-      <c r="BA8" s="270" t="s">
+      <c r="AW8" s="253"/>
+      <c r="AX8" s="253"/>
+      <c r="AY8" s="253"/>
+      <c r="AZ8" s="254"/>
+      <c r="BA8" s="259" t="s">
         <v>24</v>
       </c>
-      <c r="BB8" s="240"/>
-      <c r="BC8" s="240"/>
-      <c r="BD8" s="240"/>
-      <c r="BE8" s="241"/>
-      <c r="BF8" s="271" t="s">
+      <c r="BB8" s="253"/>
+      <c r="BC8" s="253"/>
+      <c r="BD8" s="253"/>
+      <c r="BE8" s="254"/>
+      <c r="BF8" s="260" t="s">
         <v>25</v>
       </c>
-      <c r="BG8" s="240"/>
-      <c r="BH8" s="240"/>
-      <c r="BI8" s="240"/>
-      <c r="BJ8" s="241"/>
-      <c r="BK8" s="239"/>
-      <c r="BL8" s="240"/>
-      <c r="BM8" s="240"/>
-      <c r="BN8" s="240"/>
-      <c r="BO8" s="241"/>
-      <c r="BP8" s="239"/>
-      <c r="BQ8" s="240"/>
-      <c r="BR8" s="240"/>
-      <c r="BS8" s="240"/>
-      <c r="BT8" s="241"/>
+      <c r="BG8" s="253"/>
+      <c r="BH8" s="253"/>
+      <c r="BI8" s="253"/>
+      <c r="BJ8" s="254"/>
+      <c r="BK8" s="261"/>
+      <c r="BL8" s="253"/>
+      <c r="BM8" s="253"/>
+      <c r="BN8" s="253"/>
+      <c r="BO8" s="254"/>
+      <c r="BP8" s="261"/>
+      <c r="BQ8" s="253"/>
+      <c r="BR8" s="253"/>
+      <c r="BS8" s="253"/>
+      <c r="BT8" s="254"/>
       <c r="BU8" s="38"/>
       <c r="BV8" s="39"/>
     </row>
     <row r="9" spans="1:74" ht="23.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B9" s="243"/>
-      <c r="C9" s="252"/>
-      <c r="D9" s="247"/>
+      <c r="B9" s="263"/>
+      <c r="C9" s="271"/>
+      <c r="D9" s="267"/>
       <c r="E9" s="58" t="s">
         <v>28</v>
       </c>
@@ -26600,11 +27103,11 @@
       <c r="G9" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="245"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="250"/>
-      <c r="K9" s="250"/>
-      <c r="L9" s="264"/>
+      <c r="H9" s="265"/>
+      <c r="I9" s="254"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="251"/>
       <c r="M9" s="61" t="s">
         <v>31</v>
       </c>
@@ -28559,7 +29062,7 @@
         <v>36</v>
       </c>
       <c r="N29" s="97">
-        <f t="shared" ref="N29:S29" si="1">M31</f>
+        <f t="shared" ref="N29:Q29" si="1">M31</f>
         <v>24</v>
       </c>
       <c r="O29" s="97">
@@ -28742,7 +29245,7 @@
         <v>52</v>
       </c>
       <c r="M31" s="97">
-        <f t="shared" ref="M31:S31" si="2">M29-M30</f>
+        <f t="shared" ref="M31:Q31" si="2">M29-M30</f>
         <v>24</v>
       </c>
       <c r="N31" s="97">
@@ -28831,82 +29334,91 @@
     <row r="33" spans="2:74" ht="381.95" customHeight="1"/>
     <row r="34" spans="2:74" ht="216.95" customHeight="1"/>
     <row r="36" spans="2:74" ht="50.1" customHeight="1">
-      <c r="B36" s="253"/>
-      <c r="C36" s="254"/>
-      <c r="D36" s="254"/>
-      <c r="E36" s="254"/>
-      <c r="F36" s="254"/>
-      <c r="G36" s="254"/>
-      <c r="H36" s="254"/>
-      <c r="I36" s="254"/>
-      <c r="J36" s="254"/>
-      <c r="K36" s="254"/>
-      <c r="L36" s="254"/>
-      <c r="M36" s="254"/>
-      <c r="N36" s="254"/>
-      <c r="O36" s="254"/>
-      <c r="P36" s="254"/>
-      <c r="Q36" s="254"/>
-      <c r="R36" s="254"/>
-      <c r="S36" s="254"/>
-      <c r="T36" s="254"/>
-      <c r="U36" s="254"/>
-      <c r="V36" s="254"/>
-      <c r="W36" s="254"/>
-      <c r="X36" s="254"/>
-      <c r="Y36" s="254"/>
-      <c r="Z36" s="254"/>
-      <c r="AA36" s="254"/>
-      <c r="AB36" s="254"/>
-      <c r="AC36" s="254"/>
-      <c r="AD36" s="254"/>
-      <c r="AE36" s="254"/>
-      <c r="AF36" s="254"/>
-      <c r="AG36" s="254"/>
-      <c r="AH36" s="254"/>
-      <c r="AI36" s="254"/>
-      <c r="AJ36" s="254"/>
-      <c r="AK36" s="254"/>
-      <c r="AL36" s="254"/>
-      <c r="AM36" s="254"/>
-      <c r="AN36" s="254"/>
-      <c r="AO36" s="254"/>
-      <c r="AP36" s="254"/>
-      <c r="AQ36" s="254"/>
-      <c r="AR36" s="254"/>
-      <c r="AS36" s="254"/>
-      <c r="AT36" s="254"/>
-      <c r="AU36" s="254"/>
-      <c r="AV36" s="254"/>
-      <c r="AW36" s="254"/>
-      <c r="AX36" s="254"/>
-      <c r="AY36" s="254"/>
-      <c r="AZ36" s="254"/>
-      <c r="BA36" s="254"/>
-      <c r="BB36" s="254"/>
-      <c r="BC36" s="254"/>
-      <c r="BD36" s="254"/>
-      <c r="BE36" s="254"/>
-      <c r="BF36" s="254"/>
-      <c r="BG36" s="254"/>
-      <c r="BH36" s="254"/>
-      <c r="BI36" s="254"/>
-      <c r="BJ36" s="254"/>
-      <c r="BK36" s="254"/>
-      <c r="BL36" s="254"/>
-      <c r="BM36" s="254"/>
-      <c r="BN36" s="254"/>
-      <c r="BO36" s="254"/>
-      <c r="BP36" s="254"/>
-      <c r="BQ36" s="254"/>
-      <c r="BR36" s="254"/>
-      <c r="BS36" s="254"/>
-      <c r="BT36" s="254"/>
-      <c r="BU36" s="254"/>
-      <c r="BV36" s="255"/>
+      <c r="B36" s="239"/>
+      <c r="C36" s="240"/>
+      <c r="D36" s="240"/>
+      <c r="E36" s="240"/>
+      <c r="F36" s="240"/>
+      <c r="G36" s="240"/>
+      <c r="H36" s="240"/>
+      <c r="I36" s="240"/>
+      <c r="J36" s="240"/>
+      <c r="K36" s="240"/>
+      <c r="L36" s="240"/>
+      <c r="M36" s="240"/>
+      <c r="N36" s="240"/>
+      <c r="O36" s="240"/>
+      <c r="P36" s="240"/>
+      <c r="Q36" s="240"/>
+      <c r="R36" s="240"/>
+      <c r="S36" s="240"/>
+      <c r="T36" s="240"/>
+      <c r="U36" s="240"/>
+      <c r="V36" s="240"/>
+      <c r="W36" s="240"/>
+      <c r="X36" s="240"/>
+      <c r="Y36" s="240"/>
+      <c r="Z36" s="240"/>
+      <c r="AA36" s="240"/>
+      <c r="AB36" s="240"/>
+      <c r="AC36" s="240"/>
+      <c r="AD36" s="240"/>
+      <c r="AE36" s="240"/>
+      <c r="AF36" s="240"/>
+      <c r="AG36" s="240"/>
+      <c r="AH36" s="240"/>
+      <c r="AI36" s="240"/>
+      <c r="AJ36" s="240"/>
+      <c r="AK36" s="240"/>
+      <c r="AL36" s="240"/>
+      <c r="AM36" s="240"/>
+      <c r="AN36" s="240"/>
+      <c r="AO36" s="240"/>
+      <c r="AP36" s="240"/>
+      <c r="AQ36" s="240"/>
+      <c r="AR36" s="240"/>
+      <c r="AS36" s="240"/>
+      <c r="AT36" s="240"/>
+      <c r="AU36" s="240"/>
+      <c r="AV36" s="240"/>
+      <c r="AW36" s="240"/>
+      <c r="AX36" s="240"/>
+      <c r="AY36" s="240"/>
+      <c r="AZ36" s="240"/>
+      <c r="BA36" s="240"/>
+      <c r="BB36" s="240"/>
+      <c r="BC36" s="240"/>
+      <c r="BD36" s="240"/>
+      <c r="BE36" s="240"/>
+      <c r="BF36" s="240"/>
+      <c r="BG36" s="240"/>
+      <c r="BH36" s="240"/>
+      <c r="BI36" s="240"/>
+      <c r="BJ36" s="240"/>
+      <c r="BK36" s="240"/>
+      <c r="BL36" s="240"/>
+      <c r="BM36" s="240"/>
+      <c r="BN36" s="240"/>
+      <c r="BO36" s="240"/>
+      <c r="BP36" s="240"/>
+      <c r="BQ36" s="240"/>
+      <c r="BR36" s="240"/>
+      <c r="BS36" s="240"/>
+      <c r="BT36" s="240"/>
+      <c r="BU36" s="240"/>
+      <c r="BV36" s="241"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="K3:K7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
     <mergeCell ref="BP8:BT8"/>
     <mergeCell ref="B36:BV36"/>
     <mergeCell ref="AL8:AP8"/>
@@ -28921,15 +29433,6 @@
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="K3:K7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
   </mergeCells>
   <conditionalFormatting sqref="L10">
     <cfRule type="dataBar" priority="7">
@@ -29118,6 +29621,835 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A42A8A-1645-4F26-8951-6DF6CC3DD203}">
+  <dimension ref="A1:AB24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="29" width="5.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28">
+      <c r="A1" s="278"/>
+      <c r="B1" s="279"/>
+      <c r="C1" s="279"/>
+      <c r="D1" s="279"/>
+      <c r="E1" s="279"/>
+      <c r="F1" s="279"/>
+      <c r="G1" s="279"/>
+      <c r="H1" s="279"/>
+      <c r="I1" s="279"/>
+      <c r="J1" s="279"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="279"/>
+      <c r="M1" s="279"/>
+      <c r="N1" s="279"/>
+      <c r="O1" s="279"/>
+      <c r="P1" s="279"/>
+      <c r="Q1" s="279"/>
+      <c r="R1" s="279"/>
+      <c r="S1" s="279"/>
+      <c r="T1" s="279"/>
+      <c r="U1" s="279"/>
+      <c r="V1" s="279"/>
+      <c r="W1" s="279"/>
+      <c r="X1" s="279"/>
+      <c r="Y1" s="279"/>
+      <c r="Z1" s="279"/>
+      <c r="AA1" s="278"/>
+      <c r="AB1" s="274"/>
+    </row>
+    <row r="2" spans="1:28" ht="18">
+      <c r="A2" s="278"/>
+      <c r="B2" s="279"/>
+      <c r="C2" s="279"/>
+      <c r="D2" s="279"/>
+      <c r="E2" s="279"/>
+      <c r="F2" s="279"/>
+      <c r="G2" s="280">
+        <v>7</v>
+      </c>
+      <c r="H2" s="275" t="s">
+        <v>244</v>
+      </c>
+      <c r="I2" s="280">
+        <f>G2+H3</f>
+        <v>14.17</v>
+      </c>
+      <c r="J2" s="281"/>
+      <c r="K2" s="282"/>
+      <c r="L2" s="283">
+        <v>21.16</v>
+      </c>
+      <c r="M2" s="276" t="s">
+        <v>247</v>
+      </c>
+      <c r="N2" s="283">
+        <f>L2+M3</f>
+        <v>27.990000000000002</v>
+      </c>
+      <c r="O2" s="279"/>
+      <c r="P2" s="279"/>
+      <c r="Q2" s="279"/>
+      <c r="R2" s="279"/>
+      <c r="S2" s="279"/>
+      <c r="T2" s="279"/>
+      <c r="U2" s="279"/>
+      <c r="V2" s="279"/>
+      <c r="W2" s="279"/>
+      <c r="X2" s="279"/>
+      <c r="Y2" s="279"/>
+      <c r="Z2" s="279"/>
+      <c r="AA2" s="284"/>
+      <c r="AB2" s="277"/>
+    </row>
+    <row r="3" spans="1:28" ht="18">
+      <c r="A3" s="278"/>
+      <c r="B3" s="279"/>
+      <c r="C3" s="279"/>
+      <c r="D3" s="279"/>
+      <c r="E3" s="279"/>
+      <c r="F3" s="285"/>
+      <c r="G3" s="280">
+        <f>I3-H3</f>
+        <v>13.990000000000004</v>
+      </c>
+      <c r="H3" s="280">
+        <v>7.17</v>
+      </c>
+      <c r="I3" s="280">
+        <v>21.160000000000004</v>
+      </c>
+      <c r="J3" s="279"/>
+      <c r="K3" s="286"/>
+      <c r="L3" s="283">
+        <f>N3-M3</f>
+        <v>21.159999999999997</v>
+      </c>
+      <c r="M3" s="283">
+        <v>6.83</v>
+      </c>
+      <c r="N3" s="283">
+        <v>27.99</v>
+      </c>
+      <c r="O3" s="287"/>
+      <c r="P3" s="288"/>
+      <c r="Q3" s="279"/>
+      <c r="R3" s="279"/>
+      <c r="S3" s="279"/>
+      <c r="T3" s="279"/>
+      <c r="U3" s="279"/>
+      <c r="V3" s="279"/>
+      <c r="W3" s="279"/>
+      <c r="X3" s="279"/>
+      <c r="Y3" s="279"/>
+      <c r="Z3" s="279"/>
+      <c r="AA3" s="284"/>
+      <c r="AB3" s="277"/>
+    </row>
+    <row r="4" spans="1:28" ht="18">
+      <c r="A4" s="278"/>
+      <c r="B4" s="279"/>
+      <c r="C4" s="279"/>
+      <c r="D4" s="279"/>
+      <c r="E4" s="279"/>
+      <c r="F4" s="289"/>
+      <c r="G4" s="279"/>
+      <c r="H4" s="279"/>
+      <c r="I4" s="279"/>
+      <c r="J4" s="279"/>
+      <c r="K4" s="288"/>
+      <c r="L4" s="279"/>
+      <c r="M4" s="279"/>
+      <c r="N4" s="279"/>
+      <c r="O4" s="290"/>
+      <c r="P4" s="288"/>
+      <c r="Q4" s="279"/>
+      <c r="R4" s="279"/>
+      <c r="S4" s="279"/>
+      <c r="T4" s="279"/>
+      <c r="U4" s="279"/>
+      <c r="V4" s="279"/>
+      <c r="W4" s="279"/>
+      <c r="X4" s="279"/>
+      <c r="Y4" s="279"/>
+      <c r="Z4" s="279"/>
+      <c r="AA4" s="284"/>
+      <c r="AB4" s="277"/>
+    </row>
+    <row r="5" spans="1:28" ht="18">
+      <c r="A5" s="278"/>
+      <c r="B5" s="280">
+        <v>0</v>
+      </c>
+      <c r="C5" s="275" t="s">
+        <v>243</v>
+      </c>
+      <c r="D5" s="280">
+        <f>B5+C6</f>
+        <v>7</v>
+      </c>
+      <c r="E5" s="291"/>
+      <c r="F5" s="289"/>
+      <c r="G5" s="279"/>
+      <c r="H5" s="279"/>
+      <c r="I5" s="279"/>
+      <c r="J5" s="279"/>
+      <c r="K5" s="288"/>
+      <c r="L5" s="279"/>
+      <c r="M5" s="279"/>
+      <c r="N5" s="279"/>
+      <c r="O5" s="290"/>
+      <c r="P5" s="292"/>
+      <c r="Q5" s="283">
+        <v>27.990000000000002</v>
+      </c>
+      <c r="R5" s="276" t="s">
+        <v>35</v>
+      </c>
+      <c r="S5" s="283">
+        <f>Q5+R6</f>
+        <v>34.99</v>
+      </c>
+      <c r="T5" s="289"/>
+      <c r="U5" s="282"/>
+      <c r="V5" s="283">
+        <v>34.99</v>
+      </c>
+      <c r="W5" s="276" t="s">
+        <v>248</v>
+      </c>
+      <c r="X5" s="283">
+        <f>W6+V5</f>
+        <v>41.660000000000004</v>
+      </c>
+      <c r="Y5" s="279"/>
+      <c r="Z5" s="279"/>
+      <c r="AA5" s="284"/>
+      <c r="AB5" s="277"/>
+    </row>
+    <row r="6" spans="1:28" ht="18">
+      <c r="A6" s="278"/>
+      <c r="B6" s="280">
+        <f>D6-C6</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="280">
+        <v>7</v>
+      </c>
+      <c r="D6" s="280">
+        <v>6.9999999999999964</v>
+      </c>
+      <c r="E6" s="293"/>
+      <c r="F6" s="290"/>
+      <c r="G6" s="279"/>
+      <c r="H6" s="279"/>
+      <c r="I6" s="279"/>
+      <c r="J6" s="279"/>
+      <c r="K6" s="288"/>
+      <c r="L6" s="279"/>
+      <c r="M6" s="279"/>
+      <c r="N6" s="279"/>
+      <c r="O6" s="282"/>
+      <c r="P6" s="279"/>
+      <c r="Q6" s="283">
+        <f>S6-R6</f>
+        <v>27.990000000000002</v>
+      </c>
+      <c r="R6" s="283">
+        <v>7</v>
+      </c>
+      <c r="S6" s="283">
+        <v>34.99</v>
+      </c>
+      <c r="T6" s="294"/>
+      <c r="U6" s="295"/>
+      <c r="V6" s="283">
+        <f>X6-W6</f>
+        <v>34.99</v>
+      </c>
+      <c r="W6" s="283">
+        <v>6.67</v>
+      </c>
+      <c r="X6" s="283">
+        <v>41.660000000000004</v>
+      </c>
+      <c r="Y6" s="279"/>
+      <c r="Z6" s="279"/>
+      <c r="AA6" s="284"/>
+      <c r="AB6" s="277"/>
+    </row>
+    <row r="7" spans="1:28" ht="18">
+      <c r="A7" s="278"/>
+      <c r="B7" s="279"/>
+      <c r="C7" s="279"/>
+      <c r="D7" s="279"/>
+      <c r="E7" s="296"/>
+      <c r="F7" s="290"/>
+      <c r="G7" s="279"/>
+      <c r="H7" s="279"/>
+      <c r="I7" s="279"/>
+      <c r="J7" s="279"/>
+      <c r="K7" s="288"/>
+      <c r="L7" s="279"/>
+      <c r="M7" s="279"/>
+      <c r="N7" s="279"/>
+      <c r="O7" s="282"/>
+      <c r="P7" s="279"/>
+      <c r="Q7" s="279"/>
+      <c r="R7" s="279"/>
+      <c r="S7" s="279"/>
+      <c r="T7" s="279"/>
+      <c r="U7" s="279"/>
+      <c r="V7" s="279"/>
+      <c r="W7" s="279"/>
+      <c r="X7" s="279"/>
+      <c r="Y7" s="279"/>
+      <c r="Z7" s="279"/>
+      <c r="AA7" s="284"/>
+      <c r="AB7" s="277"/>
+    </row>
+    <row r="8" spans="1:28" ht="18">
+      <c r="A8" s="278"/>
+      <c r="B8" s="279"/>
+      <c r="C8" s="279"/>
+      <c r="D8" s="279"/>
+      <c r="E8" s="296"/>
+      <c r="F8" s="290"/>
+      <c r="G8" s="283">
+        <v>7</v>
+      </c>
+      <c r="H8" s="276" t="s">
+        <v>245</v>
+      </c>
+      <c r="I8" s="283">
+        <f>G8+H9</f>
+        <v>14.5</v>
+      </c>
+      <c r="J8" s="289"/>
+      <c r="K8" s="292"/>
+      <c r="L8" s="283">
+        <v>14.5</v>
+      </c>
+      <c r="M8" s="276" t="s">
+        <v>246</v>
+      </c>
+      <c r="N8" s="283">
+        <f>L8+M9</f>
+        <v>21.16</v>
+      </c>
+      <c r="O8" s="297"/>
+      <c r="P8" s="279"/>
+      <c r="Q8" s="279"/>
+      <c r="R8" s="279"/>
+      <c r="S8" s="279"/>
+      <c r="T8" s="279"/>
+      <c r="U8" s="279"/>
+      <c r="V8" s="279"/>
+      <c r="W8" s="279"/>
+      <c r="X8" s="279"/>
+      <c r="Y8" s="279"/>
+      <c r="Z8" s="279"/>
+      <c r="AA8" s="284"/>
+      <c r="AB8" s="277"/>
+    </row>
+    <row r="9" spans="1:28" ht="18">
+      <c r="A9" s="278"/>
+      <c r="B9" s="279"/>
+      <c r="C9" s="279"/>
+      <c r="D9" s="279"/>
+      <c r="E9" s="279"/>
+      <c r="F9" s="295"/>
+      <c r="G9" s="283">
+        <f>I9-H9</f>
+        <v>6.9999999999999964</v>
+      </c>
+      <c r="H9" s="283">
+        <v>7.5</v>
+      </c>
+      <c r="I9" s="283">
+        <v>14.499999999999996</v>
+      </c>
+      <c r="J9" s="294"/>
+      <c r="K9" s="295"/>
+      <c r="L9" s="283">
+        <f>N9-M9</f>
+        <v>14.499999999999996</v>
+      </c>
+      <c r="M9" s="283">
+        <v>6.66</v>
+      </c>
+      <c r="N9" s="283">
+        <v>21.159999999999997</v>
+      </c>
+      <c r="O9" s="279"/>
+      <c r="P9" s="279"/>
+      <c r="Q9" s="279"/>
+      <c r="R9" s="279"/>
+      <c r="S9" s="279"/>
+      <c r="T9" s="279"/>
+      <c r="U9" s="279"/>
+      <c r="V9" s="279"/>
+      <c r="W9" s="279"/>
+      <c r="X9" s="279"/>
+      <c r="Y9" s="279"/>
+      <c r="Z9" s="279"/>
+      <c r="AA9" s="284"/>
+      <c r="AB9" s="277"/>
+    </row>
+    <row r="10" spans="1:28" ht="18">
+      <c r="A10" s="278"/>
+      <c r="B10" s="279"/>
+      <c r="C10" s="279"/>
+      <c r="D10" s="279"/>
+      <c r="E10" s="279"/>
+      <c r="F10" s="279"/>
+      <c r="G10" s="279"/>
+      <c r="H10" s="279"/>
+      <c r="I10" s="279"/>
+      <c r="J10" s="279"/>
+      <c r="K10" s="279"/>
+      <c r="L10" s="279"/>
+      <c r="M10" s="279"/>
+      <c r="N10" s="279"/>
+      <c r="O10" s="279"/>
+      <c r="P10" s="279"/>
+      <c r="Q10" s="279"/>
+      <c r="R10" s="279"/>
+      <c r="S10" s="279"/>
+      <c r="T10" s="279"/>
+      <c r="U10" s="279"/>
+      <c r="V10" s="279"/>
+      <c r="W10" s="279"/>
+      <c r="X10" s="279"/>
+      <c r="Y10" s="279"/>
+      <c r="Z10" s="279"/>
+      <c r="AA10" s="284"/>
+      <c r="AB10" s="277"/>
+    </row>
+    <row r="11" spans="1:28" ht="18">
+      <c r="A11" s="278"/>
+      <c r="B11" s="279"/>
+      <c r="C11" s="279"/>
+      <c r="D11" s="279"/>
+      <c r="E11" s="279"/>
+      <c r="F11" s="279"/>
+      <c r="G11" s="279"/>
+      <c r="H11" s="279"/>
+      <c r="I11" s="279"/>
+      <c r="J11" s="279"/>
+      <c r="K11" s="279"/>
+      <c r="L11" s="279"/>
+      <c r="M11" s="279"/>
+      <c r="N11" s="279"/>
+      <c r="O11" s="279"/>
+      <c r="P11" s="279"/>
+      <c r="Q11" s="279"/>
+      <c r="R11" s="279"/>
+      <c r="S11" s="279"/>
+      <c r="T11" s="279"/>
+      <c r="U11" s="279"/>
+      <c r="V11" s="279"/>
+      <c r="W11" s="279"/>
+      <c r="X11" s="279"/>
+      <c r="Y11" s="279"/>
+      <c r="Z11" s="279"/>
+      <c r="AA11" s="284"/>
+      <c r="AB11" s="277"/>
+    </row>
+    <row r="12" spans="1:28" ht="18">
+      <c r="A12" s="278"/>
+      <c r="B12" s="279"/>
+      <c r="C12" s="279"/>
+      <c r="D12" s="279"/>
+      <c r="E12" s="279"/>
+      <c r="F12" s="279"/>
+      <c r="G12" s="279"/>
+      <c r="H12" s="279"/>
+      <c r="I12" s="279"/>
+      <c r="J12" s="279"/>
+      <c r="K12" s="279"/>
+      <c r="L12" s="279"/>
+      <c r="M12" s="279"/>
+      <c r="N12" s="279"/>
+      <c r="O12" s="279"/>
+      <c r="P12" s="279"/>
+      <c r="Q12" s="279"/>
+      <c r="R12" s="279"/>
+      <c r="S12" s="279"/>
+      <c r="T12" s="279"/>
+      <c r="U12" s="279"/>
+      <c r="V12" s="279"/>
+      <c r="W12" s="279"/>
+      <c r="X12" s="279"/>
+      <c r="Y12" s="279"/>
+      <c r="Z12" s="279"/>
+      <c r="AA12" s="284"/>
+      <c r="AB12" s="277"/>
+    </row>
+    <row r="13" spans="1:28" ht="18">
+      <c r="A13" s="278"/>
+      <c r="B13" s="279"/>
+      <c r="C13" s="279"/>
+      <c r="D13" s="279"/>
+      <c r="E13" s="279"/>
+      <c r="F13" s="279"/>
+      <c r="G13" s="279"/>
+      <c r="H13" s="279"/>
+      <c r="I13" s="279"/>
+      <c r="J13" s="279"/>
+      <c r="K13" s="279"/>
+      <c r="L13" s="279"/>
+      <c r="M13" s="279"/>
+      <c r="N13" s="279"/>
+      <c r="O13" s="279"/>
+      <c r="P13" s="279"/>
+      <c r="Q13" s="279"/>
+      <c r="R13" s="279"/>
+      <c r="S13" s="279"/>
+      <c r="T13" s="279"/>
+      <c r="U13" s="279"/>
+      <c r="V13" s="279"/>
+      <c r="W13" s="279"/>
+      <c r="X13" s="279"/>
+      <c r="Y13" s="279"/>
+      <c r="Z13" s="279"/>
+      <c r="AA13" s="284"/>
+      <c r="AB13" s="277"/>
+    </row>
+    <row r="14" spans="1:28" ht="18">
+      <c r="A14" s="278"/>
+      <c r="B14" s="284"/>
+      <c r="C14" s="284"/>
+      <c r="D14" s="284"/>
+      <c r="E14" s="284"/>
+      <c r="F14" s="284"/>
+      <c r="G14" s="284"/>
+      <c r="H14" s="284"/>
+      <c r="I14" s="284"/>
+      <c r="J14" s="284"/>
+      <c r="K14" s="284"/>
+      <c r="L14" s="284"/>
+      <c r="M14" s="284"/>
+      <c r="N14" s="284"/>
+      <c r="O14" s="284"/>
+      <c r="P14" s="284"/>
+      <c r="Q14" s="284"/>
+      <c r="R14" s="284"/>
+      <c r="S14" s="284"/>
+      <c r="T14" s="284"/>
+      <c r="U14" s="284"/>
+      <c r="V14" s="284"/>
+      <c r="W14" s="284"/>
+      <c r="X14" s="284"/>
+      <c r="Y14" s="284"/>
+      <c r="Z14" s="284"/>
+      <c r="AA14" s="284"/>
+      <c r="AB14" s="277"/>
+    </row>
+    <row r="15" spans="1:28" ht="18">
+      <c r="A15" s="278"/>
+      <c r="B15" s="284"/>
+      <c r="C15" s="284"/>
+      <c r="D15" s="284"/>
+      <c r="E15" s="284"/>
+      <c r="F15" s="284"/>
+      <c r="G15" s="284"/>
+      <c r="H15" s="284"/>
+      <c r="I15" s="284"/>
+      <c r="J15" s="284"/>
+      <c r="K15" s="284"/>
+      <c r="L15" s="284"/>
+      <c r="M15" s="284"/>
+      <c r="N15" s="284"/>
+      <c r="O15" s="284"/>
+      <c r="P15" s="284"/>
+      <c r="Q15" s="284"/>
+      <c r="R15" s="284"/>
+      <c r="S15" s="284"/>
+      <c r="T15" s="284"/>
+      <c r="U15" s="284"/>
+      <c r="V15" s="284"/>
+      <c r="W15" s="284"/>
+      <c r="X15" s="284"/>
+      <c r="Y15" s="284"/>
+      <c r="Z15" s="284"/>
+      <c r="AA15" s="284"/>
+      <c r="AB15" s="277"/>
+    </row>
+    <row r="16" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A16" s="298"/>
+      <c r="B16" s="299"/>
+      <c r="C16" s="299"/>
+      <c r="D16" s="299"/>
+      <c r="E16" s="299"/>
+      <c r="F16" s="299"/>
+      <c r="G16" s="299"/>
+      <c r="H16" s="299"/>
+      <c r="I16" s="299"/>
+      <c r="J16" s="299"/>
+      <c r="K16" s="299"/>
+      <c r="L16" s="299"/>
+      <c r="M16" s="299"/>
+      <c r="N16" s="299"/>
+      <c r="O16" s="299"/>
+      <c r="P16" s="299"/>
+      <c r="Q16" s="299"/>
+      <c r="R16" s="299"/>
+      <c r="S16" s="299"/>
+      <c r="T16" s="299"/>
+      <c r="U16" s="299"/>
+      <c r="V16" s="299"/>
+      <c r="W16" s="299"/>
+      <c r="X16" s="299"/>
+      <c r="Y16" s="299"/>
+      <c r="Z16" s="299"/>
+      <c r="AA16" s="299"/>
+      <c r="AB16" s="273"/>
+    </row>
+    <row r="17" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A17" s="298"/>
+      <c r="B17" s="299"/>
+      <c r="C17" s="299"/>
+      <c r="D17" s="299"/>
+      <c r="E17" s="299"/>
+      <c r="F17" s="299"/>
+      <c r="G17" s="299"/>
+      <c r="H17" s="299"/>
+      <c r="I17" s="299"/>
+      <c r="J17" s="299"/>
+      <c r="K17" s="299"/>
+      <c r="L17" s="299"/>
+      <c r="M17" s="299"/>
+      <c r="N17" s="299"/>
+      <c r="O17" s="299"/>
+      <c r="P17" s="299"/>
+      <c r="Q17" s="299"/>
+      <c r="R17" s="299"/>
+      <c r="S17" s="299"/>
+      <c r="T17" s="299"/>
+      <c r="U17" s="299"/>
+      <c r="V17" s="299"/>
+      <c r="W17" s="299"/>
+      <c r="X17" s="299"/>
+      <c r="Y17" s="299"/>
+      <c r="Z17" s="299"/>
+      <c r="AA17" s="299"/>
+      <c r="AB17" s="273"/>
+    </row>
+    <row r="18" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A18" s="298"/>
+      <c r="B18" s="299"/>
+      <c r="C18" s="299"/>
+      <c r="D18" s="299"/>
+      <c r="E18" s="299"/>
+      <c r="F18" s="299"/>
+      <c r="G18" s="299"/>
+      <c r="H18" s="299"/>
+      <c r="I18" s="299"/>
+      <c r="J18" s="299"/>
+      <c r="K18" s="299"/>
+      <c r="L18" s="299"/>
+      <c r="M18" s="299"/>
+      <c r="N18" s="299"/>
+      <c r="O18" s="299"/>
+      <c r="P18" s="299"/>
+      <c r="Q18" s="299"/>
+      <c r="R18" s="299"/>
+      <c r="S18" s="299"/>
+      <c r="T18" s="299"/>
+      <c r="U18" s="299"/>
+      <c r="V18" s="299"/>
+      <c r="W18" s="299"/>
+      <c r="X18" s="299"/>
+      <c r="Y18" s="299"/>
+      <c r="Z18" s="299"/>
+      <c r="AA18" s="299"/>
+      <c r="AB18" s="273"/>
+    </row>
+    <row r="19" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A19" s="298"/>
+      <c r="B19" s="299"/>
+      <c r="C19" s="299"/>
+      <c r="D19" s="299"/>
+      <c r="E19" s="299"/>
+      <c r="F19" s="299"/>
+      <c r="G19" s="299"/>
+      <c r="H19" s="299"/>
+      <c r="I19" s="299"/>
+      <c r="J19" s="299"/>
+      <c r="K19" s="299"/>
+      <c r="L19" s="299"/>
+      <c r="M19" s="299"/>
+      <c r="N19" s="299"/>
+      <c r="O19" s="299"/>
+      <c r="P19" s="299"/>
+      <c r="Q19" s="299"/>
+      <c r="R19" s="299"/>
+      <c r="S19" s="299"/>
+      <c r="T19" s="299"/>
+      <c r="U19" s="299"/>
+      <c r="V19" s="299"/>
+      <c r="W19" s="299"/>
+      <c r="X19" s="299"/>
+      <c r="Y19" s="299"/>
+      <c r="Z19" s="299"/>
+      <c r="AA19" s="299"/>
+      <c r="AB19" s="273"/>
+    </row>
+    <row r="20" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A20" s="298"/>
+      <c r="B20" s="299"/>
+      <c r="C20" s="299"/>
+      <c r="D20" s="299"/>
+      <c r="E20" s="299"/>
+      <c r="F20" s="299"/>
+      <c r="G20" s="299"/>
+      <c r="H20" s="299"/>
+      <c r="I20" s="299"/>
+      <c r="J20" s="299"/>
+      <c r="K20" s="299"/>
+      <c r="L20" s="299"/>
+      <c r="M20" s="299"/>
+      <c r="N20" s="299"/>
+      <c r="O20" s="299"/>
+      <c r="P20" s="299"/>
+      <c r="Q20" s="299"/>
+      <c r="R20" s="299"/>
+      <c r="S20" s="299"/>
+      <c r="T20" s="299"/>
+      <c r="U20" s="299"/>
+      <c r="V20" s="299"/>
+      <c r="W20" s="299"/>
+      <c r="X20" s="299"/>
+      <c r="Y20" s="299"/>
+      <c r="Z20" s="299"/>
+      <c r="AA20" s="299"/>
+      <c r="AB20" s="273"/>
+    </row>
+    <row r="21" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A21" s="298"/>
+      <c r="B21" s="299"/>
+      <c r="C21" s="299"/>
+      <c r="D21" s="299"/>
+      <c r="E21" s="299"/>
+      <c r="F21" s="299"/>
+      <c r="G21" s="299"/>
+      <c r="H21" s="299"/>
+      <c r="I21" s="299"/>
+      <c r="J21" s="299"/>
+      <c r="K21" s="299"/>
+      <c r="L21" s="299"/>
+      <c r="M21" s="299"/>
+      <c r="N21" s="299"/>
+      <c r="O21" s="299"/>
+      <c r="P21" s="299"/>
+      <c r="Q21" s="299"/>
+      <c r="R21" s="299"/>
+      <c r="S21" s="299"/>
+      <c r="T21" s="299"/>
+      <c r="U21" s="299"/>
+      <c r="V21" s="299"/>
+      <c r="W21" s="299"/>
+      <c r="X21" s="299"/>
+      <c r="Y21" s="299"/>
+      <c r="Z21" s="299"/>
+      <c r="AA21" s="299"/>
+      <c r="AB21" s="273"/>
+    </row>
+    <row r="22" spans="1:28" ht="18">
+      <c r="B22" s="273"/>
+      <c r="C22" s="273"/>
+      <c r="D22" s="273"/>
+      <c r="E22" s="273"/>
+      <c r="F22" s="273"/>
+      <c r="G22" s="273"/>
+      <c r="H22" s="273"/>
+      <c r="I22" s="273"/>
+      <c r="J22" s="273"/>
+      <c r="K22" s="273"/>
+      <c r="L22" s="273"/>
+      <c r="M22" s="273"/>
+      <c r="N22" s="273"/>
+      <c r="O22" s="273"/>
+      <c r="P22" s="273"/>
+      <c r="Q22" s="273"/>
+      <c r="R22" s="273"/>
+      <c r="S22" s="273"/>
+      <c r="T22" s="273"/>
+      <c r="U22" s="273"/>
+      <c r="V22" s="273"/>
+      <c r="W22" s="273"/>
+      <c r="X22" s="273"/>
+      <c r="Y22" s="273"/>
+      <c r="Z22" s="273"/>
+      <c r="AA22" s="273"/>
+      <c r="AB22" s="273"/>
+    </row>
+    <row r="23" spans="1:28" ht="17.25">
+      <c r="B23" s="273"/>
+      <c r="C23" s="273"/>
+      <c r="D23" s="273"/>
+      <c r="E23" s="273"/>
+      <c r="F23" s="273"/>
+      <c r="G23" s="273"/>
+      <c r="H23" s="273"/>
+      <c r="I23" s="273"/>
+      <c r="J23" s="273"/>
+      <c r="K23" s="273"/>
+      <c r="L23" s="273"/>
+      <c r="M23" s="273"/>
+      <c r="N23" s="273"/>
+      <c r="O23" s="273"/>
+      <c r="P23" s="273"/>
+      <c r="Q23" s="273"/>
+      <c r="R23" s="273"/>
+      <c r="S23" s="273"/>
+      <c r="T23" s="273"/>
+      <c r="U23" s="273"/>
+      <c r="V23" s="273"/>
+      <c r="W23" s="273"/>
+      <c r="X23" s="273"/>
+      <c r="Y23" s="273"/>
+      <c r="Z23" s="273"/>
+      <c r="AA23" s="273"/>
+      <c r="AB23" s="273"/>
+    </row>
+    <row r="24" spans="1:28" ht="17.25">
+      <c r="B24" s="273"/>
+      <c r="C24" s="273"/>
+      <c r="D24" s="273"/>
+      <c r="E24" s="273"/>
+      <c r="F24" s="273"/>
+      <c r="G24" s="273"/>
+      <c r="H24" s="273"/>
+      <c r="I24" s="273"/>
+      <c r="J24" s="273"/>
+      <c r="K24" s="273"/>
+      <c r="L24" s="273"/>
+      <c r="M24" s="273"/>
+      <c r="N24" s="273"/>
+      <c r="O24" s="273"/>
+      <c r="P24" s="273"/>
+      <c r="Q24" s="273"/>
+      <c r="R24" s="273"/>
+      <c r="S24" s="273"/>
+      <c r="T24" s="273"/>
+      <c r="U24" s="273"/>
+      <c r="V24" s="273"/>
+      <c r="W24" s="273"/>
+      <c r="X24" s="273"/>
+      <c r="Y24" s="273"/>
+      <c r="Z24" s="273"/>
+      <c r="AA24" s="273"/>
+      <c r="AB24" s="273"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{097109D2-447F-4F39-A4BD-92E74C4EFF49}">
   <dimension ref="B3:I9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
@@ -29218,7 +30550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3" tint="0.39997558519241921"/>
@@ -29328,7 +30660,7 @@
       <c r="H2" s="40"/>
       <c r="I2" s="40"/>
       <c r="J2" s="41"/>
-      <c r="K2" s="259" t="s">
+      <c r="K2" s="245" t="s">
         <v>1</v>
       </c>
       <c r="L2" s="42" t="s">
@@ -29407,7 +30739,7 @@
       <c r="H3" s="40"/>
       <c r="I3" s="40"/>
       <c r="J3" s="41"/>
-      <c r="K3" s="260"/>
+      <c r="K3" s="246"/>
       <c r="L3" s="47" t="s">
         <v>3</v>
       </c>
@@ -29484,7 +30816,7 @@
       <c r="H4" s="37"/>
       <c r="I4" s="36"/>
       <c r="J4" s="37"/>
-      <c r="K4" s="260"/>
+      <c r="K4" s="246"/>
       <c r="L4" s="52" t="s">
         <v>4</v>
       </c>
@@ -29561,7 +30893,7 @@
       <c r="H5" s="37"/>
       <c r="I5" s="36"/>
       <c r="J5" s="37"/>
-      <c r="K5" s="260"/>
+      <c r="K5" s="246"/>
       <c r="L5" s="54" t="s">
         <v>5</v>
       </c>
@@ -29638,7 +30970,7 @@
       <c r="H6" s="37"/>
       <c r="I6" s="36"/>
       <c r="J6" s="37"/>
-      <c r="K6" s="261"/>
+      <c r="K6" s="247"/>
       <c r="L6" s="56" t="s">
         <v>6</v>
       </c>
@@ -29706,126 +31038,126 @@
       <c r="BV6" s="39"/>
     </row>
     <row r="7" spans="2:74" ht="23.1" customHeight="1">
-      <c r="B7" s="242" t="s">
+      <c r="B7" s="262" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="251" t="s">
+      <c r="C7" s="270" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="246" t="s">
+      <c r="D7" s="266" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="256" t="s">
+      <c r="E7" s="242" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="257"/>
-      <c r="G7" s="258"/>
-      <c r="H7" s="244" t="s">
+      <c r="F7" s="243"/>
+      <c r="G7" s="244"/>
+      <c r="H7" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="248" t="s">
+      <c r="I7" s="268" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="249" t="s">
+      <c r="J7" s="269" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="262" t="s">
+      <c r="K7" s="248" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="263" t="s">
+      <c r="L7" s="250" t="s">
         <v>15</v>
       </c>
-      <c r="M7" s="265" t="s">
+      <c r="M7" s="252" t="s">
         <v>16</v>
       </c>
-      <c r="N7" s="240"/>
-      <c r="O7" s="240"/>
-      <c r="P7" s="240"/>
-      <c r="Q7" s="241"/>
-      <c r="R7" s="266" t="s">
+      <c r="N7" s="253"/>
+      <c r="O7" s="253"/>
+      <c r="P7" s="253"/>
+      <c r="Q7" s="254"/>
+      <c r="R7" s="255" t="s">
         <v>17</v>
       </c>
-      <c r="S7" s="240"/>
-      <c r="T7" s="240"/>
-      <c r="U7" s="240"/>
-      <c r="V7" s="241"/>
-      <c r="W7" s="266" t="s">
+      <c r="S7" s="253"/>
+      <c r="T7" s="253"/>
+      <c r="U7" s="253"/>
+      <c r="V7" s="254"/>
+      <c r="W7" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="X7" s="240"/>
-      <c r="Y7" s="240"/>
-      <c r="Z7" s="240"/>
-      <c r="AA7" s="241"/>
-      <c r="AB7" s="268" t="s">
+      <c r="X7" s="253"/>
+      <c r="Y7" s="253"/>
+      <c r="Z7" s="253"/>
+      <c r="AA7" s="254"/>
+      <c r="AB7" s="257" t="s">
         <v>19</v>
       </c>
-      <c r="AC7" s="240"/>
-      <c r="AD7" s="240"/>
-      <c r="AE7" s="240"/>
-      <c r="AF7" s="241"/>
-      <c r="AG7" s="269" t="s">
+      <c r="AC7" s="253"/>
+      <c r="AD7" s="253"/>
+      <c r="AE7" s="253"/>
+      <c r="AF7" s="254"/>
+      <c r="AG7" s="258" t="s">
         <v>20</v>
       </c>
-      <c r="AH7" s="240"/>
-      <c r="AI7" s="240"/>
-      <c r="AJ7" s="240"/>
-      <c r="AK7" s="241"/>
-      <c r="AL7" s="269" t="s">
+      <c r="AH7" s="253"/>
+      <c r="AI7" s="253"/>
+      <c r="AJ7" s="253"/>
+      <c r="AK7" s="254"/>
+      <c r="AL7" s="258" t="s">
         <v>21</v>
       </c>
-      <c r="AM7" s="240"/>
-      <c r="AN7" s="240"/>
-      <c r="AO7" s="240"/>
-      <c r="AP7" s="241"/>
-      <c r="AQ7" s="267" t="s">
+      <c r="AM7" s="253"/>
+      <c r="AN7" s="253"/>
+      <c r="AO7" s="253"/>
+      <c r="AP7" s="254"/>
+      <c r="AQ7" s="256" t="s">
         <v>22</v>
       </c>
-      <c r="AR7" s="240"/>
-      <c r="AS7" s="240"/>
-      <c r="AT7" s="240"/>
-      <c r="AU7" s="241"/>
-      <c r="AV7" s="270" t="s">
+      <c r="AR7" s="253"/>
+      <c r="AS7" s="253"/>
+      <c r="AT7" s="253"/>
+      <c r="AU7" s="254"/>
+      <c r="AV7" s="259" t="s">
         <v>23</v>
       </c>
-      <c r="AW7" s="240"/>
-      <c r="AX7" s="240"/>
-      <c r="AY7" s="240"/>
-      <c r="AZ7" s="241"/>
-      <c r="BA7" s="270" t="s">
+      <c r="AW7" s="253"/>
+      <c r="AX7" s="253"/>
+      <c r="AY7" s="253"/>
+      <c r="AZ7" s="254"/>
+      <c r="BA7" s="259" t="s">
         <v>24</v>
       </c>
-      <c r="BB7" s="240"/>
-      <c r="BC7" s="240"/>
-      <c r="BD7" s="240"/>
-      <c r="BE7" s="241"/>
-      <c r="BF7" s="271" t="s">
+      <c r="BB7" s="253"/>
+      <c r="BC7" s="253"/>
+      <c r="BD7" s="253"/>
+      <c r="BE7" s="254"/>
+      <c r="BF7" s="260" t="s">
         <v>25</v>
       </c>
-      <c r="BG7" s="240"/>
-      <c r="BH7" s="240"/>
-      <c r="BI7" s="240"/>
-      <c r="BJ7" s="241"/>
+      <c r="BG7" s="253"/>
+      <c r="BH7" s="253"/>
+      <c r="BI7" s="253"/>
+      <c r="BJ7" s="254"/>
       <c r="BK7" s="272" t="s">
         <v>26</v>
       </c>
-      <c r="BL7" s="240"/>
-      <c r="BM7" s="240"/>
-      <c r="BN7" s="240"/>
-      <c r="BO7" s="241"/>
+      <c r="BL7" s="253"/>
+      <c r="BM7" s="253"/>
+      <c r="BN7" s="253"/>
+      <c r="BO7" s="254"/>
       <c r="BP7" s="272" t="s">
         <v>27</v>
       </c>
-      <c r="BQ7" s="240"/>
-      <c r="BR7" s="240"/>
-      <c r="BS7" s="240"/>
-      <c r="BT7" s="241"/>
+      <c r="BQ7" s="253"/>
+      <c r="BR7" s="253"/>
+      <c r="BS7" s="253"/>
+      <c r="BT7" s="254"/>
       <c r="BU7" s="38"/>
       <c r="BV7" s="39"/>
     </row>
     <row r="8" spans="2:74" ht="23.1" customHeight="1" thickBot="1">
-      <c r="B8" s="243"/>
-      <c r="C8" s="252"/>
-      <c r="D8" s="247"/>
+      <c r="B8" s="263"/>
+      <c r="C8" s="271"/>
+      <c r="D8" s="267"/>
       <c r="E8" s="58" t="s">
         <v>28</v>
       </c>
@@ -29835,11 +31167,11 @@
       <c r="G8" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="245"/>
-      <c r="I8" s="241"/>
-      <c r="J8" s="250"/>
-      <c r="K8" s="250"/>
-      <c r="L8" s="264"/>
+      <c r="H8" s="265"/>
+      <c r="I8" s="254"/>
+      <c r="J8" s="249"/>
+      <c r="K8" s="249"/>
+      <c r="L8" s="251"/>
       <c r="M8" s="61" t="s">
         <v>31</v>
       </c>
@@ -33359,13 +34691,6 @@
     <row r="42" spans="2:74" ht="216.95" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="BP7:BT7"/>
-    <mergeCell ref="AL7:AP7"/>
-    <mergeCell ref="AQ7:AU7"/>
-    <mergeCell ref="AV7:AZ7"/>
-    <mergeCell ref="BA7:BE7"/>
-    <mergeCell ref="BF7:BJ7"/>
-    <mergeCell ref="BK7:BO7"/>
     <mergeCell ref="AG7:AK7"/>
     <mergeCell ref="K2:K6"/>
     <mergeCell ref="B7:B8"/>
@@ -33381,6 +34706,13 @@
     <mergeCell ref="R7:V7"/>
     <mergeCell ref="W7:AA7"/>
     <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="BP7:BT7"/>
+    <mergeCell ref="AL7:AP7"/>
+    <mergeCell ref="AQ7:AU7"/>
+    <mergeCell ref="AV7:AZ7"/>
+    <mergeCell ref="BA7:BE7"/>
+    <mergeCell ref="BF7:BJ7"/>
+    <mergeCell ref="BK7:BO7"/>
   </mergeCells>
   <conditionalFormatting sqref="L9:L33">
     <cfRule type="dataBar" priority="1">
@@ -33397,7 +34729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
@@ -34125,272 +35457,4 @@
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0" footer="0"/>
   <pageSetup scale="53" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
-    <tabColor theme="3" tint="0.79998168889431442"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:F39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.125" defaultRowHeight="15.75"/>
-  <cols>
-    <col min="1" max="1" width="3.25" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="65.875" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="13.875" customWidth="1"/>
-    <col min="6" max="6" width="3.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:6" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B1" s="106" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="15"/>
-    </row>
-    <row r="2" spans="2:6" ht="20.100000000000001" customHeight="1">
-      <c r="B2" s="128" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="128" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="129" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="130" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="100"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="104"/>
-    </row>
-    <row r="4" spans="2:6" ht="20.100000000000001" customHeight="1">
-      <c r="B4" s="100"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="104"/>
-    </row>
-    <row r="5" spans="2:6" ht="20.100000000000001" customHeight="1">
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="104"/>
-    </row>
-    <row r="6" spans="2:6" ht="20.100000000000001" customHeight="1">
-      <c r="B6" s="100"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="104"/>
-    </row>
-    <row r="7" spans="2:6" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="104"/>
-    </row>
-    <row r="8" spans="2:6" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="100"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="101"/>
-      <c r="E8" s="104"/>
-    </row>
-    <row r="9" spans="2:6" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="100"/>
-      <c r="C9" s="100"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="104"/>
-    </row>
-    <row r="10" spans="2:6" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="100"/>
-      <c r="C10" s="100"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="104"/>
-    </row>
-    <row r="11" spans="2:6" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="100"/>
-      <c r="C11" s="100"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="104"/>
-    </row>
-    <row r="12" spans="2:6" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="100"/>
-      <c r="C12" s="100"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="104"/>
-    </row>
-    <row r="13" spans="2:6" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="100"/>
-      <c r="C13" s="100"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="104"/>
-    </row>
-    <row r="14" spans="2:6" ht="20.100000000000001" customHeight="1">
-      <c r="B14" s="100"/>
-      <c r="C14" s="100"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="104"/>
-    </row>
-    <row r="15" spans="2:6" ht="20.100000000000001" customHeight="1">
-      <c r="B15" s="100"/>
-      <c r="C15" s="100"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="104"/>
-    </row>
-    <row r="16" spans="2:6" ht="20.100000000000001" customHeight="1">
-      <c r="B16" s="100"/>
-      <c r="C16" s="100"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="104"/>
-    </row>
-    <row r="17" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B17" s="100"/>
-      <c r="C17" s="100"/>
-      <c r="D17" s="101"/>
-      <c r="E17" s="104"/>
-    </row>
-    <row r="18" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B18" s="100"/>
-      <c r="C18" s="100"/>
-      <c r="D18" s="101"/>
-      <c r="E18" s="104"/>
-    </row>
-    <row r="19" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B19" s="100"/>
-      <c r="C19" s="100"/>
-      <c r="D19" s="101"/>
-      <c r="E19" s="104"/>
-    </row>
-    <row r="20" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B20" s="100"/>
-      <c r="C20" s="100"/>
-      <c r="D20" s="101"/>
-      <c r="E20" s="104"/>
-    </row>
-    <row r="21" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="100"/>
-      <c r="C21" s="100"/>
-      <c r="D21" s="101"/>
-      <c r="E21" s="104"/>
-    </row>
-    <row r="22" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B22" s="100"/>
-      <c r="C22" s="100"/>
-      <c r="D22" s="101"/>
-      <c r="E22" s="104"/>
-    </row>
-    <row r="23" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="100"/>
-      <c r="C23" s="100"/>
-      <c r="D23" s="101"/>
-      <c r="E23" s="104"/>
-    </row>
-    <row r="24" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B24" s="100"/>
-      <c r="C24" s="100"/>
-      <c r="D24" s="101"/>
-      <c r="E24" s="104"/>
-    </row>
-    <row r="25" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B25" s="100"/>
-      <c r="C25" s="100"/>
-      <c r="D25" s="101"/>
-      <c r="E25" s="104"/>
-    </row>
-    <row r="26" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B26" s="100"/>
-      <c r="C26" s="100"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="104"/>
-    </row>
-    <row r="27" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B27" s="100"/>
-      <c r="C27" s="100"/>
-      <c r="D27" s="101"/>
-      <c r="E27" s="104"/>
-    </row>
-    <row r="28" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B28" s="100"/>
-      <c r="C28" s="100"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="104"/>
-    </row>
-    <row r="29" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B29" s="100"/>
-      <c r="C29" s="100"/>
-      <c r="D29" s="101"/>
-      <c r="E29" s="104"/>
-    </row>
-    <row r="30" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B30" s="100"/>
-      <c r="C30" s="100"/>
-      <c r="D30" s="101"/>
-      <c r="E30" s="104"/>
-    </row>
-    <row r="31" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B31" s="100"/>
-      <c r="C31" s="100"/>
-      <c r="D31" s="101"/>
-      <c r="E31" s="104"/>
-    </row>
-    <row r="32" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B32" s="100"/>
-      <c r="C32" s="100"/>
-      <c r="D32" s="101"/>
-      <c r="E32" s="104"/>
-    </row>
-    <row r="33" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B33" s="100"/>
-      <c r="C33" s="100"/>
-      <c r="D33" s="101"/>
-      <c r="E33" s="104"/>
-    </row>
-    <row r="34" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B34" s="100"/>
-      <c r="C34" s="100"/>
-      <c r="D34" s="101"/>
-      <c r="E34" s="104"/>
-    </row>
-    <row r="35" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B35" s="100"/>
-      <c r="C35" s="100"/>
-      <c r="D35" s="101"/>
-      <c r="E35" s="104"/>
-    </row>
-    <row r="36" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B36" s="100"/>
-      <c r="C36" s="100"/>
-      <c r="D36" s="101"/>
-      <c r="E36" s="104"/>
-    </row>
-    <row r="37" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B37" s="100"/>
-      <c r="C37" s="100"/>
-      <c r="D37" s="101"/>
-      <c r="E37" s="104"/>
-    </row>
-    <row r="38" spans="2:5" ht="20.100000000000001" customHeight="1">
-      <c r="B38" s="100"/>
-      <c r="C38" s="100"/>
-      <c r="D38" s="101"/>
-      <c r="E38" s="104"/>
-    </row>
-    <row r="39" spans="2:5" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B39" s="102"/>
-      <c r="C39" s="102"/>
-      <c r="D39" s="103"/>
-      <c r="E39" s="105"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0" footer="0"/>
-  <pageSetup scale="97" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
 </file>